--- a/docs/data/latest_results.xlsx
+++ b/docs/data/latest_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Todas as Ofertas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Supermercado" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Categoria" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Todas as Ofertas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Por Supermercado" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Por Categoria" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +21,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -63,19 +60,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -95,30 +86,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -486,106 +474,5176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="77" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="588" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>supermercado</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>data_postagem</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>link</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Supermercado Tuiuiú</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Bazar / Eletro</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Pote Vidro Nadir Mandacaru / Maracatu 2L</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Bazar / Eletro</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Ventilador Mondial Super Power 40cm 127V Uni</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Alcoólicos Diversos</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Vinho Português Casal Garcia 750ml</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Alcoólicos Diversos</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Whisky White Horse 1L</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Bebidas / Cervejas</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Cerveja Heineken 350ml</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Skol ou Antártctica Litrinho Retornável - 300ml</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Skol Litrinho Retornável 300ml</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Antarctica Litrinho Retornável 300ml</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Original Retornável - Litrinho 300ml</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Original Litrinho Retornável 300ml</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Milho Verde Quero Lata 170g</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Corona Lata 269ml</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Long Neck Michelob Ultra 330ml</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Corona Extra 330ml</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Refrigerante Guaraná Antarctica Original 2L</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Stella Artois 600ml</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Achocolatado em Pó Chocolatto Sachê 700g</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Leite em Pó Ninho Lata Integral Instantâneo 380g</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Spaten - Multipack c/ 8 Und. - Lata 269ml</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Spaten Multipack c/ 8 Und. Lata 269ml</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Corona - Multipack c/ 8 Und. - Lata 269ml</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Corona Multipack c/ 8 Und. Lata 269ml</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Amstel Puro Malte Cx C/12x269ml</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Heineken 269 ml c/8 Latas</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Michelob Ultra Cx C/6x330ml</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Skol 269 ml Multipack c/15 Latas</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Skol - Multipack c/ 15 Und. - Lata 269ml</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Skol Multipack c/ 15 Und. Lata 269ml</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Skol 269ml Multipack c/15 Latas</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Cerveja Original 269 ml Multipack c/15 Latas</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Cervejas</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Cerveja Original Multipack C/ 15 Latas de 269ml</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Refrigerantes</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Refrigerante Pepsi 2L Sabores PET</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Sucos e Diversos</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Powerade Laranja 500ml</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel17-1.fna.fbcdn.net/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=iR530pYisUwQ7kNvwGcW66R&amp;_nc_oc=AdqjgXO5Pupn_42AQ9VpGIPMxqCD4EgX00XbVjsdR9ZoRjPe6yWF-7RI9N_eH5dfaMU&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel17-1.fna&amp;_nc_gid=UL6aT8Mg1HgX-3g_A965fg&amp;_nc_ss=72a8c&amp;oh=00_AQG3rvMT0z3oseciM-7IX_x248nvgwto9O6ti7BsWGVr1g&amp;oe=6A90E8FB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Sucos e Diversos</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Powerade Limão 500ml</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel17-1.fna.fbcdn.net/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=iR530pYisUwQ7kNvwGcW66R&amp;_nc_oc=AdqjgXO5Pupn_42AQ9VpGIPMxqCD4EgX00XbVjsdR9ZoRjPe6yWF-7RI9N_eH5dfaMU&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel17-1.fna&amp;_nc_gid=UL6aT8Mg1HgX-3g_A965fg&amp;_nc_ss=72a8c&amp;oh=00_AQG3rvMT0z3oseciM-7IX_x248nvgwto9O6ti7BsWGVr1g&amp;oe=6A90E8FB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Sucos e Diversos</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Powerade Uva 500ml</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel17-1.fna.fbcdn.net/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=iR530pYisUwQ7kNvwGcW66R&amp;_nc_oc=AdqjgXO5Pupn_42AQ9VpGIPMxqCD4EgX00XbVjsdR9ZoRjPe6yWF-7RI9N_eH5dfaMU&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel17-1.fna&amp;_nc_gid=UL6aT8Mg1HgX-3g_A965fg&amp;_nc_ss=72a8c&amp;oh=00_AQG3rvMT0z3oseciM-7IX_x248nvgwto9O6ti7BsWGVr1g&amp;oe=6A90E8FB</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Sucos e Diversos</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Salsicha Seara</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Sucos e Diversos</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Kit Copo - Zumba / Nature / Aurora - Kit Com 6 Unidades</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Sucos e Diversos</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Papel Higiênico Mili 30m Neutro e Perfumado, Folha Dupla, com 12 Unidades</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Sucos e Diversos</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Campari 998 ml</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Sucos e Diversos</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Whisky Buchanan's 12 Anos 1L</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Limpador Perfumado Casa &amp; Perfume 500ml mix</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Coxas Sobrecoxas C/Dorsal Canção</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Coxas Sobrecoxas C/Dorsal Canção KG</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778256078_18373759237237813_68945980692155706_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk2ODYwMzg1OTMyNDAzMjgwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mnkfzLJbUGcQ7kNvwEXmGqm&amp;_nc_oc=AdoC7VAUoR2ymM3sDFkxuvhl7xySk8Muws1qG326KNzVA2MlJBks66SbyREtS350pWQ&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGCU1fJW8u4iIeaRuqZw994fbhFHcy-2lRNJ1h6J-1w5A&amp;oe=6A9105C3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Coxa e Sobrecoxa Bello (kg)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Coxa com Sobrecoxa de Frango Sadia - Kg</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Frango Inteiro Congelado Seara</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>COXINHA DA ASA</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra5-1.cdninstagram.com/v/t51.82787-15/784428408_18093165719531849_770231522003913391_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDAyODMzNTQzMzkzNjEwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GmsJ3vXSy68Q7kNvwGVSkpu&amp;_nc_oc=AdrX8bB7qu-gebCkviipVGlLQBoWjR3klESFn4IDdWp5bK13cysX49UPbueDkRufjDQ&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-1.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQEDm3gEunrfUYdARNpzzDwo5CwS5UgvXEEnZXE5WYRy-g&amp;oe=6A910F00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Coxinha da Asa de Frango Super Frango 1 Kg</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Coxas de Frango Sadia Pct C/1kg</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>MOELA FRANGO SEARA PCT C/1KG</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Lasanha Sadia Sabores 600g</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Frango Inteiro Caipira Nho Bento (kg)</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Linguiça c/Pimenta Biquinho Perdigão Na Brasa 600g</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/780840877_18194460187382122_8037755132885706798_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwOTg5NjU5MjY4NjA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AVqS_fxt8Z8Q7kNvwHIXPK_&amp;_nc_oc=AdpTt1pAaMnOomHjxu-D-lqIx6IiMm5tMm7pycYUP6JlvAShGZb2E3V9KpslHHSkLCo&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQGLd45wm_Sul7Dln0PtDVkvy2tceIK-y1xOxTeXlW4wnA&amp;oe=6A90F0A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>MEIO DAS ASAS FRANGO SEARA PCT C/1KG</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Meio das Asas Sem Tempero kg</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.ffsz1-1.fna.fbcdn.net/v/t39.30808-6/784080473_1657848796345518_7184352931358203406_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk2ODk0NTQwODQ3NDQ3ODQ5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ok7KKhGT1G4Q7kNvwHXgnjf&amp;_nc_oc=Adqo4L58Vj84JS4wAevGaBjGABsqhArK3phNvzgrvCb-oLBz7cnSPjzBmEnpc-lxjUQ&amp;_nc_zt=23&amp;_nc_ht=instagram.ffsz1-1.fna&amp;_nc_gid=sBcQSkjaaUnYjycH3Stg0w&amp;_nc_ss=72689&amp;oh=00_AQF-NsdqX6GS4TyVjRlqD8NgKFriZ1MRItYeQk-XJZEAKQ&amp;oe=6A910CF5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Coração Frango Seara Pct C/1kg</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Pernil ou Paleta Suína - Kg</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Pernil e Paleta Suína Max Free</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Paleta Suína (kg)</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Bisteca Suína (kg)</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Costela Suína Max Free</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Costela Suína kg</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.ffsz1-2.fna.fbcdn.net/v/t39.30808-6/783592781_1657848779678853_846802542024845217_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQwNzM1MDQwNDUxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iB6xP_moLBkQ7kNvwFPBa6X&amp;_nc_oc=AdqJH-8uZRIQxaKMk_Ml38CUAN6JBNttUXmjoP0B92jE9WMiTxCkR2gh7TrinJ91T20&amp;_nc_zt=23&amp;_nc_ht=instagram.ffsz1-2.fna&amp;_nc_gid=sBcQSkjaaUnYjycH3Stg0w&amp;_nc_ss=72689&amp;oh=00_AQGlmL2kbhKVnG_Ve-bZ17g1P_iqz4w9A_Mn2NMYJuCosQ&amp;oe=6A9100B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Costela Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Costela Bovina (kg)</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Costela Suína com Pele Kg</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/780840877_18194460187382122_8037755132885706798_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwOTg5NjU5MjY4NjA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AVqS_fxt8Z8Q7kNvwHIXPK_&amp;_nc_oc=AdpTt1pAaMnOomHjxu-D-lqIx6IiMm5tMm7pycYUP6JlvAShGZb2E3V9KpslHHSkLCo&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQGLd45wm_Sul7Dln0PtDVkvy2tceIK-y1xOxTeXlW4wnA&amp;oe=6A90F0A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Costela Bovina Sulbeef</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Costela Minga kg</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.ffsz1-1.fna.fbcdn.net/v/t39.30808-6/784080473_1657848796345518_7184352931358203406_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk2ODk0NTQwODQ3NDQ3ODQ5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ok7KKhGT1G4Q7kNvwHXgnjf&amp;_nc_oc=Adqo4L58Vj84JS4wAevGaBjGABsqhArK3phNvzgrvCb-oLBz7cnSPjzBmEnpc-lxjUQ&amp;_nc_zt=23&amp;_nc_ht=instagram.ffsz1-1.fna&amp;_nc_gid=sBcQSkjaaUnYjycH3Stg0w&amp;_nc_ss=72689&amp;oh=00_AQF-NsdqX6GS4TyVjRlqD8NgKFriZ1MRItYeQk-XJZEAKQ&amp;oe=6A910CF5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Costela Bovina para Assar Kg</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/780840877_18194460187382122_8037755132885706798_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwOTg5NjU5MjY4NjA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AVqS_fxt8Z8Q7kNvwHIXPK_&amp;_nc_oc=AdpTt1pAaMnOomHjxu-D-lqIx6IiMm5tMm7pycYUP6JlvAShGZb2E3V9KpslHHSkLCo&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQGLd45wm_Sul7Dln0PtDVkvy2tceIK-y1xOxTeXlW4wnA&amp;oe=6A90F0A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Picanha Suína Nutribrás Kg</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/780840877_18194460187382122_8037755132885706798_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwOTg5NjU5MjY4NjA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AVqS_fxt8Z8Q7kNvwHIXPK_&amp;_nc_oc=AdpTt1pAaMnOomHjxu-D-lqIx6IiMm5tMm7pycYUP6JlvAShGZb2E3V9KpslHHSkLCo&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQGLd45wm_Sul7Dln0PtDVkvy2tceIK-y1xOxTeXlW4wnA&amp;oe=6A90F0A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>BISTECA DO C. FILÉ</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra5-1.cdninstagram.com/v/t51.82787-15/784428408_18093165719531849_770231522003913391_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDAyODMzNTQzMzkzNjEwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GmsJ3vXSy68Q7kNvwGVSkpu&amp;_nc_oc=AdrX8bB7qu-gebCkviipVGlLQBoWjR3klESFn4IDdWp5bK13cysX49UPbueDkRufjDQ&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-1.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQEDm3gEunrfUYdARNpzzDwo5CwS5UgvXEEnZXE5WYRy-g&amp;oe=6A910F00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Bisteca Mineira Kg</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/780840877_18194460187382122_8037755132885706798_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwOTg5NjU5MjY4NjA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AVqS_fxt8Z8Q7kNvwHIXPK_&amp;_nc_oc=AdpTt1pAaMnOomHjxu-D-lqIx6IiMm5tMm7pycYUP6JlvAShGZb2E3V9KpslHHSkLCo&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQGLd45wm_Sul7Dln0PtDVkvy2tceIK-y1xOxTeXlW4wnA&amp;oe=6A90F0A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Capa de Contra Filé (kg)</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>COXÃO DURO</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra5-1.cdninstagram.com/v/t51.82787-15/784428408_18093165719531849_770231522003913391_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDAyODMzNTQzMzkzNjEwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GmsJ3vXSy68Q7kNvwGVSkpu&amp;_nc_oc=AdrX8bB7qu-gebCkviipVGlLQBoWjR3klESFn4IDdWp5bK13cysX49UPbueDkRufjDQ&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-1.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQEDm3gEunrfUYdARNpzzDwo5CwS5UgvXEEnZXE5WYRy-g&amp;oe=6A910F00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Corte Grill Kg</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/780840877_18194460187382122_8037755132885706798_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwOTg5NjU5MjY4NjA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AVqS_fxt8Z8Q7kNvwHIXPK_&amp;_nc_oc=AdpTt1pAaMnOomHjxu-D-lqIx6IiMm5tMm7pycYUP6JlvAShGZb2E3V9KpslHHSkLCo&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQGLd45wm_Sul7Dln0PtDVkvy2tceIK-y1xOxTeXlW4wnA&amp;oe=6A90F0A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Capa de Contra Filé Bovina kg</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.ffsz1-1.fna.fbcdn.net/v/t39.30808-6/784080473_1657848796345518_7184352931358203406_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk2ODk0NTQwODQ3NDQ3ODQ5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ok7KKhGT1G4Q7kNvwHXgnjf&amp;_nc_oc=Adqo4L58Vj84JS4wAevGaBjGABsqhArK3phNvzgrvCb-oLBz7cnSPjzBmEnpc-lxjUQ&amp;_nc_zt=23&amp;_nc_ht=instagram.ffsz1-1.fna&amp;_nc_gid=sBcQSkjaaUnYjycH3Stg0w&amp;_nc_ss=72689&amp;oh=00_AQF-NsdqX6GS4TyVjRlqD8NgKFriZ1MRItYeQk-XJZEAKQ&amp;oe=6A910CF5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Coxão Mole (kg)</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Patinho Bovino (kg)</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Fraldinha Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Picanha Fatiada Bovina kg</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.ffsz1-1.fna.fbcdn.net/v/t39.30808-6/784080473_1657848796345518_7184352931358203406_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk2ODk0NTQwODQ3NDQ3ODQ5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ok7KKhGT1G4Q7kNvwHXgnjf&amp;_nc_oc=Adqo4L58Vj84JS4wAevGaBjGABsqhArK3phNvzgrvCb-oLBz7cnSPjzBmEnpc-lxjUQ&amp;_nc_zt=23&amp;_nc_ht=instagram.ffsz1-1.fna&amp;_nc_gid=sBcQSkjaaUnYjycH3Stg0w&amp;_nc_ss=72689&amp;oh=00_AQF-NsdqX6GS4TyVjRlqD8NgKFriZ1MRItYeQk-XJZEAKQ&amp;oe=6A910CF5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Cupim Mexicano Kg</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/780840877_18194460187382122_8037755132885706798_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwOTg5NjU5MjY4NjA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AVqS_fxt8Z8Q7kNvwHIXPK_&amp;_nc_oc=AdpTt1pAaMnOomHjxu-D-lqIx6IiMm5tMm7pycYUP6JlvAShGZb2E3V9KpslHHSkLCo&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQGLd45wm_Sul7Dln0PtDVkvy2tceIK-y1xOxTeXlW4wnA&amp;oe=6A90F0A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Maminha Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>MAMINHA</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra5-1.cdninstagram.com/v/t51.82787-15/784428408_18093165719531849_770231522003913391_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDAyODMzNTQzMzkzNjEwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GmsJ3vXSy68Q7kNvwGVSkpu&amp;_nc_oc=AdrX8bB7qu-gebCkviipVGlLQBoWjR3klESFn4IDdWp5bK13cysX49UPbueDkRufjDQ&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-1.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQEDm3gEunrfUYdARNpzzDwo5CwS5UgvXEEnZXE5WYRy-g&amp;oe=6A910F00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Cupim Bovino kg</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.ffsz1-2.fna.fbcdn.net/v/t39.30808-6/783592781_1657848779678853_846802542024845217_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQwNzM1MDQwNDUxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iB6xP_moLBkQ7kNvwFPBa6X&amp;_nc_oc=AdqJH-8uZRIQxaKMk_Ml38CUAN6JBNttUXmjoP0B92jE9WMiTxCkR2gh7TrinJ91T20&amp;_nc_zt=23&amp;_nc_ht=instagram.ffsz1-2.fna&amp;_nc_gid=sBcQSkjaaUnYjycH3Stg0w&amp;_nc_ss=72689&amp;oh=00_AQGlmL2kbhKVnG_Ve-bZ17g1P_iqz4w9A_Mn2NMYJuCosQ&amp;oe=6A9100B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Bananinha a Vácuo Boi Branco Kg</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/780840877_18194460187382122_8037755132885706798_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwOTg5NjU5MjY4NjA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AVqS_fxt8Z8Q7kNvwHIXPK_&amp;_nc_oc=AdpTt1pAaMnOomHjxu-D-lqIx6IiMm5tMm7pycYUP6JlvAShGZb2E3V9KpslHHSkLCo&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQGLd45wm_Sul7Dln0PtDVkvy2tceIK-y1xOxTeXlW4wnA&amp;oe=6A90F0A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Alcatra Bovina Kg</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Bovina</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Maminha a Vácuo Friboi Kg</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/780840877_18194460187382122_8037755132885706798_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwOTg5NjU5MjY4NjA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AVqS_fxt8Z8Q7kNvwHIXPK_&amp;_nc_oc=AdpTt1pAaMnOomHjxu-D-lqIx6IiMm5tMm7pycYUP6JlvAShGZb2E3V9KpslHHSkLCo&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQGLd45wm_Sul7Dln0PtDVkvy2tceIK-y1xOxTeXlW4wnA&amp;oe=6A90F0A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Peixes</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Peixe Tambatinga (kg)</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Peixes</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Peixe Inteiro Pintado</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>HAMBURGUER BOVINO E AVES SADIA 56G</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Mortadela Defumada Sadia 180g</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>PERNIL SUINO</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra5-1.cdninstagram.com/v/t51.82787-15/784428408_18093165719531849_770231522003913391_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDAyODMzNTQzMzkzNjEwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GmsJ3vXSy68Q7kNvwGVSkpu&amp;_nc_oc=AdrX8bB7qu-gebCkviipVGlLQBoWjR3klESFn4IDdWp5bK13cysX49UPbueDkRufjDQ&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-1.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQEDm3gEunrfUYdARNpzzDwo5CwS5UgvXEEnZXE5WYRy-g&amp;oe=6A910F00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Mortadela Perdigão Bolognella - Kg</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Linguiça Calabresa Excelência Black 400g</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Pernil Suíno (kg)</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Linguiça Toscana Excelência (kg)</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>LINGUIÇA TIPO CALABRESA ENROLADINHA PERDIGÃO 500G</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Linguiça Toscana Excelência Kg</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/780840877_18194460187382122_8037755132885706798_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwOTg5NjU5MjY4NjA3MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=AVqS_fxt8Z8Q7kNvwHIXPK_&amp;_nc_oc=AdpTt1pAaMnOomHjxu-D-lqIx6IiMm5tMm7pycYUP6JlvAShGZb2E3V9KpslHHSkLCo&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQGLd45wm_Sul7Dln0PtDVkvy2tceIK-y1xOxTeXlW4wnA&amp;oe=6A90F0A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Linguiça Toscana Excelência</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA TOSCANA EXCELÊNCIA</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra5-1.cdninstagram.com/v/t51.82787-15/784428408_18093165719531849_770231522003913391_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDAyODMzNTQzMzkzNjEwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GmsJ3vXSy68Q7kNvwGVSkpu&amp;_nc_oc=AdrX8bB7qu-gebCkviipVGlLQBoWjR3klESFn4IDdWp5bK13cysX49UPbueDkRufjDQ&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-1.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQEDm3gEunrfUYdARNpzzDwo5CwS5UgvXEEnZXE5WYRy-g&amp;oe=6A910F00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Bacon Fatiado Perdigão 250g</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Linguiça Suína Api. - Kg</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Linguiça Apimentada (kg)</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Presunto Cozido Excelência</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Mortadela Fatiada Perdigão Ouro (kg)</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Presunto Fatiado (kg)</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Salame Italiano Sadia (kg)</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Congelados e Sobremesas</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Pizza Sadia Sabores 460g</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Higiene / Cuidados Pessoais</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Sabonete em Barra Nivea Fragrâncias 85g</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Higiene / Cuidados Pessoais</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Desodorante Aerosol Antitranspirante Nivea Fragrâncias 150ml</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Higiene / Cuidados Pessoais</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Fralda Huggies tripla proteção mega mix tamanhos</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Higiene / Cuidados Pessoais</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Fralda Bovina kg</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>44.99</v>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.ffsz1-1.fna.fbcdn.net/v/t39.30808-6/784080473_1657848796345518_7184352931358203406_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk2ODk0NTQwODQ3NDQ3ODQ5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=ok7KKhGT1G4Q7kNvwHXgnjf&amp;_nc_oc=Adqo4L58Vj84JS4wAevGaBjGABsqhArK3phNvzgrvCb-oLBz7cnSPjzBmEnpc-lxjUQ&amp;_nc_zt=23&amp;_nc_ht=instagram.ffsz1-1.fna&amp;_nc_gid=sBcQSkjaaUnYjycH3Stg0w&amp;_nc_ss=72689&amp;oh=00_AQF-NsdqX6GS4TyVjRlqD8NgKFriZ1MRItYeQk-XJZEAKQ&amp;oe=6A910CF5</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Hortifruti / Ovos</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Melancia</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/783255974_18093165728531849_313858570458509058_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDAyODMzNjE3MjA4NzkxNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=S3NzwTUdCcYQ7kNvwHQETia&amp;_nc_oc=AdqMxt7aEVykCarUHYulNruhakhZYQkrGNgn9MR1j44U4bQTYNfZFmIQO6uLuCHZZx8&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQHrtCmfbQupjkZtpj2kHAWEcHqJc6FpuSBMXa3hfafI0g&amp;oe=6A9107BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Hortifruti / Ovos</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Batata Kg</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Hortifruti / Ovos</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/783255974_18093165728531849_313858570458509058_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDAyODMzNjE3MjA4NzkxNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=S3NzwTUdCcYQ7kNvwHQETia&amp;_nc_oc=AdqMxt7aEVykCarUHYulNruhakhZYQkrGNgn9MR1j44U4bQTYNfZFmIQO6uLuCHZZx8&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQHrtCmfbQupjkZtpj2kHAWEcHqJc6FpuSBMXa3hfafI0g&amp;oe=6A9107BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Hortifruti / Ovos</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Alface Un</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Hortifruti / Ovos</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Cebola Kg</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Hortifruti / Ovos</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Cebola Kg</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Hortifruti / Ovos</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Alface - Und.</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Hortifruti / Ovos</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Abacaxi</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/783255974_18093165728531849_313858570458509058_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDAyODMzNjE3MjA4NzkxNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=S3NzwTUdCcYQ7kNvwHQETia&amp;_nc_oc=AdqMxt7aEVykCarUHYulNruhakhZYQkrGNgn9MR1j44U4bQTYNfZFmIQO6uLuCHZZx8&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQHrtCmfbQupjkZtpj2kHAWEcHqJc6FpuSBMXa3hfafI0g&amp;oe=6A9107BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Hortifruti / Ovos</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Uva Vitória BDJ</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/783255974_18093165728531849_313858570458509058_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDAyODMzNjE3MjA4NzkxNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=S3NzwTUdCcYQ7kNvwHQETia&amp;_nc_oc=AdqMxt7aEVykCarUHYulNruhakhZYQkrGNgn9MR1j44U4bQTYNfZFmIQO6uLuCHZZx8&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQHrtCmfbQupjkZtpj2kHAWEcHqJc6FpuSBMXa3hfafI0g&amp;oe=6A9107BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Empanado Frango c/Queijo Seara 100g</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Leite Uht Piracanjuba Semi/Desnatado</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Leite Condensado Piracanjuba TP 395g</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Leite Piracanjuba Semi - TP 1 Litro</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Leite Piracanjuba Desnatado - TP 1 Litro</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Requeijão Boua - 180g</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Requeijão Catupiry Pote 200g - Tradicional</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Requeijão Cremoso Tradicional ou Light Catupiry 200g</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>QUEIJO MUSSARELA FATIADA PIRACANJUBA 150G</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Manteiga Brasilac Pote 500g</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>SALGADINHOS DORITOS QUEIJO NACHO 183G</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Salgado Assado de Presunto, Queijo e Tomate Kg</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Desinfetante Uau 2L - Fragrâncias</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Amaciante Concentrado Downy 500ml - Fragrâncias</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Detergente em Pó Tixan 800g Sachê</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Lava-Roupas Líquido Omo Ciclo Rápido 750ml</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Detergente em Pó Omo 2,2 Kg Lavagem Perfeita - Caixa</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/778794332_18373759255237813_8826403310576910692_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MzYxMTAyNjY2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DryH40MHA-0Q7kNvwEvPMk5&amp;_nc_oc=AdoBY9nLjJ7lwJ5DYL1N0eP_xSN0wh29CQl3IicBMMqFmmTMhMA7Ic9-kqavP-kLoBE&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQF6iyq_nChaG0T1lWjjrCaEmhoamvPrt8vnwK4RCLXpFQ&amp;oe=6A90ED5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Arroz</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Arroz São João Agulhinha 5 Kg</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Arroz</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>ARROZ ARBÓRIO URBANO PCT C/1KG</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Biscoitos e Doces</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>CHOCOLATE WAFER HERSHEY 120G</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Biscoitos e Doces</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Biscoito Rosquinha Adoralle Coco 500g</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
         <v>4.99</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>19/08/2026</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>https://example.com/img1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Super São Pedro</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Carnes / Bovina</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Picanha Bovina kg</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>19/08/2026</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>https://example.com/img2.jpg</t>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Biscoitos e Doces</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Capa de Contra-filé Embalado Sulbeef</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Café</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Café Brasileiro 500g Tradicional/Extra Forte</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Café</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>CAFÉ PILÃO CAFETERIA ITALIANA 500G</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Farináceos</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo Globo 1 Kg</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Grãos e Conservas</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Feijão Carioca Rei 1 Kg</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Massas</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Macarrão Semolado Galo Espaguete 500g</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Óleos e Azeites</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>AZEITE OLIVA EXTRA VIRGEM GOMES DA COSTA 500ML</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Batatinha</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/783255974_18093165728531849_313858570458509058_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDAyODMzNjE3MjA4NzkxNw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=S3NzwTUdCcYQ7kNvwHQETia&amp;_nc_oc=AdqMxt7aEVykCarUHYulNruhakhZYQkrGNgn9MR1j44U4bQTYNfZFmIQO6uLuCHZZx8&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQHrtCmfbQupjkZtpj2kHAWEcHqJc6FpuSBMXa3hfafI0g&amp;oe=6A9107BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Donuts Un</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>Água Mineral (garrafa pequena, ex: Bonafont, Puríssima) 500ml/600ml</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel17-1.fna.fbcdn.net/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=iR530pYisUwQ7kNvwGcW66R&amp;_nc_oc=AdqjgXO5Pupn_42AQ9VpGIPMxqCD4EgX00XbVjsdR9ZoRjPe6yWF-7RI9N_eH5dfaMU&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel17-1.fna&amp;_nc_gid=UL6aT8Mg1HgX-3g_A965fg&amp;_nc_ss=72a8c&amp;oh=00_AQG3rvMT0z3oseciM-7IX_x248nvgwto9O6ti7BsWGVr1g&amp;oe=6A90E8FB</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Batatinha Kg</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Mandioca Congelada kg</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.ffsz1-2.fna.fbcdn.net/v/t39.30808-6/783592781_1657848779678853_846802542024845217_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQwNzM1MDQwNDUxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iB6xP_moLBkQ7kNvwFPBa6X&amp;_nc_oc=AdqJH-8uZRIQxaKMk_Ml38CUAN6JBNttUXmjoP0B92jE9WMiTxCkR2gh7TrinJ91T20&amp;_nc_zt=23&amp;_nc_ht=instagram.ffsz1-2.fna&amp;_nc_gid=sBcQSkjaaUnYjycH3Stg0w&amp;_nc_ss=72689&amp;oh=00_AQGlmL2kbhKVnG_Ve-bZ17g1P_iqz4w9A_Mn2NMYJuCosQ&amp;oe=6A9100B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Margarina Qualy Cremosa 500g</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>BOMBONS SORTIDOS LACTA FAVORITOS 250,6G</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784389478_1657849223012142_713593503530775725_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQxMTAwNzI5MjQ2Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=4yeRiUBdoz4Q7kNvwH4CAW4&amp;_nc_oc=Adr4k_7LZLxbp0Mpc1U3LRpqJwAUdmeIxcez1RLd5l-ZUOOlW-nLlVfQjkxV6qTDi7Y&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQHNk_zWVxhT71iSTJfQ-MpAR064PheCUWWVwwYmpOPcsQ&amp;oe=6A9110F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Papel Hig. Duetto - Neutro Folha Dupla - 30m c/ 12 Rolos</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>Ponta de Peito Bovino (kg)</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-mad1-1.cdninstagram.com/v/t51.82787-15/782639788_17906516796496981_1020296803527373493_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk2ODI0NTY3NDgyMDQ2MDk5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CfekLFktTToQ7kNvwGk1Vn6&amp;_nc_oc=AdpfcgZX3vadSRYhInSRIGrquIQ8UJVdMI70DGHIb7unvfbeLbNI3ipPnARKWc__Jbk&amp;_nc_zt=23&amp;_nc_ht=scontent-mad1-1.cdninstagram.com&amp;_nc_gid=BXuiN8t91u9tBAPuGiIO2g&amp;_nc_ss=72689&amp;oh=00_AQHHEPrLACHnSGbLo88YtrEAnW0vsi7dq7Zd8RxN1uRxHA&amp;oe=6A910A4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Lenha Eucalipto São Luiz Saco c/12kg</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.ffsz1-2.fna.fbcdn.net/v/t39.30808-6/783592781_1657848779678853_846802542024845217_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQwNzM1MDQwNDUxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iB6xP_moLBkQ7kNvwFPBa6X&amp;_nc_oc=AdqJH-8uZRIQxaKMk_Ml38CUAN6JBNttUXmjoP0B92jE9WMiTxCkR2gh7TrinJ91T20&amp;_nc_zt=23&amp;_nc_ht=instagram.ffsz1-2.fna&amp;_nc_gid=sBcQSkjaaUnYjycH3Stg0w&amp;_nc_ss=72689&amp;oh=00_AQGlmL2kbhKVnG_Ve-bZ17g1P_iqz4w9A_Mn2NMYJuCosQ&amp;oe=6A9100B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>Ponta de Peito Bovino Kg</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-bcn1-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=8hrJBMNPgMwQ7kNvwGnUvJT&amp;_nc_oc=AdoYXp6jvZRcmSMGgqmF11k841hgU8gGUrOfeORSS__62St6UXnxn_bR0QriGzcVs-Y&amp;_nc_zt=23&amp;_nc_ht=scontent-bcn1-1.cdninstagram.com&amp;_nc_gid=UupPG7b4DGODvN3vuiZpZQ&amp;_nc_ss=7c689&amp;oh=00_AQGFPth_49ZkwKhabICc3goRl2cNXRyeZKwTHgN8ZR1PEg&amp;oe=6A90FC60</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>CAPA C. FILÉ</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra5-1.cdninstagram.com/v/t51.82787-15/784428408_18093165719531849_770231522003913391_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDAyODMzNTQzMzkzNjEwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GmsJ3vXSy68Q7kNvwGVSkpu&amp;_nc_oc=AdrX8bB7qu-gebCkviipVGlLQBoWjR3klESFn4IDdWp5bK13cysX49UPbueDkRufjDQ&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-1.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQEDm3gEunrfUYdARNpzzDwo5CwS5UgvXEEnZXE5WYRy-g&amp;oe=6A910F00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>Peito Bovino kg</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.ffsz1-2.fna.fbcdn.net/v/t39.30808-6/783592781_1657848779678853_846802542024845217_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk2ODk0NTQwNzM1MDQwNDUxOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=iB6xP_moLBkQ7kNvwFPBa6X&amp;_nc_oc=AdqJH-8uZRIQxaKMk_Ml38CUAN6JBNttUXmjoP0B92jE9WMiTxCkR2gh7TrinJ91T20&amp;_nc_zt=23&amp;_nc_ht=instagram.ffsz1-2.fna&amp;_nc_gid=sBcQSkjaaUnYjycH3Stg0w&amp;_nc_ss=72689&amp;oh=00_AQGlmL2kbhKVnG_Ve-bZ17g1P_iqz4w9A_Mn2NMYJuCosQ&amp;oe=6A9100B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Assadeira Marinex com Alça 3,5 Litros</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Caixa Térmica Mor 18L</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/782170702_1657849206345477_5831566733473110975_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk2ODk0NTQxMzExMjgxNzUxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nPR0J7MpbqkQ7kNvwEzZDbd&amp;_nc_oc=Adpry1jPlvmvV7LmOysUv_LLV-FhwGPWDm6Rg71oYFbsfnxKMCaabjnOktNcjUzgqa4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQF-3Hwtj3T7Ih66se1e5vSAzuucm9zNOnyzT88McSTO4Q&amp;oe=6A90F3F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Congelados</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Pão De Queijo Tradicional Cuiabá Pct 1kg</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Congelados</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Pão de Queijo Congelado MC Pacote c/1kg</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t39.30808-6/784063255_1657849239678807_5513880334027503636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODk0NTQxMjQ4MzY4NTI0Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e3PyeUdWKzcQ7kNvwFfoIdM&amp;_nc_oc=AdpXHNojV04_Ztq9FS7FoxOJ5FhDWDxrZ-JFHheLjp9ArMiYqy2JRLdd5QbnmII9xF8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=dY8EOS28NOwxEEhDuq8XVw&amp;_nc_ss=7ca8c&amp;oh=00_AQFejW8B6oti8qQ6tfjagpZ5w86G3C84MOUzFLrW7Dm-tA&amp;oe=6A9115F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Congelados</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Pão de Queijo Kg</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Pão de Forma Visconti 400g Tradicional</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>PÃO DE ALHO BELLO 300G</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra5-1.cdninstagram.com/v/t51.82787-15/784428408_18093165719531849_770231522003913391_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDAyODMzNTQzMzkzNjEwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=GmsJ3vXSy68Q7kNvwGVSkpu&amp;_nc_oc=AdrX8bB7qu-gebCkviipVGlLQBoWjR3klESFn4IDdWp5bK13cysX49UPbueDkRufjDQ&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-1.cdninstagram.com&amp;_nc_gid=OmicEssyz1TeBVLhoQb82w&amp;_nc_ss=7c689&amp;oh=00_AQEDm3gEunrfUYdARNpzzDwo5CwS5UgvXEEnZXE5WYRy-g&amp;oe=6A910F00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>Pão de Alho Boua 300g</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fkix1-2.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=MnWLmv7izFEQ7kNvwHXigpa&amp;_nc_oc=AdoUtff4aarrhcvw-vdfk-s13MRYCT4UgBveYp6TRaSiAZD6Vv8wX0aDxTyuLBOkhm5IgTCXkxKRdPNG7AyDfS7U&amp;_nc_zt=23&amp;_nc_ht=instagram.fkix1-2.fna&amp;_nc_gid=0evyVvBYHSU_Cm4Iwk7vOg&amp;_nc_ss=72689&amp;oh=00_AQHGgjMqXbWr_LPI5_m7Ny1tjSUnuOJrNizw6mgVwGitfA&amp;oe=6A90EBEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Pão De Alho Dabrasa Sabores 450gr</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/782344855_18373759252237813_7320855115066332806_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MTkyMDUwNTIwMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EXXZ6F7wf7QQ7kNvwExN-F_&amp;_nc_oc=Adqy_WCiNpvnqeKDoGaznLUTOweN1UIsrQuI9YOY_SXa-FPNBFlsWjSQimULI31xoac&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQGdQP6Yd6p_wT_FEaeuUfgwheGcQsrIuZgAHmm6EwP6RA&amp;oe=6A90E02C</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>Pão de Hambúrguer Kg</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fmel14-1.fna.fbcdn.net/v/t51.82787-15/779957410_18194460196382122_4239320256883363950_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk2ODYwOTg5OTE2Nzk4NjAwMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE2MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lCs7XFPuzTIQ7kNvwHFF4nb&amp;_nc_oc=Adqdqo2VsTckPHVJ3EiF5nzerW_qgr3tOsXCIILFRiDdN1BxLl6gCZq4Cq5ABetFCxQ&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel14-1.fna&amp;_nc_gid=ux6Z-qOe2dV0WH5WnJr3RA&amp;_nc_ss=72a8c&amp;oh=00_AQFmdrN31hz1yAFrEjucFs5FYgWCLEDLeOOPE8Un15Fgpg&amp;oe=6A90F1C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Pet Shop</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Ração para Cão Thor Adulto 7 Kg</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/779844446_18373759273237813_717042095228036520_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2ODYwMzg2MjA2MzE4NjIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=m8__0j7aHxEQ7kNvwHQgQM1&amp;_nc_oc=Adqqyzxf80dnGdfoMUDYLQ78auIhXgsQRmXFG1xjO8D1VrOcfIzrq0jKFCCJUO17l1k&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=F6S7ALtEyd_ZpDSi6b98wg&amp;_nc_ss=7c689&amp;oh=00_AQFiCdSVvzE-0y00eD8uLFeynPRShLQQTeh0LsTyhUq5yg&amp;oe=6A90ED30</t>
         </is>
       </c>
     </row>
@@ -600,79 +5658,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>supermercado</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Qtd_Itens</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Preco_Medio</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Preco_Minimo</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Preco_Maximo</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Super São Pedro</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>59.9</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>20.98104166666667</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>189.9</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Supermercado Tuiuiú</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>4.99</v>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Talismã</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>17.10538461538462</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO PARANAENSE</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>23.15666666666667</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>40.99</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>17.485</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>47.99</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Bianchi</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>27.76568181818182</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>159.9</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>28.57863636363636</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>56.99</v>
       </c>
     </row>
   </sheetData>
@@ -686,67 +5820,451 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Qtd_Itens</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Preco_Medio</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Preco_Minimo</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bazar / Eletro</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>87.44500000000001</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Alcoólicos Diversos</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>77.44499999999999</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>69.98999999999999</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Bebidas / Cervejas</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B4" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>23.03653846153846</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Bebidas / Refrigerantes</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="C5" s="7" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Bebidas / Sucos e Diversos</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>38.1175</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Aves</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>15.03375</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Carnes / Bovina</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B8" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>32.37333333333333</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Carnes / Peixes</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Carnes / Suína e Embutidos</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>18.01222222222222</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Congelados e Sobremesas</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>59.9</v>
+      <c r="C11" s="7" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Higiene / Cuidados Pessoais</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Hortifruti / Ovos</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>4.612222222222223</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Laticínios / Leites e Derivados</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>10.315</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Limpeza / Cuidados com a Casa</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Limpeza / Lavanderia e Louça</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Arroz</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>18.445</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Biscoitos e Doces</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Café</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>22.49</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Farináceos</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Grãos e Conservas</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Mercearia / Massas</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Mercearia / Óleos e Azeites</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>23.56466666666667</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Congelados</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Pet Shop</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>64.90000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/latest_results.xlsx
+++ b/docs/data/latest_results.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -482,7 +482,7 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="623" customWidth="1" min="6" max="6"/>
+    <col width="628" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -530,7 +530,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Pote Tramontina Mix Color 600ml</t>
+          <t>Pote Plástico Tramontina Mix Color 600ml</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
@@ -573,14 +573,14 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -590,20 +590,20 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Molho de Tomate Fugini 1.02kg</t>
+          <t>Molho de Tomate Fugini 300g</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.49</v>
+        <v>1.69</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Vinho Cristóbal 750ml</t>
+          <t>Vinho Casal Mendes Sweet 750ml</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -718,12 +718,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Vinho Cristóbal 750ml</t>
+          <t>Vinho Casal Mendes 750ml</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -748,19 +748,19 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -770,11 +770,11 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Sérum Facial Garnier Vitamina C 100ml</t>
+          <t>Vinho Cristóbal 750ml</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>36.99</v>
+        <v>35.9</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -783,44 +783,44 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Cervejas</t>
+          <t>Bebidas / Alcoólicos Diversos</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Skol Ou Antarctica Retornável 300ml</t>
+          <t>Sérum Facial Garnier Vitamina C 100ml</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2.49</v>
+        <v>36.99</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169173_1720016753465476_6179349585647048120_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTMwMjI3OTYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=IfjxdZLhTj8Q7kNvwHoxM7u&amp;_nc_oc=AdqFG2almShqhQbnniQ7XN3sI_NFw2Oyzi1CpVIZpY1mvxTQAzo0IvykjW6alh2_i2A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQGcKbMaxGyQVtpPB59qnZj53gOvmC_hpMxcg_cgyo9_nQ&amp;oe=6A97DA21</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Antarctica 300ml</t>
+          <t>Cerveja Brahma 300ml</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -868,19 +868,19 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169173_1720016753465476_6179349585647048120_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTMwMjI3OTYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=IfjxdZLhTj8Q7kNvwHoxM7u&amp;_nc_oc=AdqFG2almShqhQbnniQ7XN3sI_NFw2Oyzi1CpVIZpY1mvxTQAzo0IvykjW6alh2_i2A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQGcKbMaxGyQVtpPB59qnZj53gOvmC_hpMxcg_cgyo9_nQ&amp;oe=6A97DA21</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Antarctica Original Retornável 300ml</t>
+          <t>Cerveja Original 300ml</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -898,19 +898,19 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/787853786_18195711469382122_4084613579796731411_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MzY3MjU2ODk4MzkzOTE2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mrOwFRh3sK8Q7kNvwGuiPxU&amp;_nc_oc=AdocWchk5QRpVZ8dLBXgW047kqu1zOIqox1GJTIk1w9BH6Gir0_2USO05ktxY04PMUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQFkCEs3hpn9RALf_1PUmHbNNicLtXSXUXy77R9obJWZgw&amp;oe=6A97CD87</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -920,27 +920,27 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Original 300ml</t>
+          <t>Saco Para Lixo Giopack Super Reforçado 30L 15L</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2.69</v>
+        <v>8.49</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -950,11 +950,11 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Saco Para Lixo Super Reforçado Giopack 30L 15L</t>
+          <t>Cerveja Império Ultra 12x269ml</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8.49</v>
+        <v>34.68</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -963,14 +963,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/788413222_1505168981656218_2918311736305518854_n.jpg?stp=c0.0.1638.2047a_dst-jpg_e35_s1638x2047_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzI3Njk2ODIzODI0MjE0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=G9lgZfFlLu0Q7kNvwF_JwlB&amp;_nc_oc=Adq9GwtOFmluK0l6bqtQD3-7JUdW48aHa_sTCsAnFrPTnylb2VgrBqoFFUk8N2umuJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQF_adVKWUB6yUSzhjAFyPiJHdJ3qkmFIpb3HWhALtZ2Rw&amp;oe=6A97B160</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -980,27 +980,27 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Spaten 269ml 8 Unidades</t>
+          <t>Cerveja Heineken 8x269ml</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>29.52</v>
+        <v>34.99</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169173_1720016753465476_6179349585647048120_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTMwMjI3OTYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=IfjxdZLhTj8Q7kNvwHoxM7u&amp;_nc_oc=AdqFG2almShqhQbnniQ7XN3sI_NFw2Oyzi1CpVIZpY1mvxTQAzo0IvykjW6alh2_i2A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQGcKbMaxGyQVtpPB59qnZj53gOvmC_hpMxcg_cgyo9_nQ&amp;oe=6A97DA21</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1010,27 +1010,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Spaten 8x269ml</t>
+          <t>Cerveja Heineken 269ml 8 Latas</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>29.52</v>
+        <v>35.92</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/787853786_18195711469382122_4084613579796731411_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MzY3MjU2ODk4MzkzOTE2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mrOwFRh3sK8Q7kNvwGuiPxU&amp;_nc_oc=AdocWchk5QRpVZ8dLBXgW047kqu1zOIqox1GJTIk1w9BH6Gir0_2USO05ktxY04PMUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQFkCEs3hpn9RALf_1PUmHbNNicLtXSXUXy77R9obJWZgw&amp;oe=6A97CD87</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1040,27 +1040,27 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Corona 269ml 8 Unidades</t>
+          <t>Cerveja Skol 15x269ml</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>34.32</v>
+        <v>43.35</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169173_1720016753465476_6179349585647048120_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTMwMjI3OTYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=IfjxdZLhTj8Q7kNvwHoxM7u&amp;_nc_oc=AdqFG2almShqhQbnniQ7XN3sI_NFw2Oyzi1CpVIZpY1mvxTQAzo0IvykjW6alh2_i2A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQGcKbMaxGyQVtpPB59qnZj53gOvmC_hpMxcg_cgyo9_nQ&amp;oe=6A97DA21</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1070,27 +1070,27 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Corona 8x269ml</t>
+          <t>Cerveja Brahma 15x269ml</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>34.32</v>
+        <v>43.35</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169173_1720016753465476_6179349585647048120_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTMwMjI3OTYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=IfjxdZLhTj8Q7kNvwHoxM7u&amp;_nc_oc=AdqFG2almShqhQbnniQ7XN3sI_NFw2Oyzi1CpVIZpY1mvxTQAzo0IvykjW6alh2_i2A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQGcKbMaxGyQVtpPB59qnZj53gOvmC_hpMxcg_cgyo9_nQ&amp;oe=6A97DA21</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/784389246_18581502034067900_514741470007781001_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MjE4Nzk0NDI0MDc2NjUyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=axgGxUji1CYQ7kNvwF5yFe_&amp;_nc_oc=AdoPdvXKkxhOnuhRHqGiq6Pt03mMi3YFrFv35FgdwDW_XLaCuthau9xVtjxvSvd3Et0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGnyh9C5KtZnA7Clr6PJqSdV_he0XIhN4EcSf3kil01jw&amp;oe=6A967986</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/788413222_1505168981656218_2918311736305518854_n.jpg?stp=c0.0.1638.2047a_dst-jpg_e35_s1638x2047_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzI3Njk2ODIzODI0MjE0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=G9lgZfFlLu0Q7kNvwF_JwlB&amp;_nc_oc=Adq9GwtOFmluK0l6bqtQD3-7JUdW48aHa_sTCsAnFrPTnylb2VgrBqoFFUk8N2umuJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQF_adVKWUB6yUSzhjAFyPiJHdJ3qkmFIpb3HWhALtZ2Rw&amp;oe=6A97B160</t>
         </is>
       </c>
     </row>
@@ -1130,27 +1130,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Brahma 15x269ml</t>
+          <t>Cerveja Antarctica Original 15x269ml</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>43.35</v>
+        <v>50.85</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/784389246_18581502034067900_514741470007781001_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MjE4Nzk0NDI0MDc2NjUyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=axgGxUji1CYQ7kNvwF5yFe_&amp;_nc_oc=AdoPdvXKkxhOnuhRHqGiq6Pt03mMi3YFrFv35FgdwDW_XLaCuthau9xVtjxvSvd3Et0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGnyh9C5KtZnA7Clr6PJqSdV_he0XIhN4EcSf3kil01jw&amp;oe=6A967986</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169173_1720016753465476_6179349585647048120_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTMwMjI3OTYzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=IfjxdZLhTj8Q7kNvwHoxM7u&amp;_nc_oc=AdqFG2almShqhQbnniQ7XN3sI_NFw2Oyzi1CpVIZpY1mvxTQAzo0IvykjW6alh2_i2A&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQGcKbMaxGyQVtpPB59qnZj53gOvmC_hpMxcg_cgyo9_nQ&amp;oe=6A97DA21</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Cerveja Skol 269ml 15 Unidades</t>
+          <t>Cerveja Original 15x269ml</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>43.35</v>
+        <v>50.85</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/788413222_1505168981656218_2918311736305518854_n.jpg?stp=c0.0.1638.2047a_dst-jpg_e35_s1638x2047_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzI3Njk2ODIzODI0MjE0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=G9lgZfFlLu0Q7kNvwF_JwlB&amp;_nc_oc=Adq9GwtOFmluK0l6bqtQD3-7JUdW48aHa_sTCsAnFrPTnylb2VgrBqoFFUk8N2umuJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQF_adVKWUB6yUSzhjAFyPiJHdJ3qkmFIpb3HWhALtZ2Rw&amp;oe=6A97B160</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1190,20 +1190,20 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Cerveja Skol 15x269ml</t>
+          <t>Cerveja Heineken 5L</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>43.35</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/787853786_18195711469382122_4084613579796731411_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MzY3MjU2ODk4MzkzOTE2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mrOwFRh3sK8Q7kNvwGuiPxU&amp;_nc_oc=AdocWchk5QRpVZ8dLBXgW047kqu1zOIqox1GJTIk1w9BH6Gir0_2USO05ktxY04PMUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQFkCEs3hpn9RALf_1PUmHbNNicLtXSXUXy77R9obJWZgw&amp;oe=6A97CD87</t>
         </is>
       </c>
     </row>
@@ -1220,57 +1220,57 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Sukita 2L</t>
+          <t>Refrigerante Sukita 2L</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>6.29</v>
+        <v>5.99</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/784389246_18581502034067900_514741470007781001_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MjE4Nzk0NDI0MDc2NjUyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=axgGxUji1CYQ7kNvwF5yFe_&amp;_nc_oc=AdoPdvXKkxhOnuhRHqGiq6Pt03mMi3YFrFv35FgdwDW_XLaCuthau9xVtjxvSvd3Et0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGnyh9C5KtZnA7Clr6PJqSdV_he0XIhN4EcSf3kil01jw&amp;oe=6A967986</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/788141803_1720016743465477_9146230528598203595_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODE5NDkyODIxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=zal2Q-KNBSMQ7kNvwHPjmHr&amp;_nc_oc=AdqbcNw8SJgkOLjv1S7OR3EO3j7y30zWKGkWsahq3R8bq5H_zt52u3sZtfAXG8TZgRQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQEr-SUAeVtvw-YnVKjGXDiWw84vTzRbtyyL_ngY1HNfgg&amp;oe=6A97C1F6</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Bebidas / Refrigerantes</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Isotônico Powerade 500ml</t>
+          <t>Refrigerante Coca Cola 2.5L</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>5.79</v>
+        <v>10.99</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fco2-1.cdninstagram.com/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=xshLq_1UYukQ7kNvwH8NEjx&amp;_nc_oc=AdppzFu-Hh0BO5RnjF9YuSyN_3_XxabLEQ8RsW1ev3ULvAAZEuGYqgDflkGsmIgvtpk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_gid=K-hLFdWbPpxYMOy6NjRGCw&amp;_nc_ss=7a22e&amp;oh=00_AQG-b1CP2iK33dzJWt-upWfT8kFYia1MjGGgavA4Gd6j9A&amp;oe=6A96673B</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/788141803_1720016743465477_9146230528598203595_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODE5NDkyODIxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=zal2Q-KNBSMQ7kNvwHPjmHr&amp;_nc_oc=AdqbcNw8SJgkOLjv1S7OR3EO3j7y30zWKGkWsahq3R8bq5H_zt52u3sZtfAXG8TZgRQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQEr-SUAeVtvw-YnVKjGXDiWw84vTzRbtyyL_ngY1HNfgg&amp;oe=6A97C1F6</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1280,20 +1280,20 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Absorvente Intimus Tripla Proteção 8 Unidades</t>
+          <t>Isotônico Powerade 500ml</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>5.99</v>
+        <v>5.79</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=fT0MPnunqcwQ7kNvwGoHPRi&amp;_nc_oc=Ado_NnTWGAC2RLX8sNpjSvme7alGmKtaDkL87QyRjEwmsVTvTxtQgzw52rTwayJtwSM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=S9kVzKn3t-x4IZA7o9dmkA&amp;_nc_ss=7a22e&amp;oh=00_AQFChcJHGtmESsZp0K7WUFlKeaX66h-aUkvSTQNwMItcHQ&amp;oe=6A97B8BB</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fco2-1.cdninstagram.com/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=xshLq_1UYukQ7kNvwH8NEjx&amp;_nc_oc=AdppzFu-Hh0BO5RnjF9YuSyN_3_XxabLEQ8RsW1ev3ULvAAZEuGYqgDflkGsmIgvtpk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_gid=K-hLFdWbPpxYMOy6NjRGCw&amp;_nc_ss=7a22e&amp;oh=00_AQG-b1CP2iK33dzJWt-upWfT8kFYia1MjGGgavA4Gd6j9A&amp;oe=6A96673B</t>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=fT0MPnunqcwQ7kNvwGoHPRi&amp;_nc_oc=Ado_NnTWGAC2RLX8sNpjSvme7alGmKtaDkL87QyRjEwmsVTvTxtQgzw52rTwayJtwSM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=S9kVzKn3t-x4IZA7o9dmkA&amp;_nc_ss=7a22e&amp;oh=00_AQFChcJHGtmESsZp0K7WUFlKeaX66h-aUkvSTQNwMItcHQ&amp;oe=6A97B8BB</t>
         </is>
       </c>
     </row>
@@ -1340,27 +1340,27 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Monster 473ml</t>
+          <t>Suco Del Valle 1L</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/784389246_18581502034067900_514741470007781001_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MjE4Nzk0NDI0MDc2NjUyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=axgGxUji1CYQ7kNvwF5yFe_&amp;_nc_oc=AdoPdvXKkxhOnuhRHqGiq6Pt03mMi3YFrFv35FgdwDW_XLaCuthau9xVtjxvSvd3Et0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGnyh9C5KtZnA7Clr6PJqSdV_he0XIhN4EcSf3kil01jw&amp;oe=6A967986</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/788141803_1720016743465477_9146230528598203595_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODE5NDkyODIxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=zal2Q-KNBSMQ7kNvwHPjmHr&amp;_nc_oc=AdqbcNw8SJgkOLjv1S7OR3EO3j7y30zWKGkWsahq3R8bq5H_zt52u3sZtfAXG8TZgRQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQEr-SUAeVtvw-YnVKjGXDiWw84vTzRbtyyL_ngY1HNfgg&amp;oe=6A97C1F6</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Papel Higiênico Stylus 12 Unidades</t>
+          <t>Salsicha Seara kg</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786656678_18581502151067900_8490347803628786235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODA0MDI2NTAzODUyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EcdOnVlttmoQ7kNvwH70PlI&amp;_nc_oc=Ado82ixek600vX3hfhL5KCdBOomq0p34CYASZrMbpFkNDU8Rn2ZRizO3W36sjpTqpT0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQFs12_u1-T868CKgrHhWNAaA-ZCp9unoHS_lu79usCNaA&amp;oe=6A966AED</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=40xkhSQE8g4Q7kNvwHrZ6fS&amp;_nc_oc=AdrQwhyO2locrqA9fhJGOet0h1z6OSsYR_JGHtkSpAE_SO1Qxhq4nZ1AaPAQZOIjiCM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=piuLZ9j-qv6denTdiMpN-w&amp;_nc_ss=7a22e&amp;oh=00_AQHlBvIUNmHk7i3Qkz9ssRG8EZJIjOAq6Lm63Ods05W5Gw&amp;oe=6A97C121</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1400,27 +1400,27 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Salsicha Seara kg</t>
+          <t>Ovos Brancos 30 Unidades</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>10.49</v>
+        <v>11.99</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=27_NHNZ1YPEQ7kNvwFoKDXp&amp;_nc_oc=Adq93sm4yjujuKl2H9qKd7A-Ri6sPJ2O7h6MT7xu_2Gn_ICjD_O8jrpMyqpEq10pxog&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=zbuJQKO7MCB6qCV9cm71qw&amp;_nc_ss=7a22e&amp;oh=00_AQFoLPeW7mZwdNBlXkTxG1Z4Q8aI7FC9c9WBaNrB5U4a1g&amp;oe=6A966FA1</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/777867278_1720016746798810_8968857745876573698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODY1NjMwNjQwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Z9Kw3OPyQ28Q7kNvwGU7Ln_&amp;_nc_oc=AdpJfiPn_5vxe3EHndUybjPKs0Rwuwmjp82GtAJYt9vGfXm0XGC_suobP_D8GbWo6hs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQHI2faikBAuy8vCmzhrj-B7S3xTDDyOtrEIlfM262JxSw&amp;oe=6A97E3C9</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1430,27 +1430,27 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ovos Campo Verde 20un</t>
+          <t>Ovo Mantiqueira 20 Unidades</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>10.9</v>
+        <v>12.99</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-gru1-2.cdninstagram.com/v/t39.30808-6/781977378_1500799415426508_4866536164507670119_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDM5MzQ4NDg1OTE4MjA5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Sm8TJqnT95wQ7kNvwEAuv_w&amp;_nc_oc=AdpZZydJ1-GE-INZNtInz7cq-SA5Wv0_1GvozmDDjQeLz4rUzU8kTBOScd6cu17GRE0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=xhJmWYiNAus3mZNW9vvJyw&amp;_nc_ss=7a22e&amp;oh=00_AQE6E29Ld-MfM-p4OWrqqGCNOmN8PZvQ5Qy2CX5my112VA&amp;oe=6A96604E</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwGTcb9I&amp;_nc_oc=AdotyJ0U7-8_sLo8qfL9hcAUr-o67JwXqVueUqr5IQZJnMdhUZHDNW_TX0L3aEj2ckc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQGVMH442dwBA7G9EyyclblhXVTqXIZHTyQy3oCh4706uw&amp;oe=6A97BA84</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -1460,87 +1460,87 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Ovo Mantiqueira 20 Unidades</t>
+          <t>Campari 998ml</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>12.99</v>
+        <v>56.99</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwHLDn1l&amp;_nc_oc=AdrjU5VMRBqsuXkwk4c0CVoFJJrfcHMHOvbiwEEFcun3p9p2hik2QEPKSkkENHmKztw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQEfQDvhG99ZAq90S9bBXXRlP1P2A7WTTAAQyJqxbjexoQ&amp;oe=6A966904</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Ovos Brancos Campo Verde 30 Und</t>
+          <t>Steak de Frango Seara 100g</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>14.99</v>
+        <v>1.99</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Bebidas / Sucos e Diversos</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Papel Higiênico Mili Folha Dupla 12 Unidades</t>
+          <t>Coxa e Sobrecoxa de Frango kg</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>18.99</v>
+        <v>5.89</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784232177_1720016766798808_2199971508535547197_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTgyMjMyNDE3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=p0-_YO7HB9IQ7kNvwFW6l4t&amp;_nc_oc=AdpDnxmlSKJ1P7l--L6nf6n2JjNCpctcRXLnroAl8-Zps1KhkYRcFViee4v0hgO123Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFwD06QnsgEkwhe1B7ZL7tzL3GUipLULAq2MonlY11XSw&amp;oe=6A97D7E4</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Coxa e Sobrecoxa de Frango Sadia kg</t>
+          <t>Frango A Passarinho Bello 800g</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwFPD8M5&amp;_nc_oc=AdpseN54VqnZluFjH3qZ3rqjr8o1Hw7zh3OQ3cCkAXd_RWyrjKvomWBm06_Oo4KrtaQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQETuNAiKLK4FGxp6nx1-cMLS1tROLflzjRGHMmrNTfC9A&amp;oe=6A97B825</t>
         </is>
       </c>
     </row>
@@ -1580,11 +1580,11 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Frango A Passarinho Bello 800g</t>
+          <t>Frango Inteiro Seara kg</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>8.99</v>
+        <v>9.69</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
@@ -1593,14 +1593,14 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwHdQvVN&amp;_nc_oc=Adr2jz83g1HMFZbddfvWSC0pL4rnuXe_n9d4o8qnNRSzg_ggtsdVyqHY1_rraZXke4fM-PacFcpd2ny--CV4tB30&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQGA5eHj920O_UhzUyPP2raQEwWZYO8b3KtcsEODu3jKRg&amp;oe=6A9666A5</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786433730_18374533639237813_3285427351558996853_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MjE2ODE2MDExNDQ2ODEyNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NsGACeUcnlQQ7kNvwGD1TbS&amp;_nc_oc=AdpDYNLOs7YQyj8Rb1M5FahFvHbFwwM78SVLcXBp7bSG7_ZPmU-4vOtD09XmR6a4XXc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQFltTqJY71E8J6NOqlaeE53oAxd28H4LKZpQH9OEwmtew&amp;oe=6A97DB55</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1610,20 +1610,20 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Frango Inteiro Seara kg</t>
+          <t>Coxas de Frango Sadia 1kg</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>9.69</v>
+        <v>10.99</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786433730_18374533639237813_3285427351558996853_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MjE2ODE2MDExNDQ2ODEyNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=NsGACeUcnlQQ7kNvwE8yRwV&amp;_nc_oc=Adp8lxjG1zYKs8eD2uNyLEyucRxpn7rXi66JaXCqG2qfVniSQmcJbxcRLK-58R73f4kIreynafsInRAYHzicea5r&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQEJYDaDHrMFHD5E9K6Z2pQH4XV62St5imH5nF7JG0vS7g&amp;oe=6A965195</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=XsYkt3_1l6QQ7kNvwHvPqBK&amp;_nc_oc=AdoxHccv3l1ezOe2SRiaKdoIKylxRFAMAa-bcY8i1nMbLQRho8hGGxaPwVCiK9K63Rk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=l2Ws1l6EHCFje39eqZ55ow&amp;_nc_ss=7a22e&amp;oh=00_AQFDMDGgiy16J0IXYT6xj-Xo6NU7bSN7xPfmly_JDARCug&amp;oe=6A965EFA</t>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lahhkTUGus0Q7kNvwH9S1HS&amp;_nc_oc=Adqzpe26NNEIgL11_-99PbnwKKsNOTm7mJQpQTT7Z3ezDvmT5yoHime4NpgbtneZf4PRFVoMnTfPUSGIQXrbL9uN&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=dBWbPpDbzRAuRx_PrvAKAA&amp;_nc_ss=7a22e&amp;oh=00_AQHGTds9cP7jlOi84o9CH_61OUSC_zTxDXtf1nHP1C5PnQ&amp;oe=6A97B07A</t>
         </is>
       </c>
     </row>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwHdQvVN&amp;_nc_oc=Adr2jz83g1HMFZbddfvWSC0pL4rnuXe_n9d4o8qnNRSzg_ggtsdVyqHY1_rraZXke4fM-PacFcpd2ny--CV4tB30&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQGA5eHj920O_UhzUyPP2raQEwWZYO8b3KtcsEODu3jKRg&amp;oe=6A9666A5</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwFPD8M5&amp;_nc_oc=AdpseN54VqnZluFjH3qZ3rqjr8o1Hw7zh3OQ3cCkAXd_RWyrjKvomWBm06_Oo4KrtaQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQETuNAiKLK4FGxp6nx1-cMLS1tROLflzjRGHMmrNTfC9A&amp;oe=6A97B825</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -1700,20 +1700,20 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Coxinhas da Asa de Frango Super Frango 1kg</t>
+          <t>Frango Inteiro Seara kg</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>12.99</v>
+        <v>10.99</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=XsYkt3_1l6QQ7kNvwHvPqBK&amp;_nc_oc=AdoxHccv3l1ezOe2SRiaKdoIKylxRFAMAa-bcY8i1nMbLQRho8hGGxaPwVCiK9K63Rk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=l2Ws1l6EHCFje39eqZ55ow&amp;_nc_ss=7a22e&amp;oh=00_AQFDMDGgiy16J0IXYT6xj-Xo6NU7bSN7xPfmly_JDARCug&amp;oe=6A965EFA</t>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lahhkTUGus0Q7kNvwH9S1HS&amp;_nc_oc=Adqzpe26NNEIgL11_-99PbnwKKsNOTm7mJQpQTT7Z3ezDvmT5yoHime4NpgbtneZf4PRFVoMnTfPUSGIQXrbL9uN&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=dBWbPpDbzRAuRx_PrvAKAA&amp;_nc_ss=7a22e&amp;oh=00_AQHGTds9cP7jlOi84o9CH_61OUSC_zTxDXtf1nHP1C5PnQ&amp;oe=6A97B07A</t>
         </is>
       </c>
     </row>
@@ -1773,14 +1773,14 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1790,11 +1790,11 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Linguiça de Frango Sadia 700g</t>
+          <t>Filé de Peito de Frango Sassami Sadia 1kg</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>14.99</v>
+        <v>15.99</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=27_NHNZ1YPEQ7kNvwFoKDXp&amp;_nc_oc=Adq93sm4yjujuKl2H9qKd7A-Ri6sPJ2O7h6MT7xu_2Gn_ICjD_O8jrpMyqpEq10pxog&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=zbuJQKO7MCB6qCV9cm71qw&amp;_nc_ss=7a22e&amp;oh=00_AQFoLPeW7mZwdNBlXkTxG1Z4Q8aI7FC9c9WBaNrB5U4a1g&amp;oe=6A966FA1</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=40xkhSQE8g4Q7kNvwHrZ6fS&amp;_nc_oc=AdrQwhyO2locrqA9fhJGOet0h1z6OSsYR_JGHtkSpAE_SO1Qxhq4nZ1AaPAQZOIjiCM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=piuLZ9j-qv6denTdiMpN-w&amp;_nc_ss=7a22e&amp;oh=00_AQHlBvIUNmHk7i3Qkz9ssRG8EZJIjOAq6Lm63Ods05W5Gw&amp;oe=6A97C121</t>
         </is>
       </c>
     </row>
@@ -1863,14 +1863,14 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -1880,41 +1880,41 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Filé de Peito de Frango Seara 1kg</t>
+          <t>Meio da Asa de Frango kg</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>19.79</v>
+        <v>24.99</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/787853786_18195711469382122_4084613579796731411_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MzY3MjU2ODk4MzkzOTE2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mrOwFRh3sK8Q7kNvwGuiPxU&amp;_nc_oc=AdocWchk5QRpVZ8dLBXgW047kqu1zOIqox1GJTIk1w9BH6Gir0_2USO05ktxY04PMUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQFkCEs3hpn9RALf_1PUmHbNNicLtXSXUXy77R9obJWZgw&amp;oe=6A97CD87</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Bovina</t>
+          <t>Carnes / Aves</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Paleta Suína kg</t>
+          <t>Meio da Asa Seara 1kg</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>8.98</v>
+        <v>28.99</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -1923,14 +1923,14 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=XsYkt3_1l6QQ7kNvwHvPqBK&amp;_nc_oc=AdoxHccv3l1ezOe2SRiaKdoIKylxRFAMAa-bcY8i1nMbLQRho8hGGxaPwVCiK9K63Rk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=l2Ws1l6EHCFje39eqZ55ow&amp;_nc_ss=7a22e&amp;oh=00_AQFDMDGgiy16J0IXYT6xj-Xo6NU7bSN7xPfmly_JDARCug&amp;oe=6A965EFA</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786467846_18581501911067900_1635849977930495039_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MjE4NzkxMTEzMDgyMDgwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=68dX_CMI8T8Q7kNvwHpguAF&amp;_nc_oc=AdpvJ8hg4jzx9Q7uK8qPvuWvKrWMP08Oeehoujr6Wpc2QxbpMYPcxWGkg2NQUSOk7C4&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQEXezKQKLTebF6L1-4Q53oshrrGdQxlFh_KVpPH4RViYA&amp;oe=6A964FDA</t>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lahhkTUGus0Q7kNvwH9S1HS&amp;_nc_oc=Adqzpe26NNEIgL11_-99PbnwKKsNOTm7mJQpQTT7Z3ezDvmT5yoHime4NpgbtneZf4PRFVoMnTfPUSGIQXrbL9uN&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=dBWbPpDbzRAuRx_PrvAKAA&amp;_nc_ss=7a22e&amp;oh=00_AQHGTds9cP7jlOi84o9CH_61OUSC_zTxDXtf1nHP1C5PnQ&amp;oe=6A97B07A</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Pernil e Paleta Suína Ochove kg</t>
+          <t>Pernil e Paleta Suína Frigorífico Ochove kg</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
@@ -1983,14 +1983,14 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwHdQvVN&amp;_nc_oc=Adr2jz83g1HMFZbddfvWSC0pL4rnuXe_n9d4o8qnNRSzg_ggtsdVyqHY1_rraZXke4fM-PacFcpd2ny--CV4tB30&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQGA5eHj920O_UhzUyPP2raQEwWZYO8b3KtcsEODu3jKRg&amp;oe=6A9666A5</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwFPD8M5&amp;_nc_oc=AdpseN54VqnZluFjH3qZ3rqjr8o1Hw7zh3OQ3cCkAXd_RWyrjKvomWBm06_Oo4KrtaQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQETuNAiKLK4FGxp6nx1-cMLS1tROLflzjRGHMmrNTfC9A&amp;oe=6A97B825</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Bisteca Suína kg</t>
+          <t>Bisteca Suína Excelência kg</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -2013,14 +2013,14 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/784389246_18581502034067900_514741470007781001_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MjE4Nzk0NDI0MDc2NjUyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=axgGxUji1CYQ7kNvwF5yFe_&amp;_nc_oc=AdoPdvXKkxhOnuhRHqGiq6Pt03mMi3YFrFv35FgdwDW_XLaCuthau9xVtjxvSvd3Et0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGnyh9C5KtZnA7Clr6PJqSdV_he0XIhN4EcSf3kil01jw&amp;oe=6A967986</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwFPD8M5&amp;_nc_oc=AdpseN54VqnZluFjH3qZ3rqjr8o1Hw7zh3OQ3cCkAXd_RWyrjKvomWBm06_Oo4KrtaQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQETuNAiKLK4FGxp6nx1-cMLS1tROLflzjRGHMmrNTfC9A&amp;oe=6A97B825</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2030,20 +2030,20 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Bisteca Suína Excelência kg</t>
+          <t>Costela Suína kg</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>12.99</v>
+        <v>15.99</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwHdQvVN&amp;_nc_oc=Adr2jz83g1HMFZbddfvWSC0pL4rnuXe_n9d4o8qnNRSzg_ggtsdVyqHY1_rraZXke4fM-PacFcpd2ny--CV4tB30&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQGA5eHj920O_UhzUyPP2raQEwWZYO8b3KtcsEODu3jKRg&amp;oe=6A9666A5</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784232177_1720016766798808_2199971508535547197_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTgyMjMyNDE3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=p0-_YO7HB9IQ7kNvwFW6l4t&amp;_nc_oc=AdpDnxmlSKJ1P7l--L6nf6n2JjNCpctcRXLnroAl8-Zps1KhkYRcFViee4v0hgO123Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFwD06QnsgEkwhe1B7ZL7tzL3GUipLULAq2MonlY11XSw&amp;oe=6A97D7E4</t>
         </is>
       </c>
     </row>
@@ -2060,20 +2060,20 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Carne Moída kg</t>
+          <t>Costela Fina Bovina kg</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786467846_18581501911067900_1635849977930495039_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MjE4NzkxMTEzMDgyMDgwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=68dX_CMI8T8Q7kNvwHpguAF&amp;_nc_oc=AdpvJ8hg4jzx9Q7uK8qPvuWvKrWMP08Oeehoujr6Wpc2QxbpMYPcxWGkg2NQUSOk7C4&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQEXezKQKLTebF6L1-4Q53oshrrGdQxlFh_KVpPH4RViYA&amp;oe=6A964FDA</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784232177_1720016766798808_2199971508535547197_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTgyMjMyNDE3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=p0-_YO7HB9IQ7kNvwFW6l4t&amp;_nc_oc=AdpDnxmlSKJ1P7l--L6nf6n2JjNCpctcRXLnroAl8-Zps1KhkYRcFViee4v0hgO123Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFwD06QnsgEkwhe1B7ZL7tzL3GUipLULAq2MonlY11XSw&amp;oe=6A97D7E4</t>
         </is>
       </c>
     </row>
@@ -2090,27 +2090,27 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Acém com Osso kg</t>
+          <t>Costela Grossa Bovina kg</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>20.99</v>
+        <v>18.99</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786467846_18581501911067900_1635849977930495039_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MjE4NzkxMTEzMDgyMDgwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=68dX_CMI8T8Q7kNvwHpguAF&amp;_nc_oc=AdpvJ8hg4jzx9Q7uK8qPvuWvKrWMP08Oeehoujr6Wpc2QxbpMYPcxWGkg2NQUSOk7C4&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQEXezKQKLTebF6L1-4Q53oshrrGdQxlFh_KVpPH4RViYA&amp;oe=6A964FDA</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784232177_1720016766798808_2199971508535547197_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTgyMjMyNDE3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=p0-_YO7HB9IQ7kNvwFW6l4t&amp;_nc_oc=AdpDnxmlSKJ1P7l--L6nf6n2JjNCpctcRXLnroAl8-Zps1KhkYRcFViee4v0hgO123Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFwD06QnsgEkwhe1B7ZL7tzL3GUipLULAq2MonlY11XSw&amp;oe=6A97D7E4</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -2120,27 +2120,27 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Costela Bovina kg</t>
+          <t>Acém e Músculo com Osso Sulbeef kg</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>20.99</v>
+        <v>21.99</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=SYZyJZ31VbUQ7kNvwEOWs2J&amp;_nc_oc=AdqpKjKxsZ7ot3N4oU482_9TygvblCc4tjiTCLWYc7ObnRUvJsRErOJIoA5fvHYgu0Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQHHkJomv6yUMRLSyd_iHYBiT3rTwwZIlyeWwGP1KkFidA&amp;oe=6A97C24B</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2150,20 +2150,20 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Acém e Músculo com Osso Sulbeef kg</t>
+          <t>Costela Suína kg</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>21.99</v>
+        <v>22.99</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wecasNb-bicQ7kNvwHn2Ans&amp;_nc_oc=AdoaD9yhEQHxNxTT6dVW2831gh9YvtHOkjIyW0HrtAmSkQFq6pF2ab2IVMLYNpZqUqhBBxd2zWPq04gPZ1t49W4Z&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQF4a0Y9_NKwZXJwWZHMF9uqX0FiNsV42rdgjR5KMV-Bpw&amp;oe=6A9670CB</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/787853786_18195711469382122_4084613579796731411_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MzY3MjU2ODk4MzkzOTE2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mrOwFRh3sK8Q7kNvwGuiPxU&amp;_nc_oc=AdocWchk5QRpVZ8dLBXgW047kqu1zOIqox1GJTIk1w9BH6Gir0_2USO05ktxY04PMUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQFkCEs3hpn9RALf_1PUmHbNNicLtXSXUXy77R9obJWZgw&amp;oe=6A97CD87</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=27_NHNZ1YPEQ7kNvwFoKDXp&amp;_nc_oc=Adq93sm4yjujuKl2H9qKd7A-Ri6sPJ2O7h6MT7xu_2Gn_ICjD_O8jrpMyqpEq10pxog&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=zbuJQKO7MCB6qCV9cm71qw&amp;_nc_ss=7a22e&amp;oh=00_AQFoLPeW7mZwdNBlXkTxG1Z4Q8aI7FC9c9WBaNrB5U4a1g&amp;oe=6A966FA1</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=40xkhSQE8g4Q7kNvwHrZ6fS&amp;_nc_oc=AdrQwhyO2locrqA9fhJGOet0h1z6OSsYR_JGHtkSpAE_SO1Qxhq4nZ1AaPAQZOIjiCM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=piuLZ9j-qv6denTdiMpN-w&amp;_nc_ss=7a22e&amp;oh=00_AQHlBvIUNmHk7i3Qkz9ssRG8EZJIjOAq6Lm63Ods05W5Gw&amp;oe=6A97C121</t>
         </is>
       </c>
     </row>
@@ -2223,14 +2223,14 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=XsYkt3_1l6QQ7kNvwHvPqBK&amp;_nc_oc=AdoxHccv3l1ezOe2SRiaKdoIKylxRFAMAa-bcY8i1nMbLQRho8hGGxaPwVCiK9K63Rk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=l2Ws1l6EHCFje39eqZ55ow&amp;_nc_ss=7a22e&amp;oh=00_AQFDMDGgiy16J0IXYT6xj-Xo6NU7bSN7xPfmly_JDARCug&amp;oe=6A965EFA</t>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lahhkTUGus0Q7kNvwH9S1HS&amp;_nc_oc=Adqzpe26NNEIgL11_-99PbnwKKsNOTm7mJQpQTT7Z3ezDvmT5yoHime4NpgbtneZf4PRFVoMnTfPUSGIQXrbL9uN&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=dBWbPpDbzRAuRx_PrvAKAA&amp;_nc_ss=7a22e&amp;oh=00_AQHGTds9cP7jlOi84o9CH_61OUSC_zTxDXtf1nHP1C5PnQ&amp;oe=6A97B07A</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -2240,20 +2240,20 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Paleta com Osso kg</t>
+          <t>Paleta Bovina com Osso kg</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>23.99</v>
+        <v>24.48</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786467846_18581501911067900_1635849977930495039_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MjE4NzkxMTEzMDgyMDgwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=68dX_CMI8T8Q7kNvwHpguAF&amp;_nc_oc=AdpvJ8hg4jzx9Q7uK8qPvuWvKrWMP08Oeehoujr6Wpc2QxbpMYPcxWGkg2NQUSOk7C4&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQEXezKQKLTebF6L1-4Q53oshrrGdQxlFh_KVpPH4RViYA&amp;oe=6A964FDA</t>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lahhkTUGus0Q7kNvwH9S1HS&amp;_nc_oc=Adqzpe26NNEIgL11_-99PbnwKKsNOTm7mJQpQTT7Z3ezDvmT5yoHime4NpgbtneZf4PRFVoMnTfPUSGIQXrbL9uN&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=dBWbPpDbzRAuRx_PrvAKAA&amp;_nc_ss=7a22e&amp;oh=00_AQHGTds9cP7jlOi84o9CH_61OUSC_zTxDXtf1nHP1C5PnQ&amp;oe=6A97B07A</t>
         </is>
       </c>
     </row>
@@ -2270,20 +2270,20 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Paleta Bovina com Osso kg</t>
+          <t>Costela Bovina kg</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>24.48</v>
+        <v>24.99</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=XsYkt3_1l6QQ7kNvwHvPqBK&amp;_nc_oc=AdoxHccv3l1ezOe2SRiaKdoIKylxRFAMAa-bcY8i1nMbLQRho8hGGxaPwVCiK9K63Rk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=l2Ws1l6EHCFje39eqZ55ow&amp;_nc_ss=7a22e&amp;oh=00_AQFDMDGgiy16J0IXYT6xj-Xo6NU7bSN7xPfmly_JDARCug&amp;oe=6A965EFA</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
@@ -2313,14 +2313,14 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=27_NHNZ1YPEQ7kNvwFoKDXp&amp;_nc_oc=Adq93sm4yjujuKl2H9qKd7A-Ri6sPJ2O7h6MT7xu_2Gn_ICjD_O8jrpMyqpEq10pxog&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=zbuJQKO7MCB6qCV9cm71qw&amp;_nc_ss=7a22e&amp;oh=00_AQFoLPeW7mZwdNBlXkTxG1Z4Q8aI7FC9c9WBaNrB5U4a1g&amp;oe=6A966FA1</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=40xkhSQE8g4Q7kNvwHrZ6fS&amp;_nc_oc=AdrQwhyO2locrqA9fhJGOet0h1z6OSsYR_JGHtkSpAE_SO1Qxhq4nZ1AaPAQZOIjiCM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=piuLZ9j-qv6denTdiMpN-w&amp;_nc_ss=7a22e&amp;oh=00_AQHlBvIUNmHk7i3Qkz9ssRG8EZJIjOAq6Lm63Ods05W5Gw&amp;oe=6A97C121</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2330,27 +2330,27 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Capa de Contra Filé Sulbeef kg</t>
+          <t>Corte Grill kg</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>32.99</v>
+        <v>27.99</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wecasNb-bicQ7kNvwHn2Ans&amp;_nc_oc=AdoaD9yhEQHxNxTT6dVW2831gh9YvtHOkjIyW0HrtAmSkQFq6pF2ab2IVMLYNpZqUqhBBxd2zWPq04gPZ1t49W4Z&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQF4a0Y9_NKwZXJwWZHMF9uqX0FiNsV42rdgjR5KMV-Bpw&amp;oe=6A9670CB</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784321179_1720016750132143_1243001508239248716_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzM0Mjg4MDE3NDY4MTI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uLCBohPgPQYQ7kNvwENG2o2&amp;_nc_oc=AdpIqeRD6CvgVgXKFFWA9WTGUuT7vNppdBJWZemIje2bYmfmlfu3V76RDLQg2A630bg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFOJaDCH3v0kUninhna4d-YzKlGOwpdtLMzyArKVwtmZA&amp;oe=6A97B219</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -2360,27 +2360,27 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Bisteca Mineira kg</t>
+          <t>Corte Americano kg</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>34.98</v>
+        <v>27.99</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=XsYkt3_1l6QQ7kNvwHvPqBK&amp;_nc_oc=AdoxHccv3l1ezOe2SRiaKdoIKylxRFAMAa-bcY8i1nMbLQRho8hGGxaPwVCiK9K63Rk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=l2Ws1l6EHCFje39eqZ55ow&amp;_nc_ss=7a22e&amp;oh=00_AQFDMDGgiy16J0IXYT6xj-Xo6NU7bSN7xPfmly_JDARCug&amp;oe=6A965EFA</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784321179_1720016750132143_1243001508239248716_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzM0Mjg4MDE3NDY4MTI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uLCBohPgPQYQ7kNvwENG2o2&amp;_nc_oc=AdpIqeRD6CvgVgXKFFWA9WTGUuT7vNppdBJWZemIje2bYmfmlfu3V76RDLQg2A630bg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFOJaDCH3v0kUninhna4d-YzKlGOwpdtLMzyArKVwtmZA&amp;oe=6A97B219</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2390,27 +2390,27 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Coxão Duro e Cupim Sulbeef kg</t>
+          <t>Costela Bovina kg</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>36.99</v>
+        <v>29.99</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wecasNb-bicQ7kNvwHn2Ans&amp;_nc_oc=AdoaD9yhEQHxNxTT6dVW2831gh9YvtHOkjIyW0HrtAmSkQFq6pF2ab2IVMLYNpZqUqhBBxd2zWPq04gPZ1t49W4Z&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQF4a0Y9_NKwZXJwWZHMF9uqX0FiNsV42rdgjR5KMV-Bpw&amp;oe=6A9670CB</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/787853786_18195711469382122_4084613579796731411_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MzY3MjU2ODk4MzkzOTE2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mrOwFRh3sK8Q7kNvwGuiPxU&amp;_nc_oc=AdocWchk5QRpVZ8dLBXgW047kqu1zOIqox1GJTIk1w9BH6Gir0_2USO05ktxY04PMUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQFkCEs3hpn9RALf_1PUmHbNNicLtXSXUXy77R9obJWZgw&amp;oe=6A97CD87</t>
         </is>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -2420,27 +2420,27 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Coxão Duro Bovino kg</t>
+          <t>Capa de Contra Filé Sulbeef kg</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>42.98</v>
+        <v>32.99</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=XsYkt3_1l6QQ7kNvwHvPqBK&amp;_nc_oc=AdoxHccv3l1ezOe2SRiaKdoIKylxRFAMAa-bcY8i1nMbLQRho8hGGxaPwVCiK9K63Rk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=l2Ws1l6EHCFje39eqZ55ow&amp;_nc_ss=7a22e&amp;oh=00_AQFDMDGgiy16J0IXYT6xj-Xo6NU7bSN7xPfmly_JDARCug&amp;oe=6A965EFA</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=SYZyJZ31VbUQ7kNvwEOWs2J&amp;_nc_oc=AdqpKjKxsZ7ot3N4oU482_9TygvblCc4tjiTCLWYc7ObnRUvJsRErOJIoA5fvHYgu0Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQHHkJomv6yUMRLSyd_iHYBiT3rTwwZIlyeWwGP1KkFidA&amp;oe=6A97C24B</t>
         </is>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2450,27 +2450,27 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Fraldinha Bovina kg</t>
+          <t>Bisteca Mineira kg</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>42.99</v>
+        <v>34.98</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lahhkTUGus0Q7kNvwH9S1HS&amp;_nc_oc=Adqzpe26NNEIgL11_-99PbnwKKsNOTm7mJQpQTT7Z3ezDvmT5yoHime4NpgbtneZf4PRFVoMnTfPUSGIQXrbL9uN&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=dBWbPpDbzRAuRx_PrvAKAA&amp;_nc_ss=7a22e&amp;oh=00_AQHGTds9cP7jlOi84o9CH_61OUSC_zTxDXtf1nHP1C5PnQ&amp;oe=6A97B07A</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -2480,20 +2480,20 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Maminha Bovina kg</t>
+          <t>Coxão Duro kg</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>44.99</v>
+        <v>34.99</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784321179_1720016750132143_1243001508239248716_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzM0Mjg4MDE3NDY4MTI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uLCBohPgPQYQ7kNvwENG2o2&amp;_nc_oc=AdpIqeRD6CvgVgXKFFWA9WTGUuT7vNppdBJWZemIje2bYmfmlfu3V76RDLQg2A630bg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFOJaDCH3v0kUninhna4d-YzKlGOwpdtLMzyArKVwtmZA&amp;oe=6A97B219</t>
         </is>
       </c>
     </row>
@@ -2510,27 +2510,27 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Coxão Mole Bovino kg</t>
+          <t>Bisteca Mineira kg</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>46.98</v>
+        <v>34.99</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=XsYkt3_1l6QQ7kNvwHvPqBK&amp;_nc_oc=AdoxHccv3l1ezOe2SRiaKdoIKylxRFAMAa-bcY8i1nMbLQRho8hGGxaPwVCiK9K63Rk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=l2Ws1l6EHCFje39eqZ55ow&amp;_nc_ss=7a22e&amp;oh=00_AQFDMDGgiy16J0IXYT6xj-Xo6NU7bSN7xPfmly_JDARCug&amp;oe=6A965EFA</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/787853786_18195711469382122_4084613579796731411_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MzY3MjU2ODk4MzkzOTE2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mrOwFRh3sK8Q7kNvwGuiPxU&amp;_nc_oc=AdocWchk5QRpVZ8dLBXgW047kqu1zOIqox1GJTIk1w9BH6Gir0_2USO05ktxY04PMUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQFkCEs3hpn9RALf_1PUmHbNNicLtXSXUXy77R9obJWZgw&amp;oe=6A97CD87</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -2540,20 +2540,20 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Alcatra Bovina kg</t>
+          <t>Corte Grill kg</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>47.99</v>
+        <v>36.99</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/787853786_18195711469382122_4084613579796731411_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MzY3MjU2ODk4MzkzOTE2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mrOwFRh3sK8Q7kNvwGuiPxU&amp;_nc_oc=AdocWchk5QRpVZ8dLBXgW047kqu1zOIqox1GJTIk1w9BH6Gir0_2USO05ktxY04PMUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQFkCEs3hpn9RALf_1PUmHbNNicLtXSXUXy77R9obJWZgw&amp;oe=6A97CD87</t>
         </is>
       </c>
     </row>
@@ -2570,11 +2570,11 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Picanha e Filé Mignon Sulbeef kg</t>
+          <t>Coxão Duro e Cupim Sulbeef kg</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>36.99</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -2583,127 +2583,127 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wecasNb-bicQ7kNvwHn2Ans&amp;_nc_oc=AdoaD9yhEQHxNxTT6dVW2831gh9YvtHOkjIyW0HrtAmSkQFq6pF2ab2IVMLYNpZqUqhBBxd2zWPq04gPZ1t49W4Z&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQF4a0Y9_NKwZXJwWZHMF9uqX0FiNsV42rdgjR5KMV-Bpw&amp;oe=6A9670CB</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=SYZyJZ31VbUQ7kNvwEOWs2J&amp;_nc_oc=AdqpKjKxsZ7ot3N4oU482_9TygvblCc4tjiTCLWYc7ObnRUvJsRErOJIoA5fvHYgu0Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQHHkJomv6yUMRLSyd_iHYBiT3rTwwZIlyeWwGP1KkFidA&amp;oe=6A97C24B</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Sardinha Iglu 400g</t>
+          <t>Coxão Mole kg</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>16.9</v>
+        <v>38.99</v>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784321179_1720016750132143_1243001508239248716_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzM0Mjg4MDE3NDY4MTI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uLCBohPgPQYQ7kNvwENG2o2&amp;_nc_oc=AdpIqeRD6CvgVgXKFFWA9WTGUuT7vNppdBJWZemIje2bYmfmlfu3V76RDLQg2A630bg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFOJaDCH3v0kUninhna4d-YzKlGOwpdtLMzyArKVwtmZA&amp;oe=6A97B219</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Sardinha Espalmada Iglu 400g</t>
+          <t>Coxão Duro Bovino kg</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>16.9</v>
+        <v>42.98</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lahhkTUGus0Q7kNvwH9S1HS&amp;_nc_oc=Adqzpe26NNEIgL11_-99PbnwKKsNOTm7mJQpQTT7Z3ezDvmT5yoHime4NpgbtneZf4PRFVoMnTfPUSGIQXrbL9uN&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=dBWbPpDbzRAuRx_PrvAKAA&amp;_nc_ss=7a22e&amp;oh=00_AQHGTds9cP7jlOi84o9CH_61OUSC_zTxDXtf1nHP1C5PnQ&amp;oe=6A97B07A</t>
         </is>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Peixe Tambatinga Delicious Fish kg</t>
+          <t>Fraldinha Bovina Friboi kg</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>21.99</v>
+        <v>42.99</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wecasNb-bicQ7kNvwHn2Ans&amp;_nc_oc=AdoaD9yhEQHxNxTT6dVW2831gh9YvtHOkjIyW0HrtAmSkQFq6pF2ab2IVMLYNpZqUqhBBxd2zWPq04gPZ1t49W4Z&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQF4a0Y9_NKwZXJwWZHMF9uqX0FiNsV42rdgjR5KMV-Bpw&amp;oe=6A9670CB</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Peixes</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Peixe Tambatinga kg</t>
+          <t>Alcatra com Maminha kg</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>23.49</v>
+        <v>43.99</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fein1-2.fna.fbcdn.net/v/t51.82787-15/788729215_18093625259531849_1531670164686177481_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3Mjk0NzI0NTE5NTkyMjY1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OIrB5YXP5WUQ7kNvwHCRGZZ&amp;_nc_oc=AdokfAr95rC3Fx22KbLeCp4E5kBUQlI5eWOR3ETdtdDqvoMuggd0JP0K3cX4LhU3mak&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fein1-2.fna&amp;_nc_gid=m8vL59IcN81voNHEYINoVA&amp;_nc_ss=7a22e&amp;oh=00_AQHFBkOvXHLxxOvr_GOB-DLHQZ6XnsuhSb6LN4SbBk_R-g&amp;oe=6A967466</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784321179_1720016750132143_1243001508239248716_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzM0Mjg4MDE3NDY4MTI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uLCBohPgPQYQ7kNvwENG2o2&amp;_nc_oc=AdpIqeRD6CvgVgXKFFWA9WTGUuT7vNppdBJWZemIje2bYmfmlfu3V76RDLQg2A630bg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFOJaDCH3v0kUninhna4d-YzKlGOwpdtLMzyArKVwtmZA&amp;oe=6A97B219</t>
         </is>
       </c>
     </row>
@@ -2715,16 +2715,16 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Pernil Suíno kg</t>
+          <t>Coxão Mole Bovino kg</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>9.98</v>
+        <v>46.98</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
@@ -2733,88 +2733,88 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=XsYkt3_1l6QQ7kNvwHvPqBK&amp;_nc_oc=AdoxHccv3l1ezOe2SRiaKdoIKylxRFAMAa-bcY8i1nMbLQRho8hGGxaPwVCiK9K63Rk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=l2Ws1l6EHCFje39eqZ55ow&amp;_nc_ss=7a22e&amp;oh=00_AQFDMDGgiy16J0IXYT6xj-Xo6NU7bSN7xPfmly_JDARCug&amp;oe=6A965EFA</t>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lahhkTUGus0Q7kNvwH9S1HS&amp;_nc_oc=Adqzpe26NNEIgL11_-99PbnwKKsNOTm7mJQpQTT7Z3ezDvmT5yoHime4NpgbtneZf4PRFVoMnTfPUSGIQXrbL9uN&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=dBWbPpDbzRAuRx_PrvAKAA&amp;_nc_ss=7a22e&amp;oh=00_AQHGTds9cP7jlOi84o9CH_61OUSC_zTxDXtf1nHP1C5PnQ&amp;oe=6A97B07A</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Bovina</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Mortadela Perdigão Bolognella kg</t>
+          <t>Picanha e Filé Mignon Sulbeef kg</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>9.99</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=SYZyJZ31VbUQ7kNvwEOWs2J&amp;_nc_oc=AdqpKjKxsZ7ot3N4oU482_9TygvblCc4tjiTCLWYc7ObnRUvJsRErOJIoA5fvHYgu0Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQHHkJomv6yUMRLSyd_iHYBiT3rTwwZIlyeWwGP1KkFidA&amp;oe=6A97C24B</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Pernil Suíno kg</t>
+          <t>Sardinha Iglu 400g</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>9.99</v>
+        <v>16.9</v>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Nutribribas kg</t>
+          <t>Peixe Tambatinga Delicious Fish kg</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>11.49</v>
+        <v>21.99</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -2823,74 +2823,74 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/784389246_18581502034067900_514741470007781001_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MjE4Nzk0NDI0MDc2NjUyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=axgGxUji1CYQ7kNvwF5yFe_&amp;_nc_oc=AdoPdvXKkxhOnuhRHqGiq6Pt03mMi3YFrFv35FgdwDW_XLaCuthau9xVtjxvSvd3Et0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGnyh9C5KtZnA7Clr6PJqSdV_he0XIhN4EcSf3kil01jw&amp;oe=6A967986</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=SYZyJZ31VbUQ7kNvwEOWs2J&amp;_nc_oc=AdqpKjKxsZ7ot3N4oU482_9TygvblCc4tjiTCLWYc7ObnRUvJsRErOJIoA5fvHYgu0Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQHHkJomv6yUMRLSyd_iHYBiT3rTwwZIlyeWwGP1KkFidA&amp;oe=6A97C24B</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Suína Perdigão kg</t>
+          <t>Camarão Fisgo 300g</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>15.99</v>
+        <v>45.9</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wecasNb-bicQ7kNvwHn2Ans&amp;_nc_oc=AdoaD9yhEQHxNxTT6dVW2831gh9YvtHOkjIyW0HrtAmSkQFq6pF2ab2IVMLYNpZqUqhBBxd2zWPq04gPZ1t49W4Z&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQF4a0Y9_NKwZXJwWZHMF9uqX0FiNsV42rdgjR5KMV-Bpw&amp;oe=6A9670CB</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Carnes / Suína e Embutidos</t>
+          <t>Carnes / Peixes</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Fina Apimentada kg</t>
+          <t>Camarão Fisgo 300g</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>16.99</v>
+        <v>45.9</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fein1-2.fna.fbcdn.net/v/t51.82787-15/788729215_18093625259531849_1531670164686177481_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3Mjk0NzI0NTE5NTkyMjY1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OIrB5YXP5WUQ7kNvwHCRGZZ&amp;_nc_oc=AdokfAr95rC3Fx22KbLeCp4E5kBUQlI5eWOR3ETdtdDqvoMuggd0JP0K3cX4LhU3mak&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fein1-2.fna&amp;_nc_gid=m8vL59IcN81voNHEYINoVA&amp;_nc_ss=7a22e&amp;oh=00_AQHFBkOvXHLxxOvr_GOB-DLHQZ6XnsuhSb6LN4SbBk_R-g&amp;oe=6A967466</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -2900,27 +2900,27 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Linguiça Calabresa Excelência kg</t>
+          <t>Pernil Suíno kg</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>19.99</v>
+        <v>8.99</v>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fein1-2.fna.fbcdn.net/v/t51.82787-15/788729215_18093625259531849_1531670164686177481_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3Mjk0NzI0NTE5NTkyMjY1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OIrB5YXP5WUQ7kNvwHCRGZZ&amp;_nc_oc=AdokfAr95rC3Fx22KbLeCp4E5kBUQlI5eWOR3ETdtdDqvoMuggd0JP0K3cX4LhU3mak&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fein1-2.fna&amp;_nc_gid=m8vL59IcN81voNHEYINoVA&amp;_nc_ss=7a22e&amp;oh=00_AQHFBkOvXHLxxOvr_GOB-DLHQZ6XnsuhSb6LN4SbBk_R-g&amp;oe=6A967466</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784232177_1720016766798808_2199971508535547197_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTgyMjMyNDE3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=p0-_YO7HB9IQ7kNvwFW6l4t&amp;_nc_oc=AdpDnxmlSKJ1P7l--L6nf6n2JjNCpctcRXLnroAl8-Zps1KhkYRcFViee4v0hgO123Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFwD06QnsgEkwhe1B7ZL7tzL3GUipLULAq2MonlY11XSw&amp;oe=6A97D7E4</t>
         </is>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -2930,20 +2930,20 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Linguiça Suína kg</t>
+          <t>Pernil Suíno kg</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>21.99</v>
+        <v>9.98</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lahhkTUGus0Q7kNvwH9S1HS&amp;_nc_oc=Adqzpe26NNEIgL11_-99PbnwKKsNOTm7mJQpQTT7Z3ezDvmT5yoHime4NpgbtneZf4PRFVoMnTfPUSGIQXrbL9uN&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=dBWbPpDbzRAuRx_PrvAKAA&amp;_nc_ss=7a22e&amp;oh=00_AQHGTds9cP7jlOi84o9CH_61OUSC_zTxDXtf1nHP1C5PnQ&amp;oe=6A97B07A</t>
         </is>
       </c>
     </row>
@@ -2960,27 +2960,27 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Presunto Cozido kg</t>
+          <t>Linguiça Perdigão kg</t>
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>24.99</v>
+        <v>14.99</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/782208226_18581670763067900_4505279802407067664_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjU4MDUzNjU2NDQyMTcwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r3oFMSDFP4cQ7kNvwG9Ys90&amp;_nc_oc=AdoC42xnlWixiFBnGTixoIoSuINXbUH7HVIiNflpXrqsxMMsZ1amfBnwQP8JJ6V6Hvz6WXBSqMA6dxY82d9H_hvt&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQHf_fl8KlU8yVIrGBu0ZZMZ0BwlmD5m-SCHFN7zxQiZVw&amp;oe=6A966CA3</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784232177_1720016766798808_2199971508535547197_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzM0Mjg3OTgyMjMyNDE3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=p0-_YO7HB9IQ7kNvwFW6l4t&amp;_nc_oc=AdpDnxmlSKJ1P7l--L6nf6n2JjNCpctcRXLnroAl8-Zps1KhkYRcFViee4v0hgO123Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFwD06QnsgEkwhe1B7ZL7tzL3GUipLULAq2MonlY11XSw&amp;oe=6A97D7E4</t>
         </is>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2990,11 +2990,11 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Bacon Excelência kg</t>
+          <t>Linguiça Toscana Excelência kg</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>25.99</v>
+        <v>15.99</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -3003,88 +3003,88 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fein1-2.fna.fbcdn.net/v/t51.82787-15/788729215_18093625259531849_1531670164686177481_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3Mjk0NzI0NTE5NTkyMjY1MA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=OIrB5YXP5WUQ7kNvwHCRGZZ&amp;_nc_oc=AdokfAr95rC3Fx22KbLeCp4E5kBUQlI5eWOR3ETdtdDqvoMuggd0JP0K3cX4LhU3mak&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fein1-2.fna&amp;_nc_gid=m8vL59IcN81voNHEYINoVA&amp;_nc_ss=7a22e&amp;oh=00_AQHFBkOvXHLxxOvr_GOB-DLHQZ6XnsuhSb6LN4SbBk_R-g&amp;oe=6A967466</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Açaí Ricaeli 1.02kg</t>
+          <t>Linguiça Suína Perdigão kg</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>25.99</v>
+        <v>15.99</v>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=SYZyJZ31VbUQ7kNvwEOWs2J&amp;_nc_oc=AdqpKjKxsZ7ot3N4oU482_9TygvblCc4tjiTCLWYc7ObnRUvJsRErOJIoA5fvHYgu0Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQHHkJomv6yUMRLSyd_iHYBiT3rTwwZIlyeWwGP1KkFidA&amp;oe=6A97C24B</t>
         </is>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Açaí Ricaeli 1.02kg</t>
+          <t>Presunto Excelência kg</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>25.99</v>
+        <v>22.99</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Congelados e Sobremesas</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Batata Palito Sadia 2kg</t>
+          <t>Presunto Cozido kg</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>27.99</v>
+        <v>24.99</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
@@ -3093,134 +3093,134 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwHdQvVN&amp;_nc_oc=Adr2jz83g1HMFZbddfvWSC0pL4rnuXe_n9d4o8qnNRSzg_ggtsdVyqHY1_rraZXke4fM-PacFcpd2ny--CV4tB30&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQGA5eHj920O_UhzUyPP2raQEwWZYO8b3KtcsEODu3jKRg&amp;oe=6A9666A5</t>
+          <t>https://instagram.fbfh3-3.fna.fbcdn.net/v/t51.82787-15/782208226_18581670763067900_4505279802407067664_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjU4MDUzNjU2NDQyMTcwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r3oFMSDFP4cQ7kNvwHDOJBb&amp;_nc_oc=AdrdBYrNxeyHXUDVYaHRy8WXM3WKcs1TCmTZXgWEhxAEu8uaTpBWCf7-IBK_iVJ_Xm0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-3.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQHpcknrSOLxm-OAhLA0oIM0CMm2BGDuxSP_QmKPeSX_WA&amp;oe=6A97BE23</t>
         </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Carnes / Suína e Embutidos</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Sabonete Albany 85g</t>
+          <t>Presunto Excelência kg</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>1.79</v>
+        <v>24.99</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Creme Dental Máxima Proteção Anticáries Colgate 120g</t>
+          <t>Pizza Sabores Super Compras</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>5.99</v>
+        <v>14.99</v>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/781804833_18192777268391764_1137004139144970890_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MzI5MzA5NzQ3NjE0OTUwNg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=DyFj_Iql6NYQ7kNvwHYLlSk&amp;_nc_oc=AdqV8bRdchMvNZp4BHa2_t2m22IgiOztm7zoDWcL2p_m1JYWnYaA9VgrtyfPstx4UQY&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=ftrHb-h5dIvuYaiBVknqqg&amp;_nc_ss=7a22e&amp;oh=00_AQEuYNN-sn9kbgUrflzEwlkkKOGj3YgeRa4NruiWHpkEeg&amp;oe=6A97CD39</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Creme Dental Colgate Total 12 90g</t>
+          <t>Açaí com Guaraná Ricaeli 1.02kg</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>9.99</v>
+        <v>25.99</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Cuidados Pessoais</t>
+          <t>Congelados e Sobremesas</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Desodorante Aerossol Rexona 150ml</t>
+          <t>Batata Palito Sadia 2kg</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>14.99</v>
+        <v>27.99</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwFPD8M5&amp;_nc_oc=AdpseN54VqnZluFjH3qZ3rqjr8o1Hw7zh3OQ3cCkAXd_RWyrjKvomWBm06_Oo4KrtaQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQETuNAiKLK4FGxp6nx1-cMLS1tROLflzjRGHMmrNTfC9A&amp;oe=6A97B825</t>
         </is>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -3230,11 +3230,11 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Shampoo Dove 190ml</t>
+          <t>Creme Dental Colgate Máxima Proteção Anticáries 120g</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>15.99</v>
+        <v>5.99</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3243,14 +3243,14 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -3260,11 +3260,11 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Absorvente Noturno com Abas Intimus 16un</t>
+          <t>Desodorante Aerossol Rexona Clinical 150ml</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>15.99</v>
+        <v>14.99</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
@@ -3290,11 +3290,11 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Desodorante Antitranspirante Aerosol Dove 150ml</t>
+          <t>Shampoo Dove 190ml</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>17.99</v>
+        <v>15.99</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -3303,14 +3303,14 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -3320,11 +3320,11 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Condicionador Dove 190ml</t>
+          <t>Absorvente Noturno Intimus Suave com Abas 16un</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>22.99</v>
+        <v>15.99</v>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
@@ -3333,28 +3333,28 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Guardanapo de Papel Mili 30cm X 29.5cm</t>
+          <t>Desodorante Antitranspirante Aerosol Dove 150ml</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>2.99</v>
+        <v>17.99</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -3363,37 +3363,37 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Higiene / Papelaria</t>
+          <t>Higiene / Cuidados Pessoais</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Papel Higiênico Duetto Folha Dupla 30m 12 Rolos</t>
+          <t>Condicionador Dove 190ml</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>18.99</v>
+        <v>22.99</v>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
@@ -3410,11 +3410,11 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Papel Higiênico Folha Dupla Duetto 30m 12un</t>
+          <t>Guardanapo de Papel Mili 30x29.5cm</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>19.9</v>
+        <v>2.99</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -3423,37 +3423,37 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Alho Nacional 100g</t>
+          <t>Papel Higiênico Duetto 12 Rolos</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>2.39</v>
+        <v>15.99</v>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwHLDn1l&amp;_nc_oc=AdrjU5VMRBqsuXkwk4c0CVoFJJrfcHMHOvbiwEEFcun3p9p2hik2QEPKSkkENHmKztw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQEfQDvhG99ZAq90S9bBXXRlP1P2A7WTTAAQyJqxbjexoQ&amp;oe=6A966904</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169170_1720016740132144_6974904276998945912_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MzM0Mjg3OTk5ODQ4MTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=q-Z25NrUeboQ7kNvwGqXKen&amp;_nc_oc=AdpneHkXhiwe-uz90HGKUxE4rzZZW3mKri8P6-IjSHDJOLKSOChvN6N2I-fSa4gotoI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQExAVubRUWKBWMwfyWEjw5jU-SQLWowdPkoPr4MjZ0Ppw&amp;oe=6A97BAC9</t>
         </is>
       </c>
     </row>
@@ -3465,55 +3465,55 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Laranja un</t>
+          <t>Papel Higiênico Duetto Folha Dupla 12 Rolos 30m</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>2.89</v>
+        <v>16.99</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-gru1-2.cdninstagram.com/v/t39.30808-6/781977378_1500799415426508_4866536164507670119_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDM5MzQ4NDg1OTE4MjA5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Sm8TJqnT95wQ7kNvwEAuv_w&amp;_nc_oc=AdpZZydJ1-GE-INZNtInz7cq-SA5Wv0_1GvozmDDjQeLz4rUzU8kTBOScd6cu17GRE0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=xhJmWYiNAus3mZNW9vvJyw&amp;_nc_ss=7a22e&amp;oh=00_AQE6E29Ld-MfM-p4OWrqqGCNOmN8PZvQ5Qy2CX5my112VA&amp;oe=6A96604E</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Higiene / Papelaria</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Laranja kg</t>
+          <t>Papel Higiênico Duetto Folha Dupla 30m 12un</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>2.99</v>
+        <v>19.9</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
@@ -3530,11 +3530,11 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Laranja Nacional kg</t>
+          <t>Alho Nacional 100g</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -3543,14 +3543,14 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwEMPYyR&amp;_nc_oc=Adr_b1bUKeRFPM7ZmqdRxfot36hQCNU24IL5_Efa9ytO3ogM1bBZT4MQjmZ9FH6Ptko&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQE80woS5j4qXeeidrqbdKnZmc1O3XfaeZ4vl-pHtiNMhQ&amp;oe=6A965889</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwGTcb9I&amp;_nc_oc=AdotyJ0U7-8_sLo8qfL9hcAUr-o67JwXqVueUqr5IQZJnMdhUZHDNW_TX0L3aEj2ckc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQGVMH442dwBA7G9EyyclblhXVTqXIZHTyQy3oCh4706uw&amp;oe=6A97BA84</t>
         </is>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -3560,27 +3560,27 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Batata kg</t>
+          <t>Laranja Nacional kg</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>3.49</v>
+        <v>2.99</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwHj1v_4&amp;_nc_oc=Ado90FjR93-zhwU94Lfyg-pdAM904p24Q7NJNp3LumI1HLaEihSxcBIwUsSt6VV6img&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQFUE5zOAKX66DqjLHHPKXOBr9gnLiSXLHs2WBc7JSe4Ww&amp;oe=6A97E249</t>
         </is>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -3590,20 +3590,20 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Cebola kg</t>
+          <t>Batata Doce kg</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-gru1-2.cdninstagram.com/v/t39.30808-6/781977378_1500799415426508_4866536164507670119_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDM5MzQ4NDg1OTE4MjA5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Sm8TJqnT95wQ7kNvwEAuv_w&amp;_nc_oc=AdpZZydJ1-GE-INZNtInz7cq-SA5Wv0_1GvozmDDjQeLz4rUzU8kTBOScd6cu17GRE0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=xhJmWYiNAus3mZNW9vvJyw&amp;_nc_ss=7a22e&amp;oh=00_AQE6E29Ld-MfM-p4OWrqqGCNOmN8PZvQ5Qy2CX5my112VA&amp;oe=6A96604E</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Banana Nanica kg</t>
+          <t>Cebola kg</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -3628,19 +3628,19 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-gru1-2.cdninstagram.com/v/t39.30808-6/781977378_1500799415426508_4866536164507670119_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDM5MzQ4NDg1OTE4MjA5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Sm8TJqnT95wQ7kNvwEAuv_w&amp;_nc_oc=AdpZZydJ1-GE-INZNtInz7cq-SA5Wv0_1GvozmDDjQeLz4rUzU8kTBOScd6cu17GRE0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=xhJmWYiNAus3mZNW9vvJyw&amp;_nc_ss=7a22e&amp;oh=00_AQE6E29Ld-MfM-p4OWrqqGCNOmN8PZvQ5Qy2CX5my112VA&amp;oe=6A96604E</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica kg</t>
+          <t>Cebola kg</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -3658,19 +3658,19 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -3680,27 +3680,27 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Cebola kg</t>
+          <t>Banana Nanica kg</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>3.99</v>
+        <v>4.49</v>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -3710,11 +3710,11 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Batata kg</t>
+          <t>Abacate kg</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -3723,14 +3723,14 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwGTcb9I&amp;_nc_oc=AdotyJ0U7-8_sLo8qfL9hcAUr-o67JwXqVueUqr5IQZJnMdhUZHDNW_TX0L3aEj2ckc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQGVMH442dwBA7G9EyyclblhXVTqXIZHTyQy3oCh4706uw&amp;oe=6A97BA84</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -3744,23 +3744,23 @@
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/784590234_18374239444237813_5954849484238865529_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MDc4NzgzMDE4NTU1ODE1Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LgS51WzQ1pUQ7kNvwHGtjOt&amp;_nc_oc=AdojMzIhWbI8tfpDFOc0ULBB7U_imvZiPwWtxF7zWFCxqEUTSg_RmLNt_AZvn4ly9Xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQH6lECKNNuPTx26tMwql-giu6Y26Vi3dH3OP1QqmPnisQ&amp;oe=6A97B87A</t>
         </is>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Abacate kg</t>
+          <t>Tomate kg</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>4.99</v>
+        <v>5.39</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwHLDn1l&amp;_nc_oc=AdrjU5VMRBqsuXkwk4c0CVoFJJrfcHMHOvbiwEEFcun3p9p2hik2QEPKSkkENHmKztw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQEfQDvhG99ZAq90S9bBXXRlP1P2A7WTTAAQyJqxbjexoQ&amp;oe=6A966904</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
         </is>
       </c>
     </row>
@@ -3800,11 +3800,11 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Cebola Nacional kg</t>
+          <t>Tomate kg</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
@@ -3813,14 +3813,14 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t51.82787-15/784590234_18374239444237813_5954849484238865529_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MDc4NzgzMDE4NTU1ODE1Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LgS51WzQ1pUQ7kNvwHS6sp3&amp;_nc_oc=Adq-I5_Xn8CCRjvz97Kn4r2f3xktur6Gu42Td7H_6XAB_ExqFmXB42vvtG4bWZmJfMQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQGnRzNkzmati-DS5NTWgMGRbxf6IoqXoAtgiegU0XTHuw&amp;oe=6A9666FA</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwGTcb9I&amp;_nc_oc=AdotyJ0U7-8_sLo8qfL9hcAUr-o67JwXqVueUqr5IQZJnMdhUZHDNW_TX0L3aEj2ckc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQGVMH442dwBA7G9EyyclblhXVTqXIZHTyQy3oCh4706uw&amp;oe=6A97BA84</t>
         </is>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -3830,11 +3830,11 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Maçã kg</t>
+          <t>Banana Nanica kg</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>5.49</v>
+        <v>5.99</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -3843,14 +3843,14 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwGTcb9I&amp;_nc_oc=AdotyJ0U7-8_sLo8qfL9hcAUr-o67JwXqVueUqr5IQZJnMdhUZHDNW_TX0L3aEj2ckc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQGVMH442dwBA7G9EyyclblhXVTqXIZHTyQy3oCh4706uw&amp;oe=6A97BA84</t>
         </is>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -3860,11 +3860,11 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Tomate kg</t>
+          <t>Batata Doce kg</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>5.49</v>
+        <v>5.99</v>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
@@ -3873,14 +3873,14 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwGTcb9I&amp;_nc_oc=AdotyJ0U7-8_sLo8qfL9hcAUr-o67JwXqVueUqr5IQZJnMdhUZHDNW_TX0L3aEj2ckc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQGVMH442dwBA7G9EyyclblhXVTqXIZHTyQy3oCh4706uw&amp;oe=6A97BA84</t>
         </is>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -3890,27 +3890,27 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Alface</t>
+          <t>Melão Amarelo kg</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>5.59</v>
+        <v>5.99</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/783707432_18374239420237813_1111475954040917869_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MDc4NzgyNzEwNDYzMDI1Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=73JIocu6eoQQ7kNvwG6jq0N&amp;_nc_oc=AdpP1sL849V9mn85Du3BmbKwuBjOscotmgPThScB4cqd2gf-rIkpnpaiNoFSmD0XsCc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQERi650jOmG1NNkGLW3XjLcQ95ICuDRXg8Uwlc65ZkZdA&amp;oe=6A97DEBC</t>
         </is>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -3920,27 +3920,27 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Mamão Formosa kg</t>
+          <t>Abacate kg</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>5.89</v>
+        <v>5.99</v>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-gru1-2.cdninstagram.com/v/t39.30808-6/781977378_1500799415426508_4866536164507670119_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDM5MzQ4NDg1OTE4MjA5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Sm8TJqnT95wQ7kNvwEAuv_w&amp;_nc_oc=AdpZZydJ1-GE-INZNtInz7cq-SA5Wv0_1GvozmDDjQeLz4rUzU8kTBOScd6cu17GRE0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=xhJmWYiNAus3mZNW9vvJyw&amp;_nc_ss=7a22e&amp;oh=00_AQE6E29Ld-MfM-p4OWrqqGCNOmN8PZvQ5Qy2CX5my112VA&amp;oe=6A96604E</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -3950,11 +3950,11 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Mamão Comum kg</t>
+          <t>Mamão Formoso kg</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -3963,14 +3963,14 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwHj1v_4&amp;_nc_oc=Ado90FjR93-zhwU94Lfyg-pdAM904p24Q7NJNp3LumI1HLaEihSxcBIwUsSt6VV6img&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQFUE5zOAKX66DqjLHHPKXOBr9gnLiSXLHs2WBc7JSe4Ww&amp;oe=6A97E249</t>
         </is>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -3980,20 +3980,20 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Tomate kg</t>
+          <t>Uva Preta sem Semente 500g</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwHLDn1l&amp;_nc_oc=AdrjU5VMRBqsuXkwk4c0CVoFJJrfcHMHOvbiwEEFcun3p9p2hik2QEPKSkkENHmKztw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQEfQDvhG99ZAq90S9bBXXRlP1P2A7WTTAAQyJqxbjexoQ&amp;oe=6A966904</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
@@ -4010,11 +4010,11 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Banana Nanica kg</t>
+          <t>Maçã Gala kg</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwHLDn1l&amp;_nc_oc=AdrjU5VMRBqsuXkwk4c0CVoFJJrfcHMHOvbiwEEFcun3p9p2hik2QEPKSkkENHmKztw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQEfQDvhG99ZAq90S9bBXXRlP1P2A7WTTAAQyJqxbjexoQ&amp;oe=6A966904</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwHj1v_4&amp;_nc_oc=Ado90FjR93-zhwU94Lfyg-pdAM904p24Q7NJNp3LumI1HLaEihSxcBIwUsSt6VV6img&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQFUE5zOAKX66DqjLHHPKXOBr9gnLiSXLHs2WBc7JSe4Ww&amp;oe=6A97E249</t>
         </is>
       </c>
     </row>
@@ -4040,11 +4040,11 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Batata Doce kg</t>
+          <t>Uva Vitória Isis 500g</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
@@ -4053,14 +4053,14 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwHLDn1l&amp;_nc_oc=AdrjU5VMRBqsuXkwk4c0CVoFJJrfcHMHOvbiwEEFcun3p9p2hik2QEPKSkkENHmKztw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQEfQDvhG99ZAq90S9bBXXRlP1P2A7WTTAAQyJqxbjexoQ&amp;oe=6A966904</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwGTcb9I&amp;_nc_oc=AdotyJ0U7-8_sLo8qfL9hcAUr-o67JwXqVueUqr5IQZJnMdhUZHDNW_TX0L3aEj2ckc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQGVMH442dwBA7G9EyyclblhXVTqXIZHTyQy3oCh4706uw&amp;oe=6A97BA84</t>
         </is>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -4070,27 +4070,27 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Melão Amarelo kg</t>
+          <t>Mamão Formosa kg</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-1.cdninstagram.com/v/t51.82787-15/783707432_18374239420237813_1111475954040917869_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MDc4NzgyNzEwNDYzMDI1Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=73JIocu6eoQQ7kNvwEvvLSK&amp;_nc_oc=AdpGuR3DSAz5WeKKbDC3kDNnpQRyfnT8q15GsH_qRF_h-YrFzURyrIARRvfGI5S__fU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-1.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQH0QkR77diIV5EFzpZKWsSier8yT2aa37bfxTC8hHX1sA&amp;oe=6A9654FC</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -4100,27 +4100,27 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Melão Amarelo kg</t>
+          <t>Ovos Brancos 20un</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>6.19</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-gru1-2.cdninstagram.com/v/t39.30808-6/781977378_1500799415426508_4866536164507670119_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDM5MzQ4NDg1OTE4MjA5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Sm8TJqnT95wQ7kNvwEAuv_w&amp;_nc_oc=AdpZZydJ1-GE-INZNtInz7cq-SA5Wv0_1GvozmDDjQeLz4rUzU8kTBOScd6cu17GRE0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=xhJmWYiNAus3mZNW9vvJyw&amp;_nc_ss=7a22e&amp;oh=00_AQE6E29Ld-MfM-p4OWrqqGCNOmN8PZvQ5Qy2CX5my112VA&amp;oe=6A96604E</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -4130,27 +4130,27 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Maçã Fuji un</t>
+          <t>Maçã Nacional kg</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>6.69</v>
+        <v>9.99</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-gru1-2.cdninstagram.com/v/t39.30808-6/781977378_1500799415426508_4866536164507670119_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDM5MzQ4NDg1OTE4MjA5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Sm8TJqnT95wQ7kNvwEAuv_w&amp;_nc_oc=AdpZZydJ1-GE-INZNtInz7cq-SA5Wv0_1GvozmDDjQeLz4rUzU8kTBOScd6cu17GRE0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=xhJmWYiNAus3mZNW9vvJyw&amp;_nc_ss=7a22e&amp;oh=00_AQE6E29Ld-MfM-p4OWrqqGCNOmN8PZvQ5Qy2CX5my112VA&amp;oe=6A96604E</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -4160,27 +4160,27 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Cenoura kg</t>
+          <t>Batata Easychef 1.1kg</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>6.89</v>
+        <v>15.99</v>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -4190,27 +4190,27 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Uva Vitória 500g</t>
+          <t>Batata Easychef 1.1kg</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>6.99</v>
+        <v>15.99</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -4220,27 +4220,27 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Melão kg</t>
+          <t>Alho kg</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>6.99</v>
+        <v>19.99</v>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -4250,177 +4250,177 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Mamão Formoso kg</t>
+          <t>Batata Sadia 2kg</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>6.99</v>
+        <v>27.49</v>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwEMPYyR&amp;_nc_oc=Adr_b1bUKeRFPM7ZmqdRxfot36hQCNU24IL5_Efa9ytO3ogM1bBZT4MQjmZ9FH6Ptko&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQE80woS5j4qXeeidrqbdKnZmc1O3XfaeZ4vl-pHtiNMhQ&amp;oe=6A965889</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
         </is>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Uva Vitória Isis 500g</t>
+          <t>Creme de Leite Piracanjuba 200ml</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>7.99</v>
+        <v>2.49</v>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwHLDn1l&amp;_nc_oc=AdrjU5VMRBqsuXkwk4c0CVoFJJrfcHMHOvbiwEEFcun3p9p2hik2QEPKSkkENHmKztw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQEfQDvhG99ZAq90S9bBXXRlP1P2A7WTTAAQyJqxbjexoQ&amp;oe=6A966904</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/752708427_1720016720132146_149709506206268519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg4MDAxNTI3Mzk0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7bG_IFJvHW0Q7kNvwEWBB6a&amp;_nc_oc=Adoq2psgJxwQ__5eYi26mTqHQHpwVaKQiCUPuNT8VaCbmFi8_6L7VlnBVQn3lG30lpA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFlahSgWlxg719RB5fWi5zPT7V0rDYMG9NxcM4FYnh23g&amp;oe=6A97DDD3</t>
         </is>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Maçã Gala kg</t>
+          <t>Creme de Leite Piracanjuba 200g</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>7.99</v>
+        <v>2.89</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwEMPYyR&amp;_nc_oc=Adr_b1bUKeRFPM7ZmqdRxfot36hQCNU24IL5_Efa9ytO3ogM1bBZT4MQjmZ9FH6Ptko&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQE80woS5j4qXeeidrqbdKnZmc1O3XfaeZ4vl-pHtiNMhQ&amp;oe=6A965889</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Ovos Brancos 20un</t>
+          <t>Leite Condensado Piracanjuba 395g</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>9.890000000000001</v>
+        <v>5.79</v>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/752708427_1720016720132146_149709506206268519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg4MDAxNTI3Mzk0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7bG_IFJvHW0Q7kNvwEWBB6a&amp;_nc_oc=Adoq2psgJxwQ__5eYi26mTqHQHpwVaKQiCUPuNT8VaCbmFi8_6L7VlnBVQn3lG30lpA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFlahSgWlxg719RB5fWi5zPT7V0rDYMG9NxcM4FYnh23g&amp;oe=6A97DDD3</t>
         </is>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Uva Crimson Und</t>
+          <t>Leite Integral Frimesa 1L</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>9.99</v>
+        <v>6.19</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/777867278_1720016746798810_8968857745876573698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODY1NjMwNjQwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Z9Kw3OPyQ28Q7kNvwGU7Ln_&amp;_nc_oc=AdpJfiPn_5vxe3EHndUybjPKs0Rwuwmjp82GtAJYt9vGfXm0XGC_suobP_D8GbWo6hs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQHI2faikBAuy8vCmzhrj-B7S3xTDDyOtrEIlfM262JxSw&amp;oe=6A97E3C9</t>
         </is>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Hortifruti / Ovos</t>
+          <t>Laticínios / Leites e Derivados</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Alho kg</t>
+          <t>Requeijão Carolina 180g</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>14.99</v>
+        <v>6.49</v>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://instagram.fbfh3-2.fna.fbcdn.net/v/t51.82787-15/786993044_18581670784067900_4451038722088372453_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjU4MDU3NDQ4MDgyOTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LMIY6vyvLpAQ7kNvwEERiL6&amp;_nc_oc=Adrqrk6k9A33-rTrGuk-JW1MM8PuvLEk3txmNTPJx5oIwWNot7-wrSoPlCsU5X3pR8g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-2.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQFcZZoNmk-6guewlsfvdi-tkB0z1BohQNthzoqZHyEFSg&amp;oe=6A97DC51</t>
         </is>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -4430,27 +4430,27 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Creme de Leite Piracanjuba 200g</t>
+          <t>Iogurte Carolina 800g</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>2.89</v>
+        <v>6.89</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://instagram.fbfh3-2.fna.fbcdn.net/v/t51.82787-15/786993044_18581670784067900_4451038722088372453_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjU4MDU3NDQ4MDgyOTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LMIY6vyvLpAQ7kNvwEERiL6&amp;_nc_oc=Adrqrk6k9A33-rTrGuk-JW1MM8PuvLEk3txmNTPJx5oIwWNot7-wrSoPlCsU5X3pR8g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-2.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQFcZZoNmk-6guewlsfvdi-tkB0z1BohQNthzoqZHyEFSg&amp;oe=6A97DC51</t>
         </is>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -4460,27 +4460,27 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Leite Condensado Piracanjuba 395g</t>
+          <t>Leite Condensado Moça 395g</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -4490,27 +4490,27 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Requeijão Carolina 180g</t>
+          <t>Leite Integral Santa Clara 1L</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>6.49</v>
+        <v>6.99</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/786993044_18581670784067900_4451038722088372453_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjU4MDU3NDQ4MDgyOTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LMIY6vyvLpAQ7kNvwFzRZDa&amp;_nc_oc=AdpnLYuz2zP3KEo9yE4Ckx3JontOm9ijObSBcYFUkYCV_U8owjFPlxcKpzBJ04C_tES90tOjidDM9ON6x_rxBt99&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQGidPGwWB3qvA3LHMWb_KOSttWUBKWO15Wrb_dDPdYJ8Q&amp;oe=6A965291</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -4520,27 +4520,27 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Leite Frimesa 1L</t>
+          <t>Leite Condensado Piracanjuba 395g</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>6.49</v>
+        <v>6.99</v>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786212952_18581502124067900_5975145042866561341_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODAxMDAwNzY0NzI2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CgyVTuZAOawQ7kNvwHb1DJI&amp;_nc_oc=AdoYfUdYRo6kmZkbOQDYTJfK2se0jNv6Cr9iFr4FmXy6ugLPifkO8lz405kN6GaqpoM&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGbe2prVq0TPzQK0Nvez0MjMe0G6l5nJQB3WnzPiI4STw&amp;oe=6A9679D1</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -4550,27 +4550,27 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Leite Semidesnatado Piracanjuba 1L</t>
+          <t>Requeijão Cremoso Poços de Caldas 400g</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>6.49</v>
+        <v>14.9</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -4580,27 +4580,27 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Leite Desnatado Piracanjuba 1L</t>
+          <t>Leite Ninho 370g</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>6.49</v>
+        <v>16.99</v>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://instagram.fbfh3-2.fna.fbcdn.net/v/t51.82787-15/786993044_18581670784067900_4451038722088372453_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjU4MDU3NDQ4MDgyOTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LMIY6vyvLpAQ7kNvwEERiL6&amp;_nc_oc=Adrqrk6k9A33-rTrGuk-JW1MM8PuvLEk3txmNTPJx5oIwWNot7-wrSoPlCsU5X3pR8g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-2.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQFcZZoNmk-6guewlsfvdi-tkB0z1BohQNthzoqZHyEFSg&amp;oe=6A97DC51</t>
         </is>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -4610,27 +4610,27 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Iogurte Carolina 800g</t>
+          <t>Queijo Brie Président 125g</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6.89</v>
+        <v>23.9</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/786993044_18581670784067900_4451038722088372453_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjU4MDU3NDQ4MDgyOTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LMIY6vyvLpAQ7kNvwFzRZDa&amp;_nc_oc=AdpnLYuz2zP3KEo9yE4Ckx3JontOm9ijObSBcYFUkYCV_U8owjFPlxcKpzBJ04C_tES90tOjidDM9ON6x_rxBt99&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQGidPGwWB3qvA3LHMWb_KOSttWUBKWO15Wrb_dDPdYJ8Q&amp;oe=6A965291</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -4640,27 +4640,27 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Requeijão Boua 180g</t>
+          <t>Queijo Queijo Mussarela kg</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>6.99</v>
+        <v>42.99</v>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://instagram.fbfh3-3.fna.fbcdn.net/v/t51.82787-15/782208226_18581670763067900_4505279802407067664_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjU4MDUzNjU2NDQyMTcwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r3oFMSDFP4cQ7kNvwHDOJBb&amp;_nc_oc=AdrdBYrNxeyHXUDVYaHRy8WXM3WKcs1TCmTZXgWEhxAEu8uaTpBWCf7-IBK_iVJ_Xm0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-3.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQHpcknrSOLxm-OAhLA0oIM0CMm2BGDuxSP_QmKPeSX_WA&amp;oe=6A97BE23</t>
         </is>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -4670,27 +4670,27 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Requeijão Cremoso Poços de Caldas 400g</t>
+          <t>Queijo Queijo Mussarela kg</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>14.9</v>
+        <v>44.99</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://instagram.fbfh3-3.fna.fbcdn.net/v/t51.82787-15/782208226_18581670763067900_4505279802407067664_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjU4MDUzNjU2NDQyMTcwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r3oFMSDFP4cQ7kNvwHDOJBb&amp;_nc_oc=AdrdBYrNxeyHXUDVYaHRy8WXM3WKcs1TCmTZXgWEhxAEu8uaTpBWCf7-IBK_iVJ_Xm0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-3.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQHpcknrSOLxm-OAhLA0oIM0CMm2BGDuxSP_QmKPeSX_WA&amp;oe=6A97BE23</t>
         </is>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -4700,27 +4700,27 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Requeijão Cremoso Poços de Caldas 400g</t>
+          <t>Queijo Queijo Mussarela Lactvit kg</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>14.9</v>
+        <v>46.99</v>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
         </is>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -4730,27 +4730,27 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Leite Ninho Nestlé 370g</t>
+          <t>Queijo Minas Padrão Président kg</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>16.99</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/786993044_18581670784067900_4451038722088372453_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjU4MDU3NDQ4MDgyOTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LMIY6vyvLpAQ7kNvwFzRZDa&amp;_nc_oc=AdpnLYuz2zP3KEo9yE4Ckx3JontOm9ijObSBcYFUkYCV_U8owjFPlxcKpzBJ04C_tES90tOjidDM9ON6x_rxBt99&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQGidPGwWB3qvA3LHMWb_KOSttWUBKWO15Wrb_dDPdYJ8Q&amp;oe=6A965291</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -4760,27 +4760,27 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Queijo Queijo Mussarela kg</t>
+          <t>Queijo Serra da Mantiqueira Cruzília kg</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>42.99</v>
+        <v>109.9</v>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/782208226_18581670763067900_4505279802407067664_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjU4MDUzNjU2NDQyMTcwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r3oFMSDFP4cQ7kNvwG9Ys90&amp;_nc_oc=AdoC42xnlWixiFBnGTixoIoSuINXbUH7HVIiNflpXrqsxMMsZ1amfBnwQP8JJ6V6Hvz6WXBSqMA6dxY82d9H_hvt&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQHf_fl8KlU8yVIrGBu0ZZMZ0BwlmD5m-SCHFN7zxQiZVw&amp;oe=6A966CA3</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -4790,27 +4790,27 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Queijo Queijo Mussarela kg</t>
+          <t>Queijo Serra da Mantiqueira Cruzília kg</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>44.99</v>
+        <v>109.9</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/782208226_18581670763067900_4505279802407067664_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjU4MDUzNjU2NDQyMTcwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r3oFMSDFP4cQ7kNvwG9Ys90&amp;_nc_oc=AdoC42xnlWixiFBnGTixoIoSuINXbUH7HVIiNflpXrqsxMMsZ1amfBnwQP8JJ6V6Hvz6WXBSqMA6dxY82d9H_hvt&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQHf_fl8KlU8yVIrGBu0ZZMZ0BwlmD5m-SCHFN7zxQiZVw&amp;oe=6A966CA3</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -4824,23 +4824,23 @@
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -4863,14 +4863,14 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
@@ -4923,14 +4923,14 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Amaciante Remmus 2L</t>
+          <t>Desinfetante Limza 2L</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169170_1720016740132144_6974904276998945912_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MzM0Mjg3OTk5ODQ4MTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=q-Z25NrUeboQ7kNvwGqXKen&amp;_nc_oc=AdpneHkXhiwe-uz90HGKUxE4rzZZW3mKri8P6-IjSHDJOLKSOChvN6N2I-fSa4gotoI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQExAVubRUWKBWMwfyWEjw5jU-SQLWowdPkoPr4MjZ0Ppw&amp;oe=6A97BAC9</t>
         </is>
       </c>
     </row>
@@ -4970,11 +4970,11 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Desinfetante Remmus 2L</t>
+          <t>Amaciante Remmus 2L</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>6.49</v>
+        <v>5.99</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
@@ -4983,14 +4983,14 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -5000,27 +5000,27 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Desinfetante Zupp 2L</t>
+          <t>Desinfetante Remmus 2L</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>6.99</v>
+        <v>6.49</v>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786656678_18581502151067900_8490347803628786235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODA0MDI2NTAzODUyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EcdOnVlttmoQ7kNvwH70PlI&amp;_nc_oc=Ado82ixek600vX3hfhL5KCdBOomq0p34CYASZrMbpFkNDU8Rn2ZRizO3W36sjpTqpT0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQFs12_u1-T868CKgrHhWNAaA-ZCp9unoHS_lu79usCNaA&amp;oe=6A966AED</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -5030,27 +5030,27 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Água Sanitária Zupp 2L</t>
+          <t>Água Sanitária Qboa 2L</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786656678_18581502151067900_8490347803628786235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODA0MDI2NTAzODUyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EcdOnVlttmoQ7kNvwH70PlI&amp;_nc_oc=Ado82ixek600vX3hfhL5KCdBOomq0p34CYASZrMbpFkNDU8Rn2ZRizO3W36sjpTqpT0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQFs12_u1-T868CKgrHhWNAaA-ZCp9unoHS_lu79usCNaA&amp;oe=6A966AED</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -5060,27 +5060,27 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Água Sanitária Qboa 2L</t>
+          <t>Amaciante Ypê 2L</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169170_1720016740132144_6974904276998945912_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MzM0Mjg3OTk5ODQ4MTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=q-Z25NrUeboQ7kNvwGqXKen&amp;_nc_oc=AdpneHkXhiwe-uz90HGKUxE4rzZZW3mKri8P6-IjSHDJOLKSOChvN6N2I-fSa4gotoI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQExAVubRUWKBWMwfyWEjw5jU-SQLWowdPkoPr4MjZ0Ppw&amp;oe=6A97BAC9</t>
         </is>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Desinfetante Pinho Sol 1L</t>
+          <t>Amaciante Concentrado Comfort 500ml</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -5098,19 +5098,19 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786656678_18581502151067900_8490347803628786235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODA0MDI2NTAzODUyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EcdOnVlttmoQ7kNvwH70PlI&amp;_nc_oc=Ado82ixek600vX3hfhL5KCdBOomq0p34CYASZrMbpFkNDU8Rn2ZRizO3W36sjpTqpT0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQFs12_u1-T868CKgrHhWNAaA-ZCp9unoHS_lu79usCNaA&amp;oe=6A966AED</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -5120,27 +5120,27 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Amaciante Concentrado Comfort 500ml</t>
+          <t>Sabão em Barra Ypê 800g</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169170_1720016740132144_6974904276998945912_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MzM0Mjg3OTk5ODQ4MTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=q-Z25NrUeboQ7kNvwGqXKen&amp;_nc_oc=AdpneHkXhiwe-uz90HGKUxE4rzZZW3mKri8P6-IjSHDJOLKSOChvN6N2I-fSa4gotoI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQExAVubRUWKBWMwfyWEjw5jU-SQLWowdPkoPr4MjZ0Ppw&amp;oe=6A97BAC9</t>
         </is>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -5150,27 +5150,27 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Sabão em Barra Ypê 5x160g</t>
+          <t>Amaciante de Carne Kitano 120g</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>12.99</v>
+        <v>11.99</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -5180,27 +5180,27 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Lava Roupas Líquido Ypê 1L</t>
+          <t>Sabão em Pó Tixan Ypê 1.6kg</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
-        <v>12.99</v>
+        <v>18.99</v>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/785993166_1505168978322885_7442982966970505933_n.jpg?stp=c0.0.1638.2048a_dst-jpg_e35_s1638x2048_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzI3Njk2ODM0NzI3MzQzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=XG9RuKFD9RsQ7kNvwE0O6Yi&amp;_nc_oc=AdrNOfdoiDImHK1tKaueyckNFES1wTo_HzsqBrRb0yXx2dyvyLbAHFqaILDIddlOK4E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQH35XKJVKqJg3LClPrFY0TmcZEvqaiYIZA_B7mJHQOfKQ&amp;oe=6A97B8CE</t>
         </is>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Amaciante Concentrado Girando Sol 1L</t>
+          <t>Água Sanitária Ypê 5L</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>15.99</v>
+        <v>20.9</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
@@ -5240,11 +5240,11 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Água Sanitária Ypê 5L</t>
+          <t>Sabão em Pó Tixan Ypê 2.2kg</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
-        <v>20.9</v>
+        <v>27.99</v>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
@@ -5253,37 +5253,37 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Limpeza / Cuidados com a Casa</t>
+          <t>Limpeza / Lavanderia e Louça</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Detergente em Pó Tixan Ypê 2.2kg</t>
+          <t>Sabão em Pó Tixan 800g</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>27.99</v>
+        <v>8.99</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169170_1720016740132144_6974904276998945912_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MzM0Mjg3OTk5ODQ4MTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=q-Z25NrUeboQ7kNvwGqXKen&amp;_nc_oc=AdpneHkXhiwe-uz90HGKUxE4rzZZW3mKri8P6-IjSHDJOLKSOChvN6N2I-fSa4gotoI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQExAVubRUWKBWMwfyWEjw5jU-SQLWowdPkoPr4MjZ0Ppw&amp;oe=6A97BAC9</t>
         </is>
       </c>
     </row>
@@ -5300,27 +5300,27 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Esponja de Aço Assolan 45g</t>
+          <t>Sabão em Pó Brilhante 800g</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
-        <v>1.89</v>
+        <v>10.99</v>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -5330,27 +5330,27 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Detergente Líquido Zupp 500ml</t>
+          <t>Lava Roupas Líquido Omo Ciclo Rápido 750ml</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>1.99</v>
+        <v>15.99</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786656678_18581502151067900_8490347803628786235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODA0MDI2NTAzODUyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EcdOnVlttmoQ7kNvwH70PlI&amp;_nc_oc=Ado82ixek600vX3hfhL5KCdBOomq0p34CYASZrMbpFkNDU8Rn2ZRizO3W36sjpTqpT0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQFs12_u1-T868CKgrHhWNAaA-ZCp9unoHS_lu79usCNaA&amp;oe=6A966AED</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -5360,27 +5360,27 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Lava Roupas Líquido Omo Ciclo Rápido 750ml</t>
+          <t>Sabão Líquido Omo 1.8L</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
-        <v>15.99</v>
+        <v>19.99</v>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/782169170_1720016740132144_6974904276998945912_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MzM0Mjg3OTk5ODQ4MTkyMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=q-Z25NrUeboQ7kNvwGqXKen&amp;_nc_oc=AdpneHkXhiwe-uz90HGKUxE4rzZZW3mKri8P6-IjSHDJOLKSOChvN6N2I-fSa4gotoI&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQExAVubRUWKBWMwfyWEjw5jU-SQLWowdPkoPr4MjZ0Ppw&amp;oe=6A97BAC9</t>
         </is>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -5390,57 +5390,57 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Sabão em Pó Tixan 1.6kg</t>
+          <t>Lava Roupas em Pó Ace 4kg</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>18.99</v>
+        <v>25.99</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786656678_18581502151067900_8490347803628786235_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODA0MDI2NTAzODUyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=EcdOnVlttmoQ7kNvwH70PlI&amp;_nc_oc=Ado82ixek600vX3hfhL5KCdBOomq0p34CYASZrMbpFkNDU8Rn2ZRizO3W36sjpTqpT0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQFs12_u1-T868CKgrHhWNAaA-ZCp9unoHS_lu79usCNaA&amp;oe=6A966AED</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Limpeza / Lavanderia e Louça</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Sabão em Pó Ace 4kg</t>
+          <t>Arroz Rei 5kg</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
-        <v>25.99</v>
+        <v>16.99</v>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/780374541_1720016716798813_3229780711925498508_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzM0Mjg3OTQ0NDg1Mjc3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hASiLMJHo8AQ7kNvwH-qYLe&amp;_nc_oc=AdpN4wyv3TFmwgHxbsPaSqzZSKlGml9qIzOkVDu6dKjppfxhFFwbJLlMZK-T2WP3Dto&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFK4o8yR0WVEc6v42d3X5d24xy0NEFbuvyW6zPYCvnbzA&amp;oe=6A97C00A</t>
         </is>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -5450,50 +5450,50 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Arroz São João 5kg</t>
+          <t>Arroz Rei 5kg</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786993107_18581502097067900_268524009214221357_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MjE4Nzk3NTM1Mzk5Mzk0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K-lwQ6xVRL8Q7kNvwGfqk3V&amp;_nc_oc=AdpGHzUvaPDhMW59etPUc1vg5VvBJuYrIeO4BmT9jxqgMtZI_lE5RS-OK4yGhpvtjcg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGhKWSf3lHdt-BATc5xgY0WHy3k_oX2Z7Rtvds16cPhuQ&amp;oe=6A96783A</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Açúcar</t>
+          <t>Mercearia / Arroz</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Açúcar Doce Dia 2kg</t>
+          <t>Arroz São João 5kg</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
-        <v>4.39</v>
+        <v>18.49</v>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786993107_18581502097067900_268524009214221357_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MjE4Nzk3NTM1Mzk5Mzk0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K-lwQ6xVRL8Q7kNvwGfqk3V&amp;_nc_oc=AdpGHzUvaPDhMW59etPUc1vg5VvBJuYrIeO4BmT9jxqgMtZI_lE5RS-OK4yGhpvtjcg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGhKWSf3lHdt-BATc5xgY0WHy3k_oX2Z7Rtvds16cPhuQ&amp;oe=6A96783A</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/788413222_1505168981656218_2918311736305518854_n.jpg?stp=c0.0.1638.2047a_dst-jpg_e35_s1638x2047_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzI3Njk2ODIzODI0MjE0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=G9lgZfFlLu0Q7kNvwF_JwlB&amp;_nc_oc=Adq9GwtOFmluK0l6bqtQD3-7JUdW48aHa_sTCsAnFrPTnylb2VgrBqoFFUk8N2umuJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQF_adVKWUB6yUSzhjAFyPiJHdJ3qkmFIpb3HWhALtZ2Rw&amp;oe=6A97B160</t>
         </is>
       </c>
     </row>
@@ -5505,25 +5505,25 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Biscoitos e Doces</t>
+          <t>Mercearia / Açúcar</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Biscoito Show Gol 76g</t>
+          <t>Açúcar Doce Dia 2kg</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>0.99</v>
+        <v>4.29</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/786993044_18581670784067900_4451038722088372453_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjU4MDU3NDQ4MDgyOTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LMIY6vyvLpAQ7kNvwFzRZDa&amp;_nc_oc=AdpnLYuz2zP3KEo9yE4Ckx3JontOm9ijObSBcYFUkYCV_U8owjFPlxcKpzBJ04C_tES90tOjidDM9ON6x_rxBt99&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQGidPGwWB3qvA3LHMWb_KOSttWUBKWO15Wrb_dDPdYJ8Q&amp;oe=6A965291</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/780374541_1720016716798813_3229780711925498508_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzM0Mjg3OTQ0NDg1Mjc3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hASiLMJHo8AQ7kNvwH-qYLe&amp;_nc_oc=AdpN4wyv3TFmwgHxbsPaSqzZSKlGml9qIzOkVDu6dKjppfxhFFwbJLlMZK-T2WP3Dto&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFK4o8yR0WVEc6v42d3X5d24xy0NEFbuvyW6zPYCvnbzA&amp;oe=6A97C00A</t>
         </is>
       </c>
     </row>
@@ -5540,11 +5540,11 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Biscoito Mousse Zabet 130g</t>
+          <t>Biscoito Show Gol 76g</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
-        <v>2.39</v>
+        <v>0.99</v>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
@@ -5553,14 +5553,14 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786212952_18581502124067900_5975145042866561341_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODAxMDAwNzY0NzI2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CgyVTuZAOawQ7kNvwHb1DJI&amp;_nc_oc=AdoYfUdYRo6kmZkbOQDYTJfK2se0jNv6Cr9iFr4FmXy6ugLPifkO8lz405kN6GaqpoM&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGbe2prVq0TPzQK0Nvez0MjMe0G6l5nJQB3WnzPiI4STw&amp;oe=6A9679D1</t>
+          <t>https://instagram.fbfh3-2.fna.fbcdn.net/v/t51.82787-15/786993044_18581670784067900_4451038722088372453_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjU4MDU3NDQ4MDgyOTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LMIY6vyvLpAQ7kNvwEERiL6&amp;_nc_oc=Adrqrk6k9A33-rTrGuk-JW1MM8PuvLEk3txmNTPJx5oIwWNot7-wrSoPlCsU5X3pR8g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-2.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQFcZZoNmk-6guewlsfvdi-tkB0z1BohQNthzoqZHyEFSg&amp;oe=6A97DC51</t>
         </is>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Biscoito Wafer Belma 90g</t>
+          <t>Biscoito Passatempo 130g</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -5578,19 +5578,19 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/752708427_1720016720132146_149709506206268519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg4MDAxNTI3Mzk0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7bG_IFJvHW0Q7kNvwEWBB6a&amp;_nc_oc=Adoq2psgJxwQ__5eYi26mTqHQHpwVaKQiCUPuNT8VaCbmFi8_6L7VlnBVQn3lG30lpA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFlahSgWlxg719RB5fWi5zPT7V0rDYMG9NxcM4FYnh23g&amp;oe=6A97DDD3</t>
         </is>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -5600,11 +5600,11 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Biscoito Quero Quero 300g</t>
+          <t>Biscoito Wafer Belma 90g</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
-        <v>5.99</v>
+        <v>2.49</v>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
@@ -5613,14 +5613,14 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -5630,27 +5630,27 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Biscoito Quero Quero 300g</t>
+          <t>Rosquinha Belma 500g</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>5.99</v>
+        <v>4.49</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/752708427_1720016720132146_149709506206268519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg4MDAxNTI3Mzk0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7bG_IFJvHW0Q7kNvwEWBB6a&amp;_nc_oc=Adoq2psgJxwQ__5eYi26mTqHQHpwVaKQiCUPuNT8VaCbmFi8_6L7VlnBVQn3lG30lpA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFlahSgWlxg719RB5fWi5zPT7V0rDYMG9NxcM4FYnh23g&amp;oe=6A97DDD3</t>
         </is>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -5660,20 +5660,20 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Bala Icekiss 500g</t>
+          <t>Mistura Para Bolo Adorale 400g</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
-        <v>7.99</v>
+        <v>5.49</v>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/777867278_1720016746798810_8968857745876573698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODY1NjMwNjQwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Z9Kw3OPyQ28Q7kNvwGU7Ln_&amp;_nc_oc=AdpJfiPn_5vxe3EHndUybjPKs0Rwuwmjp82GtAJYt9vGfXm0XGC_suobP_D8GbWo6hs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQHI2faikBAuy8vCmzhrj-B7S3xTDDyOtrEIlfM262JxSw&amp;oe=6A97E3C9</t>
         </is>
       </c>
     </row>
@@ -5690,11 +5690,11 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Bala Icekiss 500g</t>
+          <t>Biscoito Quero Quero 300g</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
@@ -5720,27 +5720,27 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Nescau 370g</t>
+          <t>Chocolate Hershey's 82g</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>9.99</v>
+        <v>7.49</v>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/782208226_18581670763067900_4505279802407067664_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjU4MDUzNjU2NDQyMTcwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r3oFMSDFP4cQ7kNvwG9Ys90&amp;_nc_oc=AdoC42xnlWixiFBnGTixoIoSuINXbUH7HVIiNflpXrqsxMMsZ1amfBnwQP8JJ6V6Hvz6WXBSqMA6dxY82d9H_hvt&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQHf_fl8KlU8yVIrGBu0ZZMZ0BwlmD5m-SCHFN7zxQiZVw&amp;oe=6A966CA3</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/752708427_1720016720132146_149709506206268519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg4MDAxNTI3Mzk0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7bG_IFJvHW0Q7kNvwEWBB6a&amp;_nc_oc=Adoq2psgJxwQ__5eYi26mTqHQHpwVaKQiCUPuNT8VaCbmFi8_6L7VlnBVQn3lG30lpA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFlahSgWlxg719RB5fWi5zPT7V0rDYMG9NxcM4FYnh23g&amp;oe=6A97DDD3</t>
         </is>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Ramin Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -5750,20 +5750,20 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Biscoito Infantil Biscotti Papapá 60g</t>
+          <t>Bala Icekiss 500g</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>11.19</v>
+        <v>7.99</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fagp5-1.fna.fbcdn.net/v/t51.82787-15/782413347_18423080377199090_2820046938058952728_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MTc0NDk1NjY5MzEzNzA5MzE4NDIzMDgwMzcxMTk5MDkw.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=1YNXWGkVTegQ7kNvwFnGD1y&amp;_nc_oc=Adqb-3k5FKK6WzXHVpCZ5gBoXBtn1gyQvQHQG9sMCMBgLMwbRjl9F2VhpR0XM09tP0M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fagp5-1.fna&amp;_nc_gid=3UEsjUfFydbfqZH2bgBZbA&amp;_nc_ss=7a22e&amp;oh=00_AQELzl4FrEMFD6d-zrVLwdU5dqNZXYf9Tk1UmsEmM7DyOQ&amp;oe=6A965A2B</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
@@ -5775,12 +5775,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Café</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Café Aroma 250g</t>
+          <t>Nescau 370g</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -5793,247 +5793,247 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786993107_18581502097067900_268524009214221357_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MjE4Nzk3NTM1Mzk5Mzk0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K-lwQ6xVRL8Q7kNvwGfqk3V&amp;_nc_oc=AdpGHzUvaPDhMW59etPUc1vg5VvBJuYrIeO4BmT9jxqgMtZI_lE5RS-OK4yGhpvtjcg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGhKWSf3lHdt-BATc5xgY0WHy3k_oX2Z7Rtvds16cPhuQ&amp;oe=6A96783A</t>
+          <t>https://instagram.fbfh3-3.fna.fbcdn.net/v/t51.82787-15/782208226_18581670763067900_4505279802407067664_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjU4MDUzNjU2NDQyMTcwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r3oFMSDFP4cQ7kNvwHDOJBb&amp;_nc_oc=AdrdBYrNxeyHXUDVYaHRy8WXM3WKcs1TCmTZXgWEhxAEu8uaTpBWCf7-IBK_iVJ_Xm0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-3.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQHpcknrSOLxm-OAhLA0oIM0CMm2BGDuxSP_QmKPeSX_WA&amp;oe=6A97BE23</t>
         </is>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Café</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Café Sinop 1kg</t>
+          <t>Bombom Sortidos Lacta Nestlé Garoto 220g</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>28.9</v>
+        <v>10.99</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/752708427_1720016720132146_149709506206268519_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg4MDAxNTI3Mzk0NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7bG_IFJvHW0Q7kNvwEWBB6a&amp;_nc_oc=Adoq2psgJxwQ__5eYi26mTqHQHpwVaKQiCUPuNT8VaCbmFi8_6L7VlnBVQn3lG30lpA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFlahSgWlxg719RB5fWi5zPT7V0rDYMG9NxcM4FYnh23g&amp;oe=6A97DDD3</t>
         </is>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Ramin Supermercado</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Café</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Café Sinop 500g</t>
+          <t>Biscoito Infantil Biscotti Papapá</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
-        <v>28.9</v>
+        <v>11.19</v>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://instagram.fyyc3-1.fna.fbcdn.net/v/t51.82787-15/782413347_18423080377199090_2820046938058952728_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MTc0NDk1NjY5MzEzNzA5MzE4NDIzMDgwMzcxMTk5MDkw.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=_cfhR42QcCUQ7kNvwEVGk_r&amp;_nc_oc=Ado_w16XBNCHwBLbzDOeTQJDleh4c3TzoW0JMumVkqZKmTQY4rj20SajQJVbxPiyleQXu3bok-FntkR8bFwJiwH9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyyc3-1.fna&amp;_nc_gid=ecXOl_A4zJTN1oAGKz2wfg&amp;_nc_ss=7a22e&amp;oh=00_AQHT3ECLdF2vApx3v1bkkG4m23ox24HMfGZKejofRgAz4Q&amp;oe=6A97E3EB</t>
         </is>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Mercearia / Biscoitos e Doces</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Macarrão Espaguete Vitoriosa 400g</t>
+          <t>Caixa de Bombom Nestlé 251g</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>2.39</v>
+        <v>12.99</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Macarrão Espaguete Vitoriosa 400g</t>
+          <t>Café Torrado e Moído Nascente Araguaia 250g</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
-        <v>2.39</v>
+        <v>8.99</v>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/777867278_1720016746798810_8968857745876573698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODY1NjMwNjQwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Z9Kw3OPyQ28Q7kNvwGU7Ln_&amp;_nc_oc=AdpJfiPn_5vxe3EHndUybjPKs0Rwuwmjp82GtAJYt9vGfXm0XGC_suobP_D8GbWo6hs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQHI2faikBAuy8vCmzhrj-B7S3xTDDyOtrEIlfM262JxSw&amp;oe=6A97E3C9</t>
         </is>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Farinha de Trigo Globo 1kg</t>
+          <t>Café Torrado e Moído Melitta 500g</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>3.89</v>
+        <v>23.9</v>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786993107_18581502097067900_268524009214221357_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MjE4Nzk3NTM1Mzk5Mzk0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K-lwQ6xVRL8Q7kNvwGfqk3V&amp;_nc_oc=AdpGHzUvaPDhMW59etPUc1vg5VvBJuYrIeO4BmT9jxqgMtZI_lE5RS-OK4yGhpvtjcg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGhKWSf3lHdt-BATc5xgY0WHy3k_oX2Z7Rtvds16cPhuQ&amp;oe=6A96783A</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Tapioca Amafil 500g</t>
+          <t>Café Caboclo 500g</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>4.99</v>
+        <v>24.49</v>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/782208226_18581670763067900_4505279802407067664_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjU4MDUzNjU2NDQyMTcwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r3oFMSDFP4cQ7kNvwG9Ys90&amp;_nc_oc=AdoC42xnlWixiFBnGTixoIoSuINXbUH7HVIiNflpXrqsxMMsZ1amfBnwQP8JJ6V6Hvz6WXBSqMA6dxY82d9H_hvt&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQHf_fl8KlU8yVIrGBu0ZZMZ0BwlmD5m-SCHFN7zxQiZVw&amp;oe=6A966CA3</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/788413222_1505168981656218_2918311736305518854_n.jpg?stp=c0.0.1638.2047a_dst-jpg_e35_s1638x2047_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzI3Njk2ODIzODI0MjE0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=G9lgZfFlLu0Q7kNvwF_JwlB&amp;_nc_oc=Adq9GwtOFmluK0l6bqtQD3-7JUdW48aHa_sTCsAnFrPTnylb2VgrBqoFFUk8N2umuJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQF_adVKWUB6yUSzhjAFyPiJHdJ3qkmFIpb3HWhALtZ2Rw&amp;oe=6A97B160</t>
         </is>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Tapioca Amafil 500g</t>
+          <t>Café Torrado e Moído Caboclo 500g</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>4.99</v>
+        <v>24.9</v>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Farinha de Rosca kg</t>
+          <t>Café Brasileiro 500g</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>11.99</v>
+        <v>24.99</v>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/786213187_18581670739067900_7614859529006382993_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MjU4MDUwMTEzMDg5NTg1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PKu5sCqaXh0Q7kNvwEZtR1F&amp;_nc_oc=AdrXnq9-E_K9Ar0dU2z_3MTrPlViu9NeiIkkLyH1ovDDVgRakx0nMLgvofX44g9PCKQdYELhczrdPChbWwcfmlyE&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQFP-keuWSslHivgVtK2a45M4wCXZwnVyjGnvVIAzWEO8Q&amp;oe=6A96826B</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
@@ -6045,16 +6045,16 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Farináceos</t>
+          <t>Mercearia / Café</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Farinha de Trigo Venturelli 5kg</t>
+          <t>Café Torrado e Moído Sinop 500g</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>25.9</v>
+        <v>28.9</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
@@ -6080,11 +6080,11 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Farinha de Trigo Venturelli 5kg</t>
+          <t>Macarrão Espaguete Vitoriosa 400g</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
-        <v>25.9</v>
+        <v>2.39</v>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
@@ -6093,37 +6093,37 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Mercearia / Farináceos</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Milho Verde Quero 170g</t>
+          <t>Tapioca Amafil 500g</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://instagram.fbfh3-3.fna.fbcdn.net/v/t51.82787-15/782208226_18581670763067900_4505279802407067664_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MjU4MDUzNjU2NDQyMTcwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=r3oFMSDFP4cQ7kNvwHDOJBb&amp;_nc_oc=AdrdBYrNxeyHXUDVYaHRy8WXM3WKcs1TCmTZXgWEhxAEu8uaTpBWCf7-IBK_iVJ_Xm0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-3.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQHpcknrSOLxm-OAhLA0oIM0CMm2BGDuxSP_QmKPeSX_WA&amp;oe=6A97BE23</t>
         </is>
       </c>
     </row>
@@ -6135,16 +6135,16 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Mercearia / Farináceos</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Feijão Kumbuca 1kg</t>
+          <t>Tapioca Amafil 500g</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
-        <v>6.59</v>
+        <v>4.99</v>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
@@ -6165,25 +6165,25 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Grãos e Conservas</t>
+          <t>Mercearia / Farináceos</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Feijão Carioca Rei 1kg</t>
+          <t>Farinha de Trigo Ventureli 1kg</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>6.99</v>
+        <v>5.49</v>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786993107_18581502097067900_268524009214221357_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MjE4Nzk3NTM1Mzk5Mzk0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K-lwQ6xVRL8Q7kNvwGfqk3V&amp;_nc_oc=AdpGHzUvaPDhMW59etPUc1vg5VvBJuYrIeO4BmT9jxqgMtZI_lE5RS-OK4yGhpvtjcg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGhKWSf3lHdt-BATc5xgY0WHy3k_oX2Z7Rtvds16cPhuQ&amp;oe=6A96783A</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/780374541_1720016716798813_3229780711925498508_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzM0Mjg3OTQ0NDg1Mjc3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hASiLMJHo8AQ7kNvwH-qYLe&amp;_nc_oc=AdpN4wyv3TFmwgHxbsPaSqzZSKlGml9qIzOkVDu6dKjppfxhFFwbJLlMZK-T2WP3Dto&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFK4o8yR0WVEc6v42d3X5d24xy0NEFbuvyW6zPYCvnbzA&amp;oe=6A97C00A</t>
         </is>
       </c>
     </row>
@@ -6195,16 +6195,16 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Massas</t>
+          <t>Mercearia / Farináceos</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Macarrão Instantâneo Adoralle 80g</t>
+          <t>Farinha de Rosca kg</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
-        <v>1.49</v>
+        <v>11.99</v>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
@@ -6213,127 +6213,127 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786212952_18581502124067900_5975145042866561341_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODAxMDAwNzY0NzI2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CgyVTuZAOawQ7kNvwHb1DJI&amp;_nc_oc=AdoYfUdYRo6kmZkbOQDYTJfK2se0jNv6Cr9iFr4FmXy6ugLPifkO8lz405kN6GaqpoM&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGbe2prVq0TPzQK0Nvez0MjMe0G6l5nJQB3WnzPiI4STw&amp;oe=6A9679D1</t>
+          <t>https://instagram.fbfh3-3.fna.fbcdn.net/v/t51.82787-15/786213187_18581670739067900_7614859529006382993_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MjU4MDUwMTEzMDg5NTg1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUxa-pkhp30Q7kNvwFboBxx&amp;_nc_oc=AdrdPmwYkIdxugjAF4fRL9r4UGVTOpjGSkUOEdAU1t5Oo3xndNO8NxT5cLPhdG2qyec&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-3.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQGIkcOFnuo_aKcrbniilp1lQXQOtK-0t77BIjYgYxXyNQ&amp;oe=6A97D3EB</t>
         </is>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Massas</t>
+          <t>Mercearia / Farináceos</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Macarrão Liane 500g</t>
+          <t>Farinha de Trigo Venturelli 5kg</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>2.99</v>
+        <v>25.9</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786212952_18581502124067900_5975145042866561341_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODAxMDAwNzY0NzI2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CgyVTuZAOawQ7kNvwHb1DJI&amp;_nc_oc=AdoYfUdYRo6kmZkbOQDYTJfK2se0jNv6Cr9iFr4FmXy6ugLPifkO8lz405kN6GaqpoM&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGbe2prVq0TPzQK0Nvez0MjMe0G6l5nJQB3WnzPiI4STw&amp;oe=6A9679D1</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Massas</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Macarrão Semolado Espaguete Galo 500g</t>
+          <t>Feijão Kumbuca 1kg</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
-        <v>3.39</v>
+        <v>6.49</v>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/780374541_1720016716798813_3229780711925498508_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzM0Mjg3OTQ0NDg1Mjc3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hASiLMJHo8AQ7kNvwH-qYLe&amp;_nc_oc=AdpN4wyv3TFmwgHxbsPaSqzZSKlGml9qIzOkVDu6dKjppfxhFFwbJLlMZK-T2WP3Dto&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFK4o8yR0WVEc6v42d3X5d24xy0NEFbuvyW6zPYCvnbzA&amp;oe=6A97C00A</t>
         </is>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Ramin Supermercado</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Massas</t>
+          <t>Mercearia / Grãos e Conservas</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Macarrão Infantil Papa Pasta Papapá 200g</t>
+          <t>Feijão Kumbuca 1kg</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>12.55</v>
+        <v>6.59</v>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fagp5-1.fna.fbcdn.net/v/t51.82787-15/782413347_18423080377199090_2820046938058952728_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MTc0NDk1NjY5MzEzNzA5MzE4NDIzMDgwMzcxMTk5MDkw.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=1YNXWGkVTegQ7kNvwFnGD1y&amp;_nc_oc=Adqb-3k5FKK6WzXHVpCZ5gBoXBtn1gyQvQHQG9sMCMBgLMwbRjl9F2VhpR0XM09tP0M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fagp5-1.fna&amp;_nc_gid=3UEsjUfFydbfqZH2bgBZbA&amp;_nc_ss=7a22e&amp;oh=00_AQELzl4FrEMFD6d-zrVLwdU5dqNZXYf9Tk1UmsEmM7DyOQ&amp;oe=6A965A2B</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Molhos e Condimentos</t>
+          <t>Mercearia / Massas</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Molho de Tomate Olé 300g</t>
+          <t>Macarrão Espaguete Ninfa 500g</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/786374804_17907135297496981_3284822547929331185_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MTUxMTM1MzQ1NTYyODIxNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Lh1PDU5a_NcQ7kNvwHRgx8E&amp;_nc_oc=Ado_ugE0xr6qbVNhg3VQkn4Et9o8ujEzC5-6w-jpV5dgznrkZzRIZbE3YYslNXjqges&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=kww7j6xPMxEEP18b0yWTkA&amp;_nc_ss=7a22e&amp;oh=00_AQGh01Ql-xaPtM0H50R8x4dS1hx__5ZEE198XJVFCwHupw&amp;oe=6A97E4BE</t>
         </is>
       </c>
     </row>
@@ -6345,102 +6345,102 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Molhos e Condimentos</t>
+          <t>Mercearia / Massas</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Molho de Tomate Olé 300g</t>
+          <t>Macarrão Caseiro D'itália 1kg</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>1.99</v>
+        <v>11.9</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Mercearia / Óleos e Azeites</t>
+          <t>Mercearia / Massas</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Batata Monalisa kg</t>
+          <t>Macarrão Caseiro D'itália 1kg</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
-        <v>3.99</v>
+        <v>11.9</v>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fra5-2.cdninstagram.com/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwHLDn1l&amp;_nc_oc=AdrjU5VMRBqsuXkwk4c0CVoFJJrfcHMHOvbiwEEFcun3p9p2hik2QEPKSkkENHmKztw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra5-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQEfQDvhG99ZAq90S9bBXXRlP1P2A7WTTAAQyJqxbjexoQ&amp;oe=6A966904</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Ramin Supermercado</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Mercearia / Óleos e Azeites</t>
+          <t>Mercearia / Massas</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Óleo Liza 900ml</t>
+          <t>Macarrão Infantil Mini Fusilli Tricolori Papapá 200g</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>6.49</v>
+        <v>12.55</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786993107_18581502097067900_268524009214221357_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MjE4Nzk3NTM1Mzk5Mzk0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=K-lwQ6xVRL8Q7kNvwGfqk3V&amp;_nc_oc=AdpGHzUvaPDhMW59etPUc1vg5VvBJuYrIeO4BmT9jxqgMtZI_lE5RS-OK4yGhpvtjcg&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGhKWSf3lHdt-BATc5xgY0WHy3k_oX2Z7Rtvds16cPhuQ&amp;oe=6A96783A</t>
+          <t>https://instagram.fyyc3-1.fna.fbcdn.net/v/t51.82787-15/782413347_18423080377199090_2820046938058952728_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MTc0NDk1NjY5MzEzNzA5MzE4NDIzMDgwMzcxMTk5MDkw.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=_cfhR42QcCUQ7kNvwEVGk_r&amp;_nc_oc=Ado_w16XBNCHwBLbzDOeTQJDleh4c3TzoW0JMumVkqZKmTQY4rj20SajQJVbxPiyleQXu3bok-FntkR8bFwJiwH9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyyc3-1.fna&amp;_nc_gid=ecXOl_A4zJTN1oAGKz2wfg&amp;_nc_ss=7a22e&amp;oh=00_AQHT3ECLdF2vApx3v1bkkG4m23ox24HMfGZKejofRgAz4Q&amp;oe=6A97E3EB</t>
         </is>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Molhos e Condimentos</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Bolinho Bauducco 40g</t>
+          <t>Molho de Tomate Olé 300g</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -6453,67 +6453,67 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Molhos e Condimentos</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Tempero Mika 50g</t>
+          <t>Extrato de Tomate Elefante 300g</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>2.39</v>
+        <v>7.19</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786212952_18581502124067900_5975145042866561341_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjE4ODAxMDAwNzY0NzI2Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=CgyVTuZAOawQ7kNvwHb1DJI&amp;_nc_oc=AdoYfUdYRo6kmZkbOQDYTJfK2se0jNv6Cr9iFr4FmXy6ugLPifkO8lz405kN6GaqpoM&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGbe2prVq0TPzQK0Nvez0MjMe0G6l5nJQB3WnzPiI4STw&amp;oe=6A9679D1</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/788413222_1505168981656218_2918311736305518854_n.jpg?stp=c0.0.1638.2047a_dst-jpg_e35_s1638x2047_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzI3Njk2ODIzODI0MjE0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=G9lgZfFlLu0Q7kNvwF_JwlB&amp;_nc_oc=Adq9GwtOFmluK0l6bqtQD3-7JUdW48aHa_sTCsAnFrPTnylb2VgrBqoFFUk8N2umuJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQF_adVKWUB6yUSzhjAFyPiJHdJ3qkmFIpb3HWhALtZ2Rw&amp;oe=6A97B160</t>
         </is>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Água Mineral sem Gás Puríssima 500ml</t>
+          <t>Macarrão Gallo 500g</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fco2-1.cdninstagram.com/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=xshLq_1UYukQ7kNvwH8NEjx&amp;_nc_oc=AdppzFu-Hh0BO5RnjF9YuSyN_3_XxabLEQ8RsW1ev3ULvAAZEuGYqgDflkGsmIgvtpk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_gid=K-hLFdWbPpxYMOy6NjRGCw&amp;_nc_ss=7a22e&amp;oh=00_AQG-b1CP2iK33dzJWt-upWfT8kFYia1MjGGgavA4Gd6j9A&amp;oe=6A96673B</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/777867278_1720016746798810_8968857745876573698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODY1NjMwNjQwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Z9Kw3OPyQ28Q7kNvwGU7Ln_&amp;_nc_oc=AdpJfiPn_5vxe3EHndUybjPKs0Rwuwmjp82GtAJYt9vGfXm0XGC_suobP_D8GbWo6hs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQHI2faikBAuy8vCmzhrj-B7S3xTDDyOtrEIlfM262JxSw&amp;oe=6A97E3C9</t>
         </is>
       </c>
     </row>
@@ -6525,106 +6525,106 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Água Mineral com Gás Puríssima 500ml</t>
+          <t>Batata Monalisa kg</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>2.89</v>
+        <v>3.99</v>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fco2-1.cdninstagram.com/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=xshLq_1UYukQ7kNvwH8NEjx&amp;_nc_oc=AdppzFu-Hh0BO5RnjF9YuSyN_3_XxabLEQ8RsW1ev3ULvAAZEuGYqgDflkGsmIgvtpk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_gid=K-hLFdWbPpxYMOy6NjRGCw&amp;_nc_ss=7a22e&amp;oh=00_AQG-b1CP2iK33dzJWt-upWfT8kFYia1MjGGgavA4Gd6j9A&amp;oe=6A96673B</t>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/780551083_18374239432237813_6720893505103105991_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MDc4NzgzMjYxOTg0ODE2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=myPGG8GAEqkQ7kNvwGTcb9I&amp;_nc_oc=AdotyJ0U7-8_sLo8qfL9hcAUr-o67JwXqVueUqr5IQZJnMdhUZHDNW_TX0L3aEj2ckc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQGVMH442dwBA7G9EyyclblhXVTqXIZHTyQy3oCh4706uw&amp;oe=6A97BA84</t>
         </is>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Água Mineral sem Gás Brunado 1.5L</t>
+          <t>Batata Monalisa kg</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
-        <v>2.89</v>
+        <v>3.99</v>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-fco2-1.cdninstagram.com/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=xshLq_1UYukQ7kNvwH8NEjx&amp;_nc_oc=AdppzFu-Hh0BO5RnjF9YuSyN_3_XxabLEQ8RsW1ev3ULvAAZEuGYqgDflkGsmIgvtpk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_gid=K-hLFdWbPpxYMOy6NjRGCw&amp;_nc_ss=7a22e&amp;oh=00_AQG-b1CP2iK33dzJWt-upWfT8kFYia1MjGGgavA4Gd6j9A&amp;oe=6A96673B</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Abóbora Cabotia kg</t>
+          <t>Óleo de Soja Liza 900ml</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/780374541_1720016716798813_3229780711925498508_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MzM0Mjg3OTQ0NDg1Mjc3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hASiLMJHo8AQ7kNvwH-qYLe&amp;_nc_oc=AdpN4wyv3TFmwgHxbsPaSqzZSKlGml9qIzOkVDu6dKjppfxhFFwbJLlMZK-T2WP3Dto&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFK4o8yR0WVEc6v42d3X5d24xy0NEFbuvyW6zPYCvnbzA&amp;oe=6A97C00A</t>
         </is>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Limpa Alumínio Polylar 500ml</t>
+          <t>Óleo de Soja Concórdia 900ml</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
-        <v>3.49</v>
+        <v>6.89</v>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
@@ -6633,127 +6633,127 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/788413222_1505168981656218_2918311736305518854_n.jpg?stp=c0.0.1638.2047a_dst-jpg_e35_s1638x2047_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzI3Njk2ODIzODI0MjE0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=G9lgZfFlLu0Q7kNvwF_JwlB&amp;_nc_oc=Adq9GwtOFmluK0l6bqtQD3-7JUdW48aHa_sTCsAnFrPTnylb2VgrBqoFFUk8N2umuJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQF_adVKWUB6yUSzhjAFyPiJHdJ3qkmFIpb3HWhALtZ2Rw&amp;oe=6A97B160</t>
         </is>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Batatinha kg</t>
+          <t>Azeite de Oliva Andorinha 250ml</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>3.69</v>
+        <v>14.9</v>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-gru1-2.cdninstagram.com/v/t39.30808-6/781977378_1500799415426508_4866536164507670119_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDM5MzQ4NDg1OTE4MjA5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Sm8TJqnT95wQ7kNvwEAuv_w&amp;_nc_oc=AdpZZydJ1-GE-INZNtInz7cq-SA5Wv0_1GvozmDDjQeLz4rUzU8kTBOScd6cu17GRE0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=xhJmWYiNAus3mZNW9vvJyw&amp;_nc_ss=7a22e&amp;oh=00_AQE6E29Ld-MfM-p4OWrqqGCNOmN8PZvQ5Qy2CX5my112VA&amp;oe=6A96604E</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Beterraba kg</t>
+          <t>Azeite de Oliva Extra Virgem Cinque Terre 500ml</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
-        <v>3.99</v>
+        <v>36.99</v>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-gru1-2.cdninstagram.com/v/t39.30808-6/781977378_1500799415426508_4866536164507670119_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDM5MzQ4NDg1OTE4MjA5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Sm8TJqnT95wQ7kNvwEAuv_w&amp;_nc_oc=AdpZZydJ1-GE-INZNtInz7cq-SA5Wv0_1GvozmDDjQeLz4rUzU8kTBOScd6cu17GRE0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=xhJmWYiNAus3mZNW9vvJyw&amp;_nc_ss=7a22e&amp;oh=00_AQE6E29Ld-MfM-p4OWrqqGCNOmN8PZvQ5Qy2CX5my112VA&amp;oe=6A96604E</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Abóbora Kabotiã kg</t>
+          <t>Azeite de Oliva Extra Virgem Ea 500ml</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>3.99</v>
+        <v>53.9</v>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwEMPYyR&amp;_nc_oc=Adr_b1bUKeRFPM7ZmqdRxfot36hQCNU24IL5_Efa9ytO3ogM1bBZT4MQjmZ9FH6Ptko&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQE80woS5j4qXeeidrqbdKnZmc1O3XfaeZ4vl-pHtiNMhQ&amp;oe=6A965889</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Mercearia / Óleos e Azeites</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Repolho Verde kg</t>
+          <t>Azeite de Oliva Extra Virgem Ea Cartuxa 500ml</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>4.39</v>
+        <v>53.9</v>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-gru1-2.cdninstagram.com/v/t39.30808-6/781977378_1500799415426508_4866536164507670119_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=110&amp;ig_cache_key=Mzk3MDM5MzQ4NDg1OTE4MjA5Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Sm8TJqnT95wQ7kNvwEAuv_w&amp;_nc_oc=AdpZZydJ1-GE-INZNtInz7cq-SA5Wv0_1GvozmDDjQeLz4rUzU8kTBOScd6cu17GRE0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gru1-2.cdninstagram.com&amp;_nc_gid=xhJmWYiNAus3mZNW9vvJyw&amp;_nc_ss=7a22e&amp;oh=00_AQE6E29Ld-MfM-p4OWrqqGCNOmN8PZvQ5Qy2CX5my112VA&amp;oe=6A96604E</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
@@ -6770,27 +6770,27 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Ponkan kg</t>
+          <t>Bolinho Bauducco 40g</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>4.99</v>
+        <v>1.99</v>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -6800,20 +6800,20 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Pilha Alcalina Aaa Kian 4un</t>
+          <t>Água Mineral sem Gás Purissima 500ml</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
-        <v>4.99</v>
+        <v>2.6</v>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=fT0MPnunqcwQ7kNvwGoHPRi&amp;_nc_oc=Ado_NnTWGAC2RLX8sNpjSvme7alGmKtaDkL87QyRjEwmsVTvTxtQgzw52rTwayJtwSM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=S9kVzKn3t-x4IZA7o9dmkA&amp;_nc_ss=7a22e&amp;oh=00_AQFChcJHGtmESsZp0K7WUFlKeaX66h-aUkvSTQNwMItcHQ&amp;oe=6A97B8BB</t>
         </is>
       </c>
     </row>
@@ -6830,27 +6830,27 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Claybom 500g</t>
+          <t>Milho em Conserva Só Fruta 170g</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>5.49</v>
+        <v>2.89</v>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/786213187_18581670739067900_7614859529006382993_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MjU4MDUwMTEzMDg5NTg1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PKu5sCqaXh0Q7kNvwEZtR1F&amp;_nc_oc=AdrXnq9-E_K9Ar0dU2z_3MTrPlViu9NeiIkkLyH1ovDDVgRakx0nMLgvofX44g9PCKQdYELhczrdPChbWwcfmlyE&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQFP-keuWSslHivgVtK2a45M4wCXZwnVyjGnvVIAzWEO8Q&amp;oe=6A96826B</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/777867278_1720016746798810_8968857745876573698_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODY1NjMwNjQwOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Z9Kw3OPyQ28Q7kNvwGU7Ln_&amp;_nc_oc=AdpJfiPn_5vxe3EHndUybjPKs0Rwuwmjp82GtAJYt9vGfXm0XGC_suobP_D8GbWo6hs&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQHI2faikBAuy8vCmzhrj-B7S3xTDDyOtrEIlfM262JxSw&amp;oe=6A97E3C9</t>
         </is>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -6860,27 +6860,27 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Amendoim Oba Oba 400g</t>
+          <t>Água Mineral sem Gás Purissima 500ml</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
-        <v>5.9</v>
+        <v>2.89</v>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=fT0MPnunqcwQ7kNvwGoHPRi&amp;_nc_oc=Ado_NnTWGAC2RLX8sNpjSvme7alGmKtaDkL87QyRjEwmsVTvTxtQgzw52rTwayJtwSM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=S9kVzKn3t-x4IZA7o9dmkA&amp;_nc_ss=7a22e&amp;oh=00_AQFChcJHGtmESsZp0K7WUFlKeaX66h-aUkvSTQNwMItcHQ&amp;oe=6A97B8BB</t>
         </is>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -6890,27 +6890,27 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Amendoim Oba Oba 400g</t>
+          <t>Água Mineral sem Gás Brufado 500ml</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>5.9</v>
+        <v>3.29</v>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/781162059_18373952632237813_4532706053079983862_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk2OTQ0MzcyNDUxNzY0ODEyMTE4MzczOTUyNjI5MjM3ODEz.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=fT0MPnunqcwQ7kNvwGoHPRi&amp;_nc_oc=Ado_NnTWGAC2RLX8sNpjSvme7alGmKtaDkL87QyRjEwmsVTvTxtQgzw52rTwayJtwSM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=S9kVzKn3t-x4IZA7o9dmkA&amp;_nc_ss=7a22e&amp;oh=00_AQFChcJHGtmESsZp0K7WUFlKeaX66h-aUkvSTQNwMItcHQ&amp;oe=6A97B8BB</t>
         </is>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -6920,11 +6920,11 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Língua Bovina kg</t>
+          <t>Limpa Alumínio Polylar 500ml</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
-        <v>5.99</v>
+        <v>3.49</v>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
@@ -6933,14 +6933,14 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -6950,27 +6950,27 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Repolho Verde kg</t>
+          <t>Mistura Láctea Condensada Cremor 395g</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>5.99</v>
+        <v>3.69</v>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwEMPYyR&amp;_nc_oc=Adr_b1bUKeRFPM7ZmqdRxfot36hQCNU24IL5_Efa9ytO3ogM1bBZT4MQjmZ9FH6Ptko&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQE80woS5j4qXeeidrqbdKnZmc1O3XfaeZ4vl-pHtiNMhQ&amp;oe=6A965889</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -6980,27 +6980,27 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Mexerica kg</t>
+          <t>Mistura Láctea Condensada Cremor 395g</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
-        <v>6.99</v>
+        <v>3.69</v>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-icn2-1.cdninstagram.com/v/t51.82787-15/778986014_18192356080391764_2727967813090525154_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDM4ODQ5NTE4MTQxNTkzNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=50Gin0TDwkYQ7kNvwFRXMk_&amp;_nc_oc=Adq1jeZCIm0fJChDH-K0bIzQsjuYRYNu5MZ_RHk9-4qDtB5RfUf-4hdhNbkkAXT492E&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-icn2-1.cdninstagram.com&amp;_nc_gid=NLn0qkOUaC7GUk6QhEmUMQ&amp;_nc_ss=7a22e&amp;oh=00_AQHNWI81bEW9P4XHyZ2-M8XSSOgHSuwwUI29oNEDVMU14A&amp;oe=6A968150</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -7010,20 +7010,20 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Sucrilhos Kellogg's 240g</t>
+          <t>Abóbora Kabotiã kg</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>7.49</v>
+        <v>3.99</v>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/786993044_18581670784067900_4451038722088372453_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjU4MDU3NDQ4MDgyOTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LMIY6vyvLpAQ7kNvwFzRZDa&amp;_nc_oc=AdpnLYuz2zP3KEo9yE4Ckx3JontOm9ijObSBcYFUkYCV_U8owjFPlxcKpzBJ04C_tES90tOjidDM9ON6x_rxBt99&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQGidPGwWB3qvA3LHMWb_KOSttWUBKWO15Wrb_dDPdYJ8Q&amp;oe=6A965291</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwHj1v_4&amp;_nc_oc=Ado90FjR93-zhwU94Lfyg-pdAM904p24Q7NJNp3LumI1HLaEihSxcBIwUsSt6VV6img&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQFUE5zOAKX66DqjLHHPKXOBr9gnLiSXLHs2WBc7JSe4Ww&amp;oe=6A97E249</t>
         </is>
       </c>
     </row>
@@ -7040,11 +7040,11 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Toalha de Papel Mili Gran Chef 200un</t>
+          <t>Pilha Alcalina Aaa Kian 4un</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
-        <v>7.49</v>
+        <v>4.99</v>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -7070,27 +7070,27 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Mocotó kg</t>
+          <t>Margarina Claybom 500g</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>8.99</v>
+        <v>5.49</v>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=27_NHNZ1YPEQ7kNvwFoKDXp&amp;_nc_oc=Adq93sm4yjujuKl2H9qKd7A-Ri6sPJ2O7h6MT7xu_2Gn_ICjD_O8jrpMyqpEq10pxog&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=zbuJQKO7MCB6qCV9cm71qw&amp;_nc_ss=7a22e&amp;oh=00_AQFoLPeW7mZwdNBlXkTxG1Z4Q8aI7FC9c9WBaNrB5U4a1g&amp;oe=6A966FA1</t>
+          <t>https://instagram.fbfh3-3.fna.fbcdn.net/v/t51.82787-15/786213187_18581670739067900_7614859529006382993_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MjU4MDUwMTEzMDg5NTg1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUxa-pkhp30Q7kNvwFboBxx&amp;_nc_oc=AdrdPmwYkIdxugjAF4fRL9r4UGVTOpjGSkUOEdAU1t5Oo3xndNO8NxT5cLPhdG2qyec&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-3.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQGIkcOFnuo_aKcrbniilp1lQXQOtK-0t77BIjYgYxXyNQ&amp;oe=6A97D3EB</t>
         </is>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>Ramin Supermercado</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
@@ -7100,11 +7100,11 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Salgadinho Orgânico Era Uma Vez Papapá 35g</t>
+          <t>Beterraba kg</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
-        <v>9.19</v>
+        <v>5.49</v>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
@@ -7113,14 +7113,14 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fagp5-1.fna.fbcdn.net/v/t51.82787-15/782413347_18423080377199090_2820046938058952728_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MTc0NDk1NjY5MzEzNzA5MzE4NDIzMDgwMzcxMTk5MDkw.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=1YNXWGkVTegQ7kNvwFnGD1y&amp;_nc_oc=Adqb-3k5FKK6WzXHVpCZ5gBoXBtn1gyQvQHQG9sMCMBgLMwbRjl9F2VhpR0XM09tP0M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fagp5-1.fna&amp;_nc_gid=3UEsjUfFydbfqZH2bgBZbA&amp;_nc_ss=7a22e&amp;oh=00_AQELzl4FrEMFD6d-zrVLwdU5dqNZXYf9Tk1UmsEmM7DyOQ&amp;oe=6A965A2B</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Ramin Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -7130,27 +7130,27 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Palitinhos de Vegetais Papapá 45g</t>
+          <t>Amendoim Oba Oba 400g</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>9.19</v>
+        <v>5.9</v>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fagp5-1.fna.fbcdn.net/v/t51.82787-15/782413347_18423080377199090_2820046938058952728_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MTc0NDk1NjY5MzEzNzA5MzE4NDIzMDgwMzcxMTk5MDkw.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=1YNXWGkVTegQ7kNvwFnGD1y&amp;_nc_oc=Adqb-3k5FKK6WzXHVpCZ5gBoXBtn1gyQvQHQG9sMCMBgLMwbRjl9F2VhpR0XM09tP0M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fagp5-1.fna&amp;_nc_gid=3UEsjUfFydbfqZH2bgBZbA&amp;_nc_ss=7a22e&amp;oh=00_AQELzl4FrEMFD6d-zrVLwdU5dqNZXYf9Tk1UmsEmM7DyOQ&amp;oe=6A965A2B</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -7160,27 +7160,27 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Bucho Bovino kg</t>
+          <t>Língua Bovina kg</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=27_NHNZ1YPEQ7kNvwFoKDXp&amp;_nc_oc=Adq93sm4yjujuKl2H9qKd7A-Ri6sPJ2O7h6MT7xu_2Gn_ICjD_O8jrpMyqpEq10pxog&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=zbuJQKO7MCB6qCV9cm71qw&amp;_nc_ss=7a22e&amp;oh=00_AQFoLPeW7mZwdNBlXkTxG1Z4Q8aI7FC9c9WBaNrB5U4a1g&amp;oe=6A966FA1</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -7190,11 +7190,11 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Fígado Bovino kg</t>
+          <t>Repolho Verde kg</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
@@ -7203,14 +7203,14 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=27_NHNZ1YPEQ7kNvwFoKDXp&amp;_nc_oc=Adq93sm4yjujuKl2H9qKd7A-Ri6sPJ2O7h6MT7xu_2Gn_ICjD_O8jrpMyqpEq10pxog&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=zbuJQKO7MCB6qCV9cm71qw&amp;_nc_ss=7a22e&amp;oh=00_AQFoLPeW7mZwdNBlXkTxG1Z4Q8aI7FC9c9WBaNrB5U4a1g&amp;oe=6A966FA1</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwHj1v_4&amp;_nc_oc=Ado90FjR93-zhwU94Lfyg-pdAM904p24Q7NJNp3LumI1HLaEihSxcBIwUsSt6VV6img&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQFUE5zOAKX66DqjLHHPKXOBr9gnLiSXLHs2WBc7JSe4Ww&amp;oe=6A97E249</t>
         </is>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -7220,27 +7220,27 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Fígado Bovino kg</t>
+          <t>Repolho Verde kg</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -7250,27 +7250,27 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Pepino em Conserva Pinduca 300g</t>
+          <t>Cabaré Ice 275ml</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>10.99</v>
+        <v>6.99</v>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/787853786_18195711469382122_4084613579796731411_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MzY3MjU2ODk4MzkzOTE2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mrOwFRh3sK8Q7kNvwGuiPxU&amp;_nc_oc=AdocWchk5QRpVZ8dLBXgW047kqu1zOIqox1GJTIk1w9BH6Gir0_2USO05ktxY04PMUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQFkCEs3hpn9RALf_1PUmHbNNicLtXSXUXy77R9obJWZgw&amp;oe=6A97CD87</t>
         </is>
       </c>
     </row>
     <row r="227" ht="20" customHeight="1">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -7280,27 +7280,27 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Pepino em Conserva Pinduca 300g</t>
+          <t>Cachorro Quente</t>
         </is>
       </c>
       <c r="D227" s="5" t="n">
-        <v>10.99</v>
+        <v>6.99</v>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
         </is>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Ramin Supermercado</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -7310,27 +7310,27 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Mocotó Bovino kg</t>
+          <t>Salgadinho Orgânico Era Uma Vez Papapá</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
-        <v>11.99</v>
+        <v>7.19</v>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://instagram.fyyc3-1.fna.fbcdn.net/v/t51.82787-15/782413347_18423080377199090_2820046938058952728_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MTc0NDk1NjY5MzEzNzA5MzE4NDIzMDgwMzcxMTk5MDkw.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fZGVmYXVsdF9jb3Zlcl9mcmFtZS5DMyJ9&amp;_nc_ohc=_cfhR42QcCUQ7kNvwEVGk_r&amp;_nc_oc=Ado_w16XBNCHwBLbzDOeTQJDleh4c3TzoW0JMumVkqZKmTQY4rj20SajQJVbxPiyleQXu3bok-FntkR8bFwJiwH9&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyyc3-1.fna&amp;_nc_gid=ecXOl_A4zJTN1oAGKz2wfg&amp;_nc_ss=7a22e&amp;oh=00_AQHT3ECLdF2vApx3v1bkkG4m23ox24HMfGZKejofRgAz4Q&amp;oe=6A97E3EB</t>
         </is>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
@@ -7340,27 +7340,27 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Bucho Bovino kg</t>
+          <t>Sucrilhos Kellogg's 240g</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
-        <v>11.99</v>
+        <v>7.49</v>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://instagram.fbfh3-2.fna.fbcdn.net/v/t51.82787-15/786993044_18581670784067900_4451038722088372453_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=106&amp;ig_cache_key=Mzk3MjU4MDU3NDQ4MDgyOTk0OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LMIY6vyvLpAQ7kNvwEERiL6&amp;_nc_oc=Adrqrk6k9A33-rTrGuk-JW1MM8PuvLEk3txmNTPJx5oIwWNot7-wrSoPlCsU5X3pR8g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-2.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQFcZZoNmk-6guewlsfvdi-tkB0z1BohQNthzoqZHyEFSg&amp;oe=6A97DC51</t>
         </is>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -7370,27 +7370,27 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Fígado Bovino kg</t>
+          <t>Toalha de Papel Mili Gran Chef 200un</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>12.99</v>
+        <v>7.49</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wecasNb-bicQ7kNvwHn2Ans&amp;_nc_oc=AdoaD9yhEQHxNxTT6dVW2831gh9YvtHOkjIyW0HrtAmSkQFq6pF2ab2IVMLYNpZqUqhBBxd2zWPq04gPZ1t49W4Z&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQF4a0Y9_NKwZXJwWZHMF9uqX0FiNsV42rdgjR5KMV-Bpw&amp;oe=6A9670CB</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
@@ -7400,27 +7400,27 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Mocotó Bovino kg</t>
+          <t>Morango Mape 250g</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
-        <v>12.99</v>
+        <v>7.99</v>
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wecasNb-bicQ7kNvwHn2Ans&amp;_nc_oc=AdoaD9yhEQHxNxTT6dVW2831gh9YvtHOkjIyW0HrtAmSkQFq6pF2ab2IVMLYNpZqUqhBBxd2zWPq04gPZ1t49W4Z&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQF4a0Y9_NKwZXJwWZHMF9uqX0FiNsV42rdgjR5KMV-Bpw&amp;oe=6A9670CB</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
         </is>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -7430,20 +7430,20 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Filé de Peito kg</t>
+          <t>Brócolis Ou Couve Flor</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>13.99</v>
+        <v>7.99</v>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/784389246_18581502034067900_514741470007781001_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MjE4Nzk0NDI0MDc2NjUyOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=axgGxUji1CYQ7kNvwF5yFe_&amp;_nc_oc=AdoPdvXKkxhOnuhRHqGiq6Pt03mMi3YFrFv35FgdwDW_XLaCuthau9xVtjxvSvd3Et0&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQGnyh9C5KtZnA7Clr6PJqSdV_he0XIhN4EcSf3kil01jw&amp;oe=6A967986</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
@@ -7460,11 +7460,11 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Moela Perdigão 1kg</t>
+          <t>Mocotó kg</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
-        <v>13.99</v>
+        <v>8.99</v>
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=27_NHNZ1YPEQ7kNvwFoKDXp&amp;_nc_oc=Adq93sm4yjujuKl2H9qKd7A-Ri6sPJ2O7h6MT7xu_2Gn_ICjD_O8jrpMyqpEq10pxog&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.cdninstagram.com&amp;_nc_gid=zbuJQKO7MCB6qCV9cm71qw&amp;_nc_ss=7a22e&amp;oh=00_AQFoLPeW7mZwdNBlXkTxG1Z4Q8aI7FC9c9WBaNrB5U4a1g&amp;oe=6A966FA1</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=40xkhSQE8g4Q7kNvwHrZ6fS&amp;_nc_oc=AdrQwhyO2locrqA9fhJGOet0h1z6OSsYR_JGHtkSpAE_SO1Qxhq4nZ1AaPAQZOIjiCM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=piuLZ9j-qv6denTdiMpN-w&amp;_nc_ss=7a22e&amp;oh=00_AQHlBvIUNmHk7i3Qkz9ssRG8EZJIjOAq6Lm63Ods05W5Gw&amp;oe=6A97C121</t>
         </is>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -7490,27 +7490,27 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Aperitivo Raiz Amarga Paratudo 900ml</t>
+          <t>Bucho Bovino kg</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>14.49</v>
+        <v>9.99</v>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787798079_1360550486164909_1488167338527184913_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzE1NjQ3MjAzMzA0ODEyMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=_YSRXBR_xEAQ7kNvwGz-Jto&amp;_nc_oc=AdpLlJzkYRevw0CSLWuqB-KI2jK2tnW7KUxNYwMqDutU8aJJamvN2PScwwK8KVSNNW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQFOWvfPu9eQQSbEeGxpEzc_ICisAWZEBaBd3B4eIkUSZg&amp;oe=6A966BD5</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=40xkhSQE8g4Q7kNvwHrZ6fS&amp;_nc_oc=AdrQwhyO2locrqA9fhJGOet0h1z6OSsYR_JGHtkSpAE_SO1Qxhq4nZ1AaPAQZOIjiCM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=piuLZ9j-qv6denTdiMpN-w&amp;_nc_ss=7a22e&amp;oh=00_AQHlBvIUNmHk7i3Qkz9ssRG8EZJIjOAq6Lm63Ods05W5Gw&amp;oe=6A97C121</t>
         </is>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -7520,27 +7520,27 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Raiz Amarga Paratudo 900ml</t>
+          <t>Fígado Bovino kg</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
-        <v>14.49</v>
+        <v>9.99</v>
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Y9MsBJNTALEQ7kNvwGWInLu&amp;_nc_oc=AdpddtOg1iPztqTH7eT-YWFaB54UHVZOR9Da1l8Mt7vhLBC-6BjRzHEH7wd_T0diJ_k&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQG49cO8fhv8rCMyE6ScwuXA1ai2xKhoND925OUDpDHoLQ&amp;oe=6A967010</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=40xkhSQE8g4Q7kNvwHrZ6fS&amp;_nc_oc=AdrQwhyO2locrqA9fhJGOet0h1z6OSsYR_JGHtkSpAE_SO1Qxhq4nZ1AaPAQZOIjiCM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=piuLZ9j-qv6denTdiMpN-w&amp;_nc_ss=7a22e&amp;oh=00_AQHlBvIUNmHk7i3Qkz9ssRG8EZJIjOAq6Lm63Ods05W5Gw&amp;oe=6A97C121</t>
         </is>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -7550,20 +7550,20 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Amendoim Mape 1kg</t>
+          <t>Fígado Bovino kg</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>14.99</v>
+        <v>9.99</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-2.cdninstagram.com/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwEMPYyR&amp;_nc_oc=Adr_b1bUKeRFPM7ZmqdRxfot36hQCNU24IL5_Efa9ytO3ogM1bBZT4MQjmZ9FH6Ptko&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-2.cdninstagram.com&amp;_nc_gid=AvC9Q5d1SS9-m3_hZ18qNA&amp;_nc_ss=7a22e&amp;oh=00_AQE80woS5j4qXeeidrqbdKnZmc1O3XfaeZ4vl-pHtiNMhQ&amp;oe=6A965889</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Rodo Para Pia de Plástico Esfrebom Bettanin</t>
+          <t>Geleia de Morango Olé 160g</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
-        <v>15.9</v>
+        <v>10.49</v>
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/785059096_1358646486355309_4355252955160182464_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MTUyNDg5Njc4NTk1NzI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=7xcost5b2JkQ7kNvwEnl6NG&amp;_nc_oc=AdqptSuugfcQCpnKtC8y8_X03y7LGAz76AxgMW-xz-FOEaPHIf72wDHlcnh4-YEihYkk7-O5dYN4yXHthGkA_Eqa&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQEWfwE-2Dq-ZjjamD5oThXrOSuwFZE1sbx6lGUmcSiaZA&amp;oe=6A97C241</t>
         </is>
       </c>
     </row>
@@ -7610,11 +7610,11 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Caixa Organizadora com Tampa Bioprátika Pleion 8L</t>
+          <t>Pepino em Conserva Pinduca 300g</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>18.9</v>
+        <v>10.99</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -7640,27 +7640,27 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Músculo com Osso kg</t>
+          <t>Maracujá Azedo kg</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
-        <v>18.99</v>
+        <v>10.99</v>
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786467846_18581501911067900_1635849977930495039_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MjE4NzkxMTEzMDgyMDgwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=68dX_CMI8T8Q7kNvwHpguAF&amp;_nc_oc=AdpvJ8hg4jzx9Q7uK8qPvuWvKrWMP08Oeehoujr6Wpc2QxbpMYPcxWGkg2NQUSOk7C4&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQEXezKQKLTebF6L1-4Q53oshrrGdQxlFh_KVpPH4RViYA&amp;oe=6A964FDA</t>
+          <t>https://instagram.fmel18-1.fna.fbcdn.net/v/t51.82787-15/786266669_17907135252496981_2844548241403019285_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTUxMTIzMTEyNDUyNjczMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=JjKOSCyFILYQ7kNvwGlh1nD&amp;_nc_oc=AdoBPep20AvuUTKELGudybUAklw8jl_X9Ek70Sj4oVpCqiQqdegGPdF0zhG-3uWh1Y8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fmel18-1.fna&amp;_nc_gid=7UfXIm5xeBR2yom4laodcg&amp;_nc_ss=7a22e&amp;oh=00_AQGWz_45ZxNcnZwpw4KxUsNYYcotG8lAkvxFuQPZ2Qy-6w&amp;oe=6A97AEC9</t>
         </is>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -7670,11 +7670,11 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Gel Fixador Bozzano 300g</t>
+          <t>Mocotó Bovino kg</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>18.99</v>
+        <v>11.99</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -7700,27 +7700,27 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Músculo com Osso kg</t>
+          <t>Bucho Bovino kg</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
-        <v>24.48</v>
+        <v>11.99</v>
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMiJ9&amp;_nc_ohc=XsYkt3_1l6QQ7kNvwHvPqBK&amp;_nc_oc=AdoxHccv3l1ezOe2SRiaKdoIKylxRFAMAa-bcY8i1nMbLQRho8hGGxaPwVCiK9K63Rk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=l2Ws1l6EHCFje39eqZ55ow&amp;_nc_ss=7a22e&amp;oh=00_AQFDMDGgiy16J0IXYT6xj-Xo6NU7bSN7xPfmly_JDARCug&amp;oe=6A965EFA</t>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
         </is>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -7730,11 +7730,11 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Ponta de Peito com Osso kg</t>
+          <t>Fígado Bovino kg</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>24.99</v>
+        <v>12.99</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -7743,14 +7743,14 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786467846_18581501911067900_1635849977930495039_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MjE4NzkxMTEzMDgyMDgwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=68dX_CMI8T8Q7kNvwHpguAF&amp;_nc_oc=AdpvJ8hg4jzx9Q7uK8qPvuWvKrWMP08Oeehoujr6Wpc2QxbpMYPcxWGkg2NQUSOk7C4&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQEXezKQKLTebF6L1-4Q53oshrrGdQxlFh_KVpPH4RViYA&amp;oe=6A964FDA</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=SYZyJZ31VbUQ7kNvwEOWs2J&amp;_nc_oc=AdqpKjKxsZ7ot3N4oU482_9TygvblCc4tjiTCLWYc7ObnRUvJsRErOJIoA5fvHYgu0Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQHHkJomv6yUMRLSyd_iHYBiT3rTwwZIlyeWwGP1KkFidA&amp;oe=6A97C24B</t>
         </is>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -7760,11 +7760,11 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Filé de Agulha kg</t>
+          <t>Mocotó Bovino kg</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
-        <v>25.99</v>
+        <v>12.99</v>
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
@@ -7773,14 +7773,14 @@
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fqpa2-1.fna.fbcdn.net/v/t51.82787-15/786467846_18581501911067900_1635849977930495039_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MjE4NzkxMTEzMDgyMDgwNA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=68dX_CMI8T8Q7kNvwHpguAF&amp;_nc_oc=AdpvJ8hg4jzx9Q7uK8qPvuWvKrWMP08Oeehoujr6Wpc2QxbpMYPcxWGkg2NQUSOk7C4&amp;_nc_ad=z-m&amp;_nc_cid=1007&amp;_nc_zt=23&amp;_nc_ht=instagram.fqpa2-1.fna&amp;_nc_gid=i0WVNSltBBtBZMld_QiciA&amp;_nc_ss=7a22e&amp;oh=00_AQEXezKQKLTebF6L1-4Q53oshrrGdQxlFh_KVpPH4RViYA&amp;oe=6A964FDA</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=SYZyJZ31VbUQ7kNvwEOWs2J&amp;_nc_oc=AdqpKjKxsZ7ot3N4oU482_9TygvblCc4tjiTCLWYc7ObnRUvJsRErOJIoA5fvHYgu0Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQHHkJomv6yUMRLSyd_iHYBiT3rTwwZIlyeWwGP1KkFidA&amp;oe=6A97C24B</t>
         </is>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Supermercado Tuiuiú</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -7790,27 +7790,27 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Salgadinho kg</t>
+          <t>Waffle Catupiry 240g</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
-        <v>29.99</v>
+        <v>12.99</v>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/786213187_18581670739067900_7614859529006382993_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MjU4MDUwMTEzMDg5NTg1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PKu5sCqaXh0Q7kNvwEZtR1F&amp;_nc_oc=AdrXnq9-E_K9Ar0dU2z_3MTrPlViu9NeiIkkLyH1ovDDVgRakx0nMLgvofX44g9PCKQdYELhczrdPChbWwcfmlyE&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQFP-keuWSslHivgVtK2a45M4wCXZwnVyjGnvVIAzWEO8Q&amp;oe=6A96826B</t>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
         </is>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -7820,11 +7820,11 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Creme de Pentear Salon Line 1kg</t>
+          <t>Moela Perdigão 1kg</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
-        <v>29.99</v>
+        <v>13.99</v>
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
@@ -7833,14 +7833,14 @@
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.ffuk1-1.fna.fbcdn.net/v/t51.82787-15/786158033_17906990622496981_4554436689859059284_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MDc1Nzk3MTU2NDU0MjYxMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=e8Edeo1LUSMQ7kNvwFDrBk2&amp;_nc_oc=Adqzn6Bjmkdn0CVNHW8fWR-x4q2Jm9LyztIwrb1H_55ZiqTojaLtlvOKaXN5oVtaKDvrLYbvHsicZly3O1fwIZds&amp;_nc_ad=z-m&amp;_nc_cid=1700&amp;_nc_zt=23&amp;_nc_ht=instagram.ffuk1-1.fna&amp;_nc_gid=oyc2vinubaI_F8oMEOxmWA&amp;_nc_ss=7a22e&amp;oh=00_AQFkRP_MezZhrd5PQXMlDm3GIkauDG_EplHb2Vb0e8p3tQ&amp;oe=6A965F8B</t>
+          <t>https://scontent-gmp1-1.cdninstagram.com/v/t51.82787-15/779866028_18195137623382122_1225681475285530325_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=104&amp;ig_cache_key=Mzk3MDg5NTAzMjEwMDYxNzYxMA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMzI0OC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=40xkhSQE8g4Q7kNvwHrZ6fS&amp;_nc_oc=AdrQwhyO2locrqA9fhJGOet0h1z6OSsYR_JGHtkSpAE_SO1Qxhq4nZ1AaPAQZOIjiCM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-gmp1-1.cdninstagram.com&amp;_nc_gid=piuLZ9j-qv6denTdiMpN-w&amp;_nc_ss=7a22e&amp;oh=00_AQHlBvIUNmHk7i3Qkz9ssRG8EZJIjOAq6Lm63Ods05W5Gw&amp;oe=6A97C121</t>
         </is>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Bom Jesus Primavera do Leste 🛒</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -7850,20 +7850,20 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Short Ribs e Shoulder Steak kg</t>
+          <t>Raiz Amarga Paratudo 900ml</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>31.99</v>
+        <v>14.49</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=wecasNb-bicQ7kNvwHn2Ans&amp;_nc_oc=AdoaD9yhEQHxNxTT6dVW2831gh9YvtHOkjIyW0HrtAmSkQFq6pF2ab2IVMLYNpZqUqhBBxd2zWPq04gPZ1t49W4Z&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQF4a0Y9_NKwZXJwWZHMF9uqX0FiNsV42rdgjR5KMV-Bpw&amp;oe=6A9670CB</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/787104328_1360550532831571_2281243341389434448_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MTc1NjIxMzA2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=BsEfA1wdsJMQ7kNvwElvBVw&amp;_nc_oc=AdotN0eHRtVwjkYS0BuXdsQlOICDI0TjH6XabtYEUFgI3kDuSHHjpm2VB3u6rM5ijWM&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQE7taI2tGK-qgb5ER4PL83BiadNx5mlrZy3hOjhiZuBuw&amp;oe=6A97C190</t>
         </is>
       </c>
     </row>
@@ -7880,27 +7880,27 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Creme Facial Garnier 85g</t>
+          <t>Amendoim Mape 1kg</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
-        <v>31.99</v>
+        <v>14.99</v>
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fadl5-1.fna.fbcdn.net/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwEpJglj&amp;_nc_oc=Adqu2KqnSf50G7TDxOquJ2uamr8oO9jzHi_BQy2aFOqyIb5SSEpi_QgfU5z94oW6Unw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fadl5-1.fna&amp;_nc_gid=zss7cGQMVjPM9PMJWPayKQ&amp;_nc_ss=7a22e&amp;oh=00_AQH6uxTgwUTWP_uXSgSbjVJi8nei0-SRcac-_DjyWODW4Q&amp;oe=6A96812E</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/784817810_18374239453237813_2825750323987932425_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=111&amp;ig_cache_key=Mzk3MDc4NzgzNDU3MDQ3NjY3NQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=P7IruUnPC1sQ7kNvwHj1v_4&amp;_nc_oc=Ado90FjR93-zhwU94Lfyg-pdAM904p24Q7NJNp3LumI1HLaEihSxcBIwUsSt6VV6img&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=ZNXNGK1plMjaDRCkkAylFA&amp;_nc_ss=7a22e&amp;oh=00_AQFUE5zOAKX66DqjLHHPKXOBr9gnLiSXLHs2WBc7JSe4Ww&amp;oe=6A97E249</t>
         </is>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Machadão Atacadista</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -7910,20 +7910,20 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Ponta de Peito Bovina kg</t>
+          <t>Rodo Para Pia Bettanin Esfrebom</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>34.99</v>
+        <v>15.9</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-fra3-1.cdninstagram.com/v/t51.82787-15/781425562_18192143110391764_1116124836587707156_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODk1MTQ4MDU4NDU2NzM5OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=hgLrqZMAdhsQ7kNvwEbw-5J&amp;_nc_oc=AdqMJnvK7o8Kx-WAwUJ2fdrF5KLMr6OzsI_0vq4LJVMC41DGK35roPYoUOxAvCDM7Jg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=FOgLUhHVTJ7XwYsIrtKNkQ&amp;_nc_ss=7a22e&amp;oh=00_AQHPwVnGq7ROV6gjQY2UsBm9sW934g0A9MrJcEShyx3c8g&amp;oe=6A967AA0</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
@@ -7940,11 +7940,11 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Frigideira Wok Alumínio sem Tampa Loreto Tramontina 28cm</t>
+          <t>Caixa Organizadora com Tampa Pleion Bioprátika 8L</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
-        <v>52.9</v>
+        <v>18.9</v>
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
@@ -7965,25 +7965,25 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Padaria / Congelados</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Pão de Queijo Cuiabá 1kg</t>
+          <t>Gel Fixador Bozzano 300g</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
-        <v>9.99</v>
+        <v>18.99</v>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwHdQvVN&amp;_nc_oc=Adr2jz83g1HMFZbddfvWSC0pL4rnuXe_n9d4o8qnNRSzg_ggtsdVyqHY1_rraZXke4fM-PacFcpd2ny--CV4tB30&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=WvhUxQv6PEktrzXyczPSSw&amp;_nc_ss=7a22e&amp;oh=00_AQGA5eHj920O_UhzUyPP2raQEwWZYO8b3KtcsEODu3jKRg&amp;oe=6A9666A5</t>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
         </is>
       </c>
     </row>
@@ -7995,55 +7995,55 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Padaria / Congelados</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Pão de Queijo kg</t>
+          <t>Carvão Paraná 5kg</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
-        <v>18.99</v>
+        <v>19.99</v>
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/786213187_18581670739067900_7614859529006382993_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MjU4MDUwMTEzMDg5NTg1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PKu5sCqaXh0Q7kNvwEZtR1F&amp;_nc_oc=AdrXnq9-E_K9Ar0dU2z_3MTrPlViu9NeiIkkLyH1ovDDVgRakx0nMLgvofX44g9PCKQdYELhczrdPChbWwcfmlyE&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQFP-keuWSslHivgVtK2a45M4wCXZwnVyjGnvVIAzWEO8Q&amp;oe=6A96826B</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/788141803_1720016743465477_9146230528598203595_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODE5NDkyODIxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=zal2Q-KNBSMQ7kNvwHPjmHr&amp;_nc_oc=AdqbcNw8SJgkOLjv1S7OR3EO3j7y30zWKGkWsahq3R8bq5H_zt52u3sZtfAXG8TZgRQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQEr-SUAeVtvw-YnVKjGXDiWw84vTzRbtyyL_ngY1HNfgg&amp;oe=6A97C1F6</t>
         </is>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Padaria / Congelados</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Pão de Queijo kg</t>
+          <t>Cuca Recheada kg</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>19.99</v>
+        <v>23.49</v>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
         </is>
       </c>
     </row>
@@ -8055,175 +8055,655 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Padaria / Pães</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Pão Francês kg</t>
+          <t>Ponta de Peito com Osso kg</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>9.99</v>
+        <v>23.99</v>
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/786213187_18581670739067900_7614859529006382993_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MjU4MDUwMTEzMDg5NTg1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=PKu5sCqaXh0Q7kNvwEZtR1F&amp;_nc_oc=AdrXnq9-E_K9Ar0dU2z_3MTrPlViu9NeiIkkLyH1ovDDVgRakx0nMLgvofX44g9PCKQdYELhczrdPChbWwcfmlyE&amp;_nc_ad=z-m&amp;_nc_cid=1088&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=wq5LuXijk1jgdzQyiugWpw&amp;_nc_ss=7a22e&amp;oh=00_AQFP-keuWSslHivgVtK2a45M4wCXZwnVyjGnvVIAzWEO8Q&amp;oe=6A96826B</t>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/784321179_1720016750132143_1243001508239248716_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzM0Mjg4MDE3NDY4MTI1NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=uLCBohPgPQYQ7kNvwENG2o2&amp;_nc_oc=AdpIqeRD6CvgVgXKFFWA9WTGUuT7vNppdBJWZemIje2bYmfmlfu3V76RDLQg2A630bg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQFOJaDCH3v0kUninhna4d-YzKlGOwpdtLMzyArKVwtmZA&amp;oe=6A97B219</t>
         </is>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Padaria / Pães</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Pão de Alho Boua 300g</t>
+          <t>Rosca Doce kg</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>10.99</v>
+        <v>23.99</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.ftgz2-1.fna.fbcdn.net/v/t51.82787-15/780140079_18192045034391764_7683991793781918786_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk2ODIxODA0ODc2ODI1MjE2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Su6wo4o_AAEQ7kNvwHKsvI3&amp;_nc_oc=AdqHpQCsDBNaEZ5-X3EB8Zab-Osn52r0xSN9LEgOV7g7pquqHCd3QeJEZZEJGdA8DBdiiAxREbsS1CzcBJWTbAD1&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.ftgz2-1.fna&amp;_nc_gid=oHv5kAUjL6YyUqpH14-hmg&amp;_nc_ss=7a22e&amp;oh=00_AQEbsXV5g3m3qWtjHn92eEIkWanBuU9SlaCt1suJ0gW0tA&amp;oe=6A966A2E</t>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
         </is>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Padaria / Pães</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Faca Para Pão Inox 7 Plenus Tramontina</t>
+          <t>Músculo com Osso kg</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
-        <v>15.9</v>
+        <v>24.48</v>
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://scontent-cdg4-1.cdninstagram.com/v/t39.30808-6/784428542_1503489418490841_697405957732902936_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MTgyNzk2NDE0ODc5MzU5NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTYzOS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=lahhkTUGus0Q7kNvwH9S1HS&amp;_nc_oc=Adqzpe26NNEIgL11_-99PbnwKKsNOTm7mJQpQTT7Z3ezDvmT5yoHime4NpgbtneZf4PRFVoMnTfPUSGIQXrbL9uN&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg4-1.cdninstagram.com&amp;_nc_gid=dBWbPpDbzRAuRx_PrvAKAA&amp;_nc_ss=7a22e&amp;oh=00_AQHGTds9cP7jlOi84o9CH_61OUSC_zTxDXtf1nHP1C5PnQ&amp;oe=6A97B07A</t>
         </is>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Machadão Atacadista</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Pet Shop</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Espeto de Bambu Theoto 30cm</t>
+          <t>Salgadinho kg</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
-        <v>3.99</v>
+        <v>29.99</v>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+          <t>https://instagram.fbfh3-3.fna.fbcdn.net/v/t51.82787-15/786213187_18581670739067900_7614859529006382993_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MjU4MDUwMTEzMDg5NTg1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUxa-pkhp30Q7kNvwFboBxx&amp;_nc_oc=AdrdPmwYkIdxugjAF4fRL9r4UGVTOpjGSkUOEdAU1t5Oo3xndNO8NxT5cLPhdG2qyec&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-3.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQGIkcOFnuo_aKcrbniilp1lQXQOtK-0t77BIjYgYxXyNQ&amp;oe=6A97D3EB</t>
         </is>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Pet Shop</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Coração Bovino kg</t>
+          <t>Short Ribs e Shoulder Steak kg</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
-        <v>6.99</v>
+        <v>31.99</v>
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=6V6MUSXxtWEQ7kNvwEiX9Iy&amp;_nc_oc=AdrQCKzt2IP-ocFF-FbaYs3Q4kwNC6iyh3WBRnpuYUxZJFYGurB5QVHUAv2UKzzbNhLZr8L5iiVMZ__Z0GwnMa4v&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=_6Bjz1Qe-apFUvGe8-R7zg&amp;_nc_ss=7a22e&amp;oh=00_AQHDedMdFifYxvYbiz35fID0ZSN6roivKw5gK-ObWEzJCw&amp;oe=6A9672A8</t>
+          <t>https://instagram.fktw4-1.fna.fbcdn.net/v/t51.82787-15/786837850_18374533663237813_2968687181146751427_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MjE2ODE2MTY3MzMwMjgxMg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=SYZyJZ31VbUQ7kNvwEOWs2J&amp;_nc_oc=AdqpKjKxsZ7ot3N4oU482_9TygvblCc4tjiTCLWYc7ObnRUvJsRErOJIoA5fvHYgu0Q&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw4-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQHHkJomv6yUMRLSyd_iHYBiT3rTwwZIlyeWwGP1KkFidA&amp;oe=6A97C24B</t>
         </is>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Creme Facial Garnier 85g</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw6-1.cdninstagram.com/v/t51.82787-15/787993259_18374687005237813_4471412213431393234_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=103&amp;ig_cache_key=Mzk3Mjk0NzA1MzQ4MTkxNTUyNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTM1MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=TDgSfUoaAVwQ7kNvwE3sOCc&amp;_nc_oc=AdqzWjaXc6bH3BxmN2INlXg38VwZxgJPdGRVLyU79fbG2qcAV9kRGZAX4dK0Kj-ce_0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-1.cdninstagram.com&amp;_nc_gid=6vV7-Oiifa_xz_COki9TZw&amp;_nc_ss=7a22e&amp;oh=00_AQHeG3BbFNY52DhlT8aEMdGg-JNF1o7ooddEWqmgZ6yjDw&amp;oe=6A97D2AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="20" customHeight="1">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>Chipa kg</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E259" s="4" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="20" customHeight="1">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Ponta de Peito Bovina kg</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/787853786_18195711469382122_4084613579796731411_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MzY3MjU2ODk4MzkzOTE2MQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=mrOwFRh3sK8Q7kNvwGuiPxU&amp;_nc_oc=AdocWchk5QRpVZ8dLBXgW047kqu1zOIqox1GJTIk1w9BH6Gir0_2USO05ktxY04PMUA&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQFkCEs3hpn9RALf_1PUmHbNNicLtXSXUXy77R9obJWZgw&amp;oe=6A97CD87</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="20" customHeight="1">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
           <t>Machadão Atacadista</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>Alicate de Cutícula Tramontina Inox</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="E261" s="4" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/786543128_1358645369688754_2779017979935584164_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk3MTUyNDg5NTIzNDEwNDA4Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=fkD66OU_vJ8Q7kNvwGVhQFg&amp;_nc_oc=AdqVV41Y6EDPDc8woKC8acJQ50fyLaMqyxqQ6XwSb0QTw7zKiZe9fCHQdh0YmvCey2oCLfsQ1SDBgH5U1MsSEJJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=oEBPHF74--AW6nyv447F6g&amp;_nc_ss=7a22e&amp;oh=00_AQF4nQ2o1bdHwhk4KCm8m6hwk4bO-EEhkiU9BWMVDhXWGw&amp;oe=6A97B484</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="20" customHeight="1">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Frigideira Wok Alumínio sem Tampa Tramontina Loreto 28cm</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="20" customHeight="1">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>Aperol 750ml</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="E263" s="4" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-bos5-1.cdninstagram.com/v/t39.30808-6/788413222_1505168981656218_2918311736305518854_n.jpg?stp=c0.0.1638.2047a_dst-jpg_e35_s1638x2047_tt6&amp;_nc_cat=107&amp;ig_cache_key=Mzk3MzI3Njk2ODIzODI0MjE0OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=G9lgZfFlLu0Q7kNvwF_JwlB&amp;_nc_oc=Adq9GwtOFmluK0l6bqtQD3-7JUdW48aHa_sTCsAnFrPTnylb2VgrBqoFFUk8N2umuJc&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-bos5-1.cdninstagram.com&amp;_nc_gid=tefus2BYMonKcSKoKgJN5Q&amp;_nc_ss=7a22e&amp;oh=00_AQF_adVKWUB6yUSzhjAFyPiJHdJ3qkmFIpb3HWhALtZ2Rw&amp;oe=6A97B160</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="20" customHeight="1">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Bom Jesus Primavera do Leste 🛒</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Congelados</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Pão de Queijo Cuiabá 1kg</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fktw1-1.fna.fbcdn.net/v/t51.82787-15/786656678_18374533654237813_1357775697752571265_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjE2ODE2MTUzODk3MjI2NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=E3K-BzvU7NkQ7kNvwFPD8M5&amp;_nc_oc=AdpseN54VqnZluFjH3qZ3rqjr8o1Hw7zh3OQ3cCkAXd_RWyrjKvomWBm06_Oo4KrtaQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fktw1-1.fna&amp;_nc_gid=PKeWG31E_OO96xbNbCbRww&amp;_nc_ss=7a22e&amp;oh=00_AQETuNAiKLK4FGxp6nx1-cMLS1tROLflzjRGHMmrNTfC9A&amp;oe=6A97B825</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="20" customHeight="1">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Congelados</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>Pão de Queijo Cuiabá 1kg</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="E265" s="4" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="20" customHeight="1">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Tuiuiú</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Congelados</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Pão de Queijo kg</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.fbfh3-3.fna.fbcdn.net/v/t51.82787-15/786213187_18581670739067900_7614859529006382993_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MjU4MDUwMTEzMDg5NTg1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUxa-pkhp30Q7kNvwFboBxx&amp;_nc_oc=AdrdPmwYkIdxugjAF4fRL9r4UGVTOpjGSkUOEdAU1t5Oo3xndNO8NxT5cLPhdG2qyec&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-3.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQGIkcOFnuo_aKcrbniilp1lQXQOtK-0t77BIjYgYxXyNQ&amp;oe=6A97D3EB</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="20" customHeight="1">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Congelados</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>Pão de Queijo kg</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E267" s="4" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="20" customHeight="1">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado Tuiuiú</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Pão de Alho Bello 300g</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-man2-1.cdninstagram.com/v/t39.30808-6/788141803_1720016743465477_9146230528598203595_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=108&amp;ig_cache_key=Mzk3MzM0Mjg3ODE5NDkyODIxMw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTI1NC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=zal2Q-KNBSMQ7kNvwHPjmHr&amp;_nc_oc=AdqbcNw8SJgkOLjv1S7OR3EO3j7y30zWKGkWsahq3R8bq5H_zt52u3sZtfAXG8TZgRQ&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-man2-1.cdninstagram.com&amp;_nc_gid=Oh1mrcvHg1sPnWTYozeyJw&amp;_nc_ss=7a22e&amp;oh=00_AQEr-SUAeVtvw-YnVKjGXDiWw84vTzRbtyyL_ngY1HNfgg&amp;oe=6A97C1F6</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="20" customHeight="1">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>Supermercado Tuiuiú</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>Pão Francês kg</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fbfh3-3.fna.fbcdn.net/v/t51.82787-15/786213187_18581670739067900_7614859529006382993_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk3MjU4MDUwMTEzMDg5NTg1Ng%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FUxa-pkhp30Q7kNvwFboBxx&amp;_nc_oc=AdrdPmwYkIdxugjAF4fRL9r4UGVTOpjGSkUOEdAU1t5Oo3xndNO8NxT5cLPhdG2qyec&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbfh3-3.fna&amp;_nc_gid=2X_YrJQXGUE-xy0wvXJaew&amp;_nc_ss=7a22e&amp;oh=00_AQGIkcOFnuo_aKcrbniilp1lQXQOtK-0t77BIjYgYxXyNQ&amp;oe=6A97D3EB</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="20" customHeight="1">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Supermercado São Pedro</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Pão de Alho Zinho 300g</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t51.82787-15/785599572_18195711460382122_5575322653184498920_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=109&amp;ig_cache_key=Mzk3MzY3MjU2OTQ3ODkxNjI0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=YlNv7Hxcm4EQ7kNvwGx0pvY&amp;_nc_oc=AdoNo6jjN9Aczf5Z8_cThIpbEt2ZDwe1YcQr7tZJtAOVSaVTC6gxm5Ibv5Ll5A3z-AE&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=Ch_pIkgnkh3nrU1AQJdMyg&amp;_nc_ss=7a22e&amp;oh=00_AQGXyVQwL6jgmiS_0oeTZz_hiLb7FmTqsSvsVWsYZAMQcg&amp;oe=6A97B292</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="20" customHeight="1">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Padaria / Pães</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>Faca Para Pão Inox Tramontina Plenus 7</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="E271" s="4" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="20" customHeight="1">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>Pet Shop</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>Ração Para Cães Gold Premium Filhote Bob Dog 15kg</t>
-        </is>
-      </c>
-      <c r="D258" s="3" t="n">
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Palito Espeto de Bambu Theoto 30cm</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="20" customHeight="1">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>Super Compras Supermercado</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Pet Shop</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Coração Bovino kg</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E273" s="4" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>https://instagram.fblq4-1.fna.fbcdn.net/v/t51.82787-15/788172202_18192669184391764_5816935157600731829_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=102&amp;ig_cache_key=Mzk3MjU2Mjg0NTk4OTQwNjA0Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkZFRUQueHBpZHMuMTQ0MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=LRlDAksdQ-AQ7kNvwH5A0p9&amp;_nc_oc=AdpLU-hFXp99iVl4paH_lhV01ASOYInyZ1bj52QO6ruRQ7Mn_SdpUoTjTXcGx6ov0Q4&amp;_nc_ad=z-m&amp;_nc_cid=1093&amp;_nc_zt=23&amp;_nc_ht=instagram.fblq4-1.fna&amp;_nc_gid=a_sG6VtFpGKB5iM0z0UKjg&amp;_nc_ss=7a22e&amp;oh=00_AQGNjb1_ysBtXgfBVfmo3P9bZ9DRLY-m9edcQGHgOI2OJA&amp;oe=6A97C428</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="20" customHeight="1">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Machadão Atacadista</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>Pet Shop</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Ração Para Cães Filhotes Bob Dog Gold Premium 15kg</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="n">
         <v>144.9</v>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>27/08/2026</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
-        <is>
-          <t>https://instagram.fyto2-1.fna.fbcdn.net/v/t39.30808-6/786141071_1360550506164907_1343288441209680541_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjAxNjIzNDQ4NA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=aMK5GLv5FBcQ7kNvwEDMxh0&amp;_nc_oc=AdpWuxL4VLkbZ6DZN4-vuIq-jU9vlST0z0KDqlNXDoTt1WlcYsRB4fwhiJICSYvj0xw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fyto2-1.fna&amp;_nc_gid=IXal9zDDXfZ0GyqCGxQXgg&amp;_nc_ss=7a22e&amp;oh=00_AQHbXvyWTmBTgINHFv510Kl1nd7qoQ2vyD-goSfn6iagJA&amp;oe=6A9682F9</t>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-ams2-1.cdninstagram.com/v/t39.30808-6/786779086_1360550472831577_8028710268323392841_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk3MzE1NjQ3MjI0MjcxMDI2OQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTYzOC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=FB6gMN-plHsQ7kNvwEI_Aau&amp;_nc_oc=Adpk9TuDHJAEt-2DRtSAL4CPHvT-D_aTBGRH_qLtLWrhbouwvsyXh-7V7KsOEMgqKco&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ams2-1.cdninstagram.com&amp;_nc_gid=W_rvWCImryD4RVuLWt4E6A&amp;_nc_ss=7a22e&amp;oh=00_AQHiVY1kVu6um-rBCrL6_AYRPIfY1ELbXFb_x8byXLqb3g&amp;oe=6A97C76F</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8285,7 +8765,7 @@
         <v>53</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>14.57377358490566</v>
+        <v>14.58132075471698</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>2.39</v>
@@ -8301,10 +8781,10 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>17.11895833333334</v>
+        <v>25.15053571428572</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>1.99</v>
@@ -8316,115 +8796,96 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Mercado Talismã</t>
+          <t>Ramin Supermercado</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>21.615</v>
+        <v>10.31</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>16.99</v>
+        <v>7.19</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>25.99</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ramin Supermercado</t>
+          <t>SUPERMERCADO PARANAENSE</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>10.53</v>
+        <v>9.857999999999999</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>9.19</v>
+        <v>1.69</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>12.55</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SUPERMERCADO PARANAENSE</t>
+          <t>Super Compras Supermercado</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>11.00666666666667</v>
+        <v>9.223333333333333</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>29.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Super Compras Supermercado</t>
+          <t>Supermercado São Pedro</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>12.75193548387097</v>
+        <v>23.31933333333334</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1.59</v>
+        <v>2.69</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>47.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Supermercado São Pedro</t>
+          <t>Supermercado Tuiuiú</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>14.72678571428571</v>
+        <v>15.40934426229508</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2.89</v>
+        <v>0.99</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>46.98</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Supermercado Tuiuiú</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>14.12086956521739</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>44.99</v>
+        <v>50.85</v>
       </c>
     </row>
   </sheetData>
@@ -8492,10 +8953,10 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>23.15625</v>
+        <v>23.92777777777778</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>1.59</v>
@@ -8508,10 +8969,10 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>23.03</v>
+        <v>34.88384615384616</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>2.49</v>
@@ -8524,13 +8985,13 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>6.29</v>
+        <v>8.49</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>6.29</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -8540,10 +9001,10 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>10.701</v>
+        <v>16.09</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>5.79</v>
@@ -8556,13 +9017,13 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>13.59833333333333</v>
+        <v>13.75</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>8.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -8572,10 +9033,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>28.63565217391304</v>
+        <v>29.84178571428571</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>8.98</v>
@@ -8591,7 +9052,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>19.82</v>
+        <v>32.6725</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>16.9</v>
@@ -8604,13 +9065,13 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>16.739</v>
+        <v>17.36375</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>9.98</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -8623,10 +9084,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>26.65666666666667</v>
+        <v>22.99</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>25.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -8636,13 +9097,13 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>13.215</v>
+        <v>15.65666666666667</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1.79</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -8652,10 +9113,10 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>13.96</v>
+        <v>13.9675</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>2.99</v>
@@ -8668,10 +9129,10 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>5.838484848484849</v>
+        <v>8.138</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>2.39</v>
@@ -8684,13 +9145,13 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>14.11461538461539</v>
+        <v>29.39833333333334</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2.89</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -8700,13 +9161,13 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>9.921875</v>
+        <v>10.004</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -8719,10 +9180,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>12.97</v>
+        <v>16.39</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1.89</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -8732,13 +9193,13 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>17.99</v>
+        <v>17.49</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -8751,10 +9212,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -8764,10 +9225,10 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>6.112222222222223</v>
+        <v>6.881666666666667</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>0.99</v>
@@ -8780,13 +9241,13 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>22.59666666666666</v>
+        <v>22.695</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -8796,10 +9257,10 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>10.305</v>
+        <v>9.291666666666666</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>2.39</v>
@@ -8812,13 +9273,13 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>5.856666666666666</v>
+        <v>6.54</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -8831,10 +9292,10 @@
         <v>4</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>5.105</v>
+        <v>9.835000000000001</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1.49</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -8847,7 +9308,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>1.99</v>
+        <v>4.59</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>1.99</v>
@@ -8860,13 +9321,13 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>5.24</v>
+        <v>20.39333333333333</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -8876,10 +9337,10 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>12.89882352941177</v>
+        <v>14.62611111111111</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>1.99</v>
@@ -8892,10 +9353,10 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>16.32333333333333</v>
+        <v>15.24</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>9.99</v>
@@ -8908,10 +9369,10 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>12.29333333333333</v>
+        <v>12.2175</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>9.99</v>
